--- a/public/conference_list.xlsx
+++ b/public/conference_list.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Conference</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Submission fee</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Topics of interest</t>
         </is>
@@ -468,27 +456,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Florida State University Truist Beach Conference</t>
+          <t>2026 Global AI Finance Research Conference</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hilton Sandestin Beach Golf Resort and Spa, Miramar Beach, Florida</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -498,71 +486,71 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>All areas of finance (empirical and theoretical)</t>
+          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Adam Smith Workshops 2026</t>
+          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>London Business School</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>99.00 USD</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Asset Pricing, Behavioral Finance, Corporate Finance, Financial Intermediation, Household Finance, International Finance (papers in all areas of finance; two parallel streams for Asset Pricing and Corporate Finance, plus a joint session)</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, decision making under risk and uncertainty, venture startups &amp; exits, trust in financial markets, sustainable finance, behavioral finance in retirement saving &amp; planning, and nudging clients and markets.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>International Conference on Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF 2026)</t>
+          <t>Colorado Finance Summit 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kingdom of Bahrain</t>
+          <t>Vail, Colorado</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -572,71 +560,71 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climate Finance; Artificial Intelligence (AI) and Machine Learning in Finance and Accounting; Green Finance, Sustainable Finance, ESG Reporting, and Climate Risk; FinTech, Blockchain, and Digital Currencies; Corporate Governance and Technological Innovation; Big Data in Accounting and Finance; Green Accounting and Carbon Disclosure; RegTech and Financial Compliance; Data Analytics and Financial Decision-Making; Digital Transformation in Public Sector Accounting; Ethical Implications of AI and Automation in Financial Services; Evolving Accounting Standards in Response to Sustainability/Technology</t>
+          <t>All areas of finance, theoretical and empirical contributions</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Disclosure, Information Sharing, and Secrecy (DISS) Workshop</t>
+          <t>2026 UNSW Asset Pricing Workshop</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Sydney (NSW, Australia)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 AUD</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Economics of disclosure, information sharing, and secrecy; information disclosure (or non-disclosure) in economics, accounting, management science, and related disciplines</t>
+          <t>All areas of Finance, with a special focus on Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9th World Symposium on Investment Research (with Review of Finance)</t>
+          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Edinburgh, Scotland, United Kingdom</t>
+          <t>Venice, Italy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -646,145 +634,145 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Arbitrage in Asset Markets; Corporate Decisions and Asset Returns; Firm Governance and Valuation; Global Investment Issues; Hedge Funds and Other Alternative Investments; High-Frequency Trading; Investor Behavior and Performance; Liquidity and Security Returns; Mutual Funds and Pension Funds; Portfolio Rebalancing Strategies; Real Economy and Asset Prices; Return Predictability</t>
+          <t>Credit Risk and Advanced Analytics, Financial Innovation and Digital Transformation, Artificial Intelligence, Data Governance and Ethical Risk, Sustainability and Long-Term Value Creation, Systemic Risk, Resilience and Policy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11th Annual University of Connecticut Finance Conference</t>
+          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Storrs, CT</t>
+          <t>Toronto, Ontario (Canada)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60 USD</t>
+          <t>100 CAD</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>All areas of finance (unpublished empirical or theoretical papers)</t>
+          <t>Financial economics and accounting</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2nd Annual Conference on the Economics and Finance of Healthcare and Medicine</t>
+          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WashU Olin Business School, St. Louis, MO</t>
+          <t>Lugano, Switzerland</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Economics and finance of healthcare and medicine; intersection of healthcare/medicine and economics/finance; theoretical, empirical, and policy-oriented papers on these topics</t>
+          <t>real estate finance, urban economics, real estate economics, regional economics</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1st Global Banking and Finance Conference 2026 – XLRI Delhi NCR</t>
+          <t>Santiago Finance Workshop 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>XLRI Xavier School of Management Delhi-NCR, Jhajjar, India</t>
+          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No submission fee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Banking and Finance; Sustainable Finance</t>
+          <t>Any topic in finance or financial economics</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27th Annual Texas Finance Festival</t>
+          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Austin, Texas</t>
+          <t>EM Normandie Business School, Caen campus, France</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -794,34 +782,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>any topic in financial economics</t>
+          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026 Asian Finance Association Annual Conference</t>
+          <t>Climate Finance &amp; Sustainability Conference</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seoul, Korea</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -831,182 +819,182 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Strategy and management, Accounting and finance, Entrepreneurship and innovation, Marketing and responsible consumption, Supply chain and operations management</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026 Bretton Woods Accounting and Finance Ski Conference</t>
+          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bretton Woods, New Hampshire</t>
+          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>USD 79 per paper</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>All areas of accounting and finance</t>
+          <t>ESG in the AI Era: Challenges and Opportunities, AI-Driven ESG Reporting and Assurance, Algorithmic Bias, Ethics, and Fairness in ESG Analytics, Regulatory Responses to AI-Enabled ESG Practices, AI, Greenwashing, and Corporate Accountability, AI for Sustainable Finance and Investment Decision-Making</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Professor James R. Lothian Memorial Workshop</t>
+          <t>2026 FMA Asia/Pacific Conference</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gabelli School of Business, Fordham University, New York City</t>
+          <t>Massey University, Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD (FMA members), $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>All topics in finance and economics; emphasis on international finance, monetary economics, and the history of economic thought</t>
+          <t>Financial decision-making, financial management, related topics</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SGF 2026 Conference</t>
+          <t>Sixth Biennial Conference on Auto Lending</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zurich, Switzerland</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CHF 60</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>All topic areas of finance (including track areas: Asset Pricing; Corporate Finance &amp; Governance; Financial Intermediation and Institutions; Behavioral Finance &amp; Household Finance; Financial Markets General)</t>
+          <t>Consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, the role of alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, and spillovers from monetary policy and macroeconomic shocks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SWFA 2026 Conference (65th Annual Meeting of the Southwestern Finance Association)</t>
+          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hyatt Regency Dallas, 300 Reunion Blvd, Dallas, TX 75207</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Regular (Non-Doctoral Student): $75; Doctoral Student: $40 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>AI, Machine Learning, and Finance; ESG and Sustainable Finance; Asset Pricing; FinTech and Cryptocurrencies; Banking and Financial Institutions; International Finance; Corporate Finance; Risk Management and Derivatives; Financial Markets and Investments; Finance in the Classroom; Behavioral Finance; Financial Engineering</t>
+          <t>Methodological advances in analyzing complex and high-dimensional data sets, Methodological advances in natural language processing, particularly with respect to causal inference, Innovative applications of generative AI, The societal impacts of AI and algorithmic decision-making</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>University of Kentucky Finance Conference</t>
+          <t>Workshop on Innovations in Credit Scoring</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lexington, KY, USA</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1016,219 +1004,219 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Innovations in credit scoring, alternative data, fairness, transparency, data privacy, artificial intelligence, machine learning</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tenth Annual Young Scholars Finance Consortium</t>
+          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>College Station, Texas, USA</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Regular: $100 USD; PhD-only: $50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Asset pricing, investments; corporate finance and financial intermediation; theoretical and empirical finance research</t>
+          <t>monitoring and forecasting of economic and financial developments; using preliminary and revised data in economic policy formulation and analysis; machine learning applications in real-time macroeconomics; probabilistic forecasts and assessments of crisis risks; related innovative data sets and toolboxes; seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21st European Winter Finance Summit</t>
+          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saas-Fee, Switzerland</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CHF 60</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>All areas of finance (empirical and theoretical contributions)</t>
+          <t>quantitative methods and asset pricing</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Finance Down Under: Building on the Best from the Cellars of Finance</t>
+          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>US$100 per submission</t>
+          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Asset pricing; corporate finance; all areas of finance; gender finance (session)</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ASU Sonoran Winter Finance Conference 2026</t>
+          <t>2026 AIM Investment Conference</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Omni Montelucia, Scottsdale, Arizona</t>
+          <t>Austin, Texas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>All areas of finance (theoretical and empirical contributions)</t>
+          <t>mutual funds, hedge funds, pension funds, investment management</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>The Friends of Women in Finance 4th Symposium in Greater New York (FWFS-GNY)</t>
+          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hofstra University, Hempstead, New York, USA</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0 USD (free)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>fintech and AI, social and behavioral finance, corporate finance and governance, financial markets and investments, climate and sustainable finance, and related fields</t>
+          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alternative Investments Conference &amp; IPC Current Issues in Alternatives Research Symposium</t>
+          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chapel Hill, North Carolina, USA</t>
+          <t>Online Conference from Durham University, England, UK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1238,34 +1226,34 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>private capital and alternative investments including buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, hedge funds, real estate, infrastructure, and other real assets</t>
+          <t>Islamic finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IIM Calcutta Finance Research Conference 2025</t>
+          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IIM Calcutta (and online), Kolkata, India</t>
+          <t>Casa de Campo, La Romana, Dominican Republic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1275,34 +1263,34 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Finance and/or accounting (any topics related to finance and/or accounting)</t>
+          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>RBF Global Finance Forum 2026</t>
+          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al-Hasa, King Faisal University, Saudi Arabia</t>
+          <t>Australian National University (ANU), Canberra, Australia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1312,108 +1300,108 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sustainable Finance and Climate Risk; Corporate Finance and Investment Strategies; Banking Stability and Innovation (FinTech, Crypto, CBDCs); Financial Regulation and Risk Governance; Emerging Markets and Geopolitical Risk; ESG Reporting, Valuation and Strategy; Sovereign Risk, Public Finance, and Inflation Dynamics; Machine Learning &amp; AI in Financial Decision-Making</t>
+          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Second Winter Finance Summit in Asia</t>
+          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Appi Resort, Japan (ANA Crowne Plaza Resort APPI Kogen, Iwate Prefecture, northern Japan)</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>No submission fees</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>finance and real estate finance (all areas of finance and real estate finance)</t>
+          <t>Municipal bond markets, primary market frictions, secondary market frictions, role of retail investors, government policies affecting bond price formation, effect of state and federal policies on access to external finance</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>13th Annual Conference on Financial Market Regulation (CFMR 2026)</t>
+          <t>Inaugural Annual Conference on Insurance</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SEC Headquarters, Washington, DC</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Asset management; Corporate finance; Enforcement; Intermediaries; Market microstructure and trading</t>
+          <t>Life insurance, Property &amp; Casualty insurance, Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities, and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RCFS Winter Conference (Review of Corporate Finance Studies Winter Conference)</t>
+          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Royal Sonesta San Juan, Puerto Rico</t>
+          <t>Imperial Business School, London</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1423,108 +1411,108 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corporate finance; financial intermediation; household finance; Global and Emerging Markets in Finance (special session)</t>
+          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026 UBC Winter Finance Conference</t>
+          <t>2026 Conference on Auditing and Capital Markets</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Whistler, BC, Canada</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CAD $100 (approx. USD $75)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>topics of general interest to the finance profession</t>
+          <t>Economic impact of auditing, audit regulation, audit oversight, auditing issuers and brokers and dealers</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2nd LSU Finance Mardi Gras Conference</t>
+          <t>Future Scholars in Finance Forum</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA</t>
+          <t>Beijing, China</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>$50 per paper (USD)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>All topics in finance</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Institute for Quantitative Investment Research Joint UK-Europe Spring Residential Seminar 2026</t>
+          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>University Arms Hotel, Cambridge, U.K.</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1534,34 +1522,34 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Recent Developments in Investment Research; any topic relevant to investment management practitioners</t>
+          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026 Georgia Tech-Atlanta Fed Household Finance Conference</t>
+          <t>15th LaBS International Banking Workshop</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia</t>
+          <t>HSE University and online</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1571,108 +1559,108 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Household financial decision-making, inflation and consumer spending, impact of AI and ML model adoption on consumers, savings and investment behavior, retirement decisions and choices, housing and mortgage markets, credit access and debt management, impact of fintech innovation and adoption, behavioral economics and household finance, disparities in credit access, household wealth and inequality, entrepreneurship, small business lending</t>
+          <t>Banking in Emerging Markets: Challenges and Opportunities, theoretical and empirical research in banking or household finance, current issues concerning banking in emerging and developing markets</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>62nd Annual Eastern Finance Association Meeting</t>
+          <t>2026 Federal Reserve Stress Testing Research Conference</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Asheville, North Carolina, USA</t>
+          <t>Boston, Massachusetts</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>The economic and macroprudential effects of stress tests and bank regulation, Novel approaches to modeling bank profitability, financial risks, and operational risks, Design and applications of stress scenarios and reverse stress testing, Nonbank credit intermediation, Financial instruments for risk transfer, Recent developments in bank regulation, The impact of emerging technologies on banks and their regulators</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Baruch-JFQA Climate Finance and Sustainability Conference</t>
+          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Baruch College, City University of New York</t>
+          <t>Pullman Paris Montparnasse Hotel</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0 USD (no submission fee)</t>
+          <t>75€</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>climate finance, sustainability; intersection of politics and climate finance (political economy, policy uncertainty, regulatory change); climate risk, disclosure, and real estate</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>European Winter Finance Conference 2026</t>
+          <t>EBA's 15th Policy Research Workshop</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Megéve, France</t>
+          <t>EBA premises (Paris, France) and remotely</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1682,34 +1670,34 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience; Impacts of efficiency and proportionality; Competition, innovation, market entry, cross border growth and new areas under financial supervision; Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>12th International Conference on Sovereign Bond Markets</t>
+          <t>3rd Financial Fraud, Misconduct and Market Manipulation Conference</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1719,71 +1707,71 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>The interaction between sovereign bond markets and monetary policy, tariffs, regulation, fiscal policy, political risk, foreign exchange, and the macroeconomy under geopolitical uncertainty; including pricing of financial assets and exchange rates, policy divergence, market participants and institutions, bank risk-taking, cross-border spillovers across economies and asset classes, currency regimes, firm investment decisions, market liquidity, sovereign debt issuance and management, financial stability, bank–sovereign risk (“doom loop”), and related areas.</t>
+          <t>Theoretical and empirical analysis of financial fraud, Case studies of recent instances of market misconduct, Insider trading, Implication of financial fraud/market manipulation for market efficiency, stability, and asset pricing, Market manipulation at a high-frequency (intraday) level, Fraudulent activities and crypto currency markets, Social networks, fake news, and their effect on financial markets, Money laundering and banking, Conflicts of interests and their implications for various stakeholders and financial markets, Hedge funds/Mutual funds and their involvement in market misconduct, Statistical/ Machine Learning methods for fraud detection, Cyber security and cyber risk management, Regulatory response to financial misconduct, Unintended consequences of politics and regulations</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Energy Finance and Climate Transition Risk Conference</t>
+          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>University of North Carolina (Rizzo Conference Center)</t>
+          <t>California State University, Fullerton</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>$100 per submission</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Financing Energy Transition; Financing the Capital Requirements in Emerging Economies; Asset Prices and Climate Transition; Corporate Climate Strategies and Financial Implications; Financial Instruments and Climate Transition; Insurance and Climate Resilience</t>
+          <t>All areas of accounting and finance, including research that overlaps these disciplines, corporate reporting, governance, and financial markets.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>World Finance Conference - Ireland</t>
+          <t>25th Annual Bank Research Conference</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>University of Limerick, Limerick, Ireland</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1793,293 +1781,293 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Finance, Fintech, Economics, Banking</t>
+          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Central Bank Payments Conference</t>
+          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Istanbul, Türkiye</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$99.00 USD</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cross-border payments and their evolving architecture; Payment fraud and scams: detection, mitigation, and prevention; Geopolitical shifts and their influence on global or domestic payment systems; Public payment infrastructure like fast payment systems and central bank digital currencies; Stablecoins and their implications for existing payment infrastructure; Payments and financial inclusion: enabling access, equity, and resilience</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Trust in Financial/Capital Markets, Financial Markets functionality, Personal Finance, Pedagogy, Evidence-Based Financial Planning, Behavioral/Cognitive Value Investing</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>7th Analyst Research Conference</t>
+          <t>17th Emerging Markets Conference</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>University of Notre Dame, Notre Dame, IN, USA</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>USD 0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Current topics in analyst research</t>
+          <t>The sources of economic success or failure in EMs, Finance in EMs (households, financial markets, financial intermediaries, firms and finance, finance and growth), Political economy, law, public administration, regulation in EMs, The impact of populism upon the possibility of sustained growth, Insights into large EMs that matter in and of themselves, Insights from narrow research projects that illuminate EMs in general, The new phase of globalisation and its consequences for international trade, international finance and the nature of the EM firm, Features of a society that enable or disable convergence into the “normal” package of high levels of freedom and prosperity, The puzzles faced by all kinds of decision makers: individuals, civil society actors, firms, all levels of government, Grand challenges such as climate change: implications for EMs and ramifications of choices made in EMs, State capability in EMs, The interplay of military affairs, foreign policy and economics for EMs</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Annual VSB Mid-Atlantic Research Conference in Finance (MARC)</t>
+          <t>2026 International Forum on Financial Regulation and RegTech</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bartley Hall, Villanova University, Villanova, PA</t>
+          <t>Beihang University, Beijing, China</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60 USD</t>
+          <t>2000 CNY (Regular / Faculty), 1000 CNY (Student)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>All topics in finance</t>
+          <t>Financial regulation, Regulatory Technology (RegTech), FinTech, financial security, AI applications in finance, risk assessment and management, algorithmic bias, data privacy, systemic vulnerabilities</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Joint World Bank - Financial Analysts Journal Conference on “Public Asset Management: Best Practices and Innovations for the Future”</t>
+          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>World Bank Headquarters, Washington DC, USA</t>
+          <t>House of Management Science, Paris Pantheon-Assas University, 1 rue Guy-de-la-Brosse 75005 Paris, France</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USD 50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Public pension funds: risk management methodologies, challenges and best practices; Central Bank Reserve Management; Sovereign Wealth Fund Management; Stability, Guarantee, and Insurance Funds Management; Local Capital Markets and Home Bias; Blended Finance; Transition Finance for Public Investors; Applications to emerging markets contexts are particularly welcome</t>
+          <t>Energy transition, environmental sustainability, banking, climate finance, financial markets, macroeconomy, Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives, Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Seventh Edinburgh Corporate Finance Conference</t>
+          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Edinburgh, Scotland</t>
+          <t>The Shard, London, UK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£45</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corporate finance</t>
+          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges (DEXs), Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia Mortgage Market Research Conference</t>
+          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia, Ten Independence Mall, Philadelphia, PA 19106</t>
+          <t>Lund, Sweden</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0 USD (no submission fee)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mortgages and the mortgage market (including residential and commercial mortgages), policy-oriented panel discussions on current issues and market trends</t>
+          <t>Crypto and blockchain technology (asset pricing, systemic risk, market microstructure), Crypto markets, households, and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems (payment firms, consumer experiences, bank competition), Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026 ITAM Finance Conference</t>
+          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ITAM Santa Teresa campus, Mexico City, Mexico</t>
+          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MXN 1,250 (approximately USD 67)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>All areas of finance and financial economics (broadly defined)</t>
+          <t>New risks in a changing political environment, innovative research papers relevant to investment practitioners</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>The 2025 Cross Country Perspectives in Finance (CCPF) Special Multi-Thematic Conference</t>
+          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>online only</t>
+          <t>Shanghai and online</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2089,34 +2077,34 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sustainable Finance; Financial Innovation, Digital and Crypto Assets, and Fintech; Family Firms and SMEs; The Effectiveness of Financial Regulation</t>
+          <t>Sustainable finance, AI, blockchain, ESG integration, financial development, financial inclusion, regulatory challenges, corporate governance, greenwashing detection, ESG backlash, climate risk modelling, big data, natural language processing, carbon markets, digital finance, decentralized finance, green lending, climate insurance, impact investing</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2nd Workshop on LLMs and Generative AI in Finance at ICAIF '25</t>
+          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Park Hyatt Busan, Busan, Korea</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2126,71 +2114,71 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Multi-Agentic Systems; Composable and Compound System Design for Explainable Reasoning; Trust and Accountability in AI Systems; Methodologies for Processing Unstructured Data; Technical Challenges of LLMs and NLP; Prompt Engineering; Retrieval-Augmented Generation (RAG); Fine-Tuning LLMs; Text-to-SQL Applications; Evaluation Techniques; Applications in Analyzing Financial Reports and Alternative Data; Financial Modeling; Multi-Lingual ESG Identification and Assessment; Financial Fraud Detection; Enhancing Investor Communication</t>
+          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>5th Edition Spring Finance Workshop - Call for Papers</t>
+          <t>FIRN Melbourne Asset Pricing Meeting</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ischgl, Austria</t>
+          <t>Melbourne, Australia</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>All fields of finance</t>
+          <t>theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Columbia/BPI Annual Bank Regulation Research Conference</t>
+          <t>Johns Hopkins Carey Finance Conference</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Columbia University, New York City, NY, USA</t>
+          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2200,108 +2188,108 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>All aspects of bank regulation (e.g., capital and liquidity regulation, stress testing, merger policy), with emphasis on the implications of financial innovation for bank regulation and intermediation, including digitalization and real-time payments; topics on digital asset innovation (e.g., stablecoins), regulation and liquidity/credit/market risk implications, regulatory adequacy for innovations, and impact on bank deposit-taking and payments services.</t>
+          <t>All areas of finance, particularly early-stage papers that would benefit from feedback and discussion</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026 Loyola Wealth Management Conference</t>
+          <t>5th Holden Conference in Finance and Real Estate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Loyola University Maryland</t>
+          <t>Bloomington, IN</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>95 USD</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>mutual funds, ETFs, REITs, private equity, cryptocurrency, and related areas of wealth management</t>
+          <t>Empirical and theoretical papers in all finance and real estate areas</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ninth Duke-UNC Asset Pricing Conference</t>
+          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Duke University - Durham, North Carolina</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Asset pricing and macro-finance</t>
+          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>The 2025 TSFS International Conference in Finance</t>
+          <t>2026 New Zealand Finance Meeting</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kuriat Palace Hotel, Monastir, Tunisia</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2311,34 +2299,34 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Accounting, auditing, and taxation; Asset allocation and valuation; Banking regulation and financial services; Behavioral and experimental finance/economics; Big data in finance, artificial intelligence, and cybersecurity; Climate finance and sustainability; Corporate finance, IPOs, SEOs, M&amp;A, and crowdfunding; Corporate governance; Country funds, sovereign funds, and hedge funds; Debt issues; Digital finance, cryptocurrency finance, and blockchain; Emerging markets finance; Energy finance and environment issues; Entrepreneurial finance, venture capital, and private equity; Ethical finance, green finance, ESG, and CSR; Financial accounting and regulation; Financial crises, contagion, integration, and global risks interconnection; Financial engineering and derivatives; Foreign currency issue; Global imbalances &amp; sustainability; Household finance, real estate finance, and microfinance; Market behavior efficiency; Multinational financial management; Portfolio management and optimization; Risk management and compliance; Small business finance</t>
+          <t>All topics related to the field of finance</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>The 2026 NYSE Market Microstructure Conference</t>
+          <t>2026 Annual Community Bank Research Conference</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NYSE | 11 Wall Street, New York, NY 10005</t>
+          <t>Federal Reserve Bank of St. Louis in St. Louis, MO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2348,108 +2336,108 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Real-world applications of market microstructure in U.S. equity and related markets</t>
+          <t>Community banking's role in the U.S. financial system; provision of financial services to households, small businesses, and small farms; impact of community banks on local/state economic activity; community banks’ response to financial and economic shocks; effects of regulatory policy on community banks; challenges and opportunities faced by community banks; advantages and disadvantages of the community bank business model</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2nd Annual Boca Finance and Real-Estate Conference</t>
+          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Florida Atlantic University, Schmidt Family Complex, Boca Raton, Florida, USA</t>
+          <t>Gleacher Center - Chicago</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>All topics related to finance and real estate; interdisciplinary forum including accounting, economics, finance, and real estate disciplines</t>
+          <t>Crony capitalism in 21st century America, political economy, interplay between economic and political power</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19th Annual Corporate Governance Academic Conference at Drexel University</t>
+          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>University of South Carolina in Columbia, SC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>$100 per paper (USD); waived for papers written by current PhD students</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>board of directors; executive compensation; ownership structure; shareholder activism; institutional investors; mergers and acquisitions; private equity; sustainable finance; regulation; talent management; etc.</t>
+          <t>fixed income, commercial and investment banks, asset management and mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Financial Research Association 2025 Annual Conference</t>
+          <t>Higher Education Finance Research Conference</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Four Seasons Hotel, Las Vegas, Nevada</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2459,34 +2447,34 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>General finance topics (finance papers of general interest)</t>
+          <t>Financial aid, student debt, higher education finance</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>The 20th Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
+          <t>2026 Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CONRAD Seoul, Seoul, Korea</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2496,71 +2484,71 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>14th International Moscow Finance Conference</t>
+          <t>Financial Decision-Making Conference 2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HSE University, Moscow and Online</t>
+          <t>Bozeman, MT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Free (no submission fee)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>All fields of finance; both theoretical and empirical research</t>
+          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, financial inclusion</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>The 35th Conference on Financial Economics and Accounting (CFEA)</t>
+          <t>39th Australasian Finance and Banking Conference</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>East Lansing, Michigan, USA (Marriott East Lansing at University Place)</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2570,145 +2558,145 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Accounting, Economics, Financial Economics, and related disciplines; theoretical and empirical contributions; focus on the intersection of accounting and financial economics</t>
+          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Future Finance and Economics Association Dubai December 2025</t>
+          <t>Finance and Real Estate Conference 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dubai, United Arab Emirates</t>
+          <t>Miami University, Oxford, OH</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>International finance; Climate and Green finance; International financial integration and financial globalization; overlaps and interactions among these areas and their implications for sustainable growth of economies, firms, and organizations</t>
+          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>The 15th Workshop on Exchange Rates</t>
+          <t>UGA Fall Finance Conference</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Banka Slovenije, Slovenia, Ljubljana</t>
+          <t>Athens, GA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>70 USD</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>The drivers of exchange rates and related asset prices from a financial perspective (including the role of intermediaries); Exchange rates and the transmission of monetary policy; Exchange rate pass-through and the role of dominant currency pricing; FX interventions and the impact of tariff policies; Exchange rates and macrofinancial stability frameworks; FX risk premia and their drivers; Global linkages between capital flows, foreign exchange rates and risk appetite; The international use of currencies and its implications for exchange rates; Digital currencies and their implications for the global monetary and financial system</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
+          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hybrid: in person at School of Business, Stevens Institute of Technology, Hoboken, NJ, USA, and virtually</t>
+          <t>Prague, Czech Republic</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>In person: $400; Online: $50 (USD)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, and repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, and venture capital</t>
+          <t>Expectations and Asset Prices; deviations from rational expectations and their implications; optimism and pessimism in asset valuations and market dynamics; investment strategies and anomalies; factor investing; strategic and tactical asset allocation; portfolio choice under model and parameter uncertainty; short selling; institutional investing and asset management.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Santiago Finance Workshop (SFW)</t>
+          <t>WFE’s Sustainability Conference 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Santiago, Chile (School of Business and Economics, University of Chile)</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2718,71 +2706,71 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>any Finance or Financial Economics topic</t>
+          <t>Transition finance and market design, Regulatory fragmentation and divergence, Sustainability reporting, data and assurance, Nature and biodiversity in capital markets, Just transition, social and gender finance, Proportionality for SMEs and emerging markets, Carbon market architecture</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rutgers-ATP India Accounting &amp; Finance Symposium</t>
+          <t>2026 FMA Annual Meeting</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IIM Bangalore, India</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>0 USD (no submission fee)</t>
+          <t>$75 (current FMA members); $85 (non-members)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>accounting; corporate finance; asset pricing; corporate governance; law; contracting; sustainability; corporate social responsibility</t>
+          <t>Financial decision-making, financial management, all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>The 7th China International Forum on Finance and Policy</t>
+          <t>3rd AI in Finance Conference</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Beijing, China</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2792,71 +2780,71 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics; Portfolio management, trading strategies, and risk management using AI; Large language models (LLMs), NLP, and textual analysis in finance; Corporate finance applications including M&amp;A and investment decisions; Banking, credit markets, and financial intermediation; Cryptocurrency, digital assets, and decentralized finance; ESG, sustainability, and climate finance; Financial regulation, policy analysis, and central bank communication; Real estate finance and urban economics; Alternative data and high-dimensional financial datasets; Investor behavior, sentiment, and attention; Macroeconomic and financial risk forecasting</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>The 19th International Behavioural Finance Conference, Chicago</t>
+          <t>2026 Summer Research Conference, Centre for Analytical Finance, Indian School of Business</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chicago, US</t>
+          <t>Indian School of Business, Hyderabad Campus</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Behavioural finance topics in financial decision making, investments, financial markets, corporate finance, fund management, banking, asset pricing, forecasting, experimental finance and sociology of finance; Banking and Regulation; Behavioural Asset Pricing; Behavioural Corporate Finance; Biases and Heuristics; Pandemic; Cryptocurrencies; Equality, Diversity &amp; Inclusion; Financial Analysts; Financial Markets; Investment Decisions; Managerial Biases; Mergers and Acquisitions; Political Environment; Retail Investors; Sentimento; Climate Finance; CSR and ESG</t>
+          <t>Recent Advances in Finance, corporate finance, asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IIM Calcutta-NYU Stern India Research Conference on Zoom</t>
+          <t>International Risk Management Conference 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stern School of Business, New York University; Online via Zoom</t>
+          <t>Warsaw, Poland</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2866,108 +2854,108 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Areas of finance, economics, and accounting focusing on India and emerging economies; preference for papers addressing policy initiatives in India; researchers encouraged to submit papers using Indian data.</t>
+          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025 FMA Annual Meeting</t>
+          <t>The Second USTC Frontiers in Finance Conference</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R.China</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 CNY</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Corporate Finance; Asset Pricing / Investments; Fintech and AI; Behavioral; Household Finance; Climate Finance</t>
+          <t>All topics of finance</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Last Call Behavioral/Cognitive Finance, Decision/Risk Sciences in the Age of Artificial Intelligence; Entrepreneurship &amp; Economics-2025</t>
+          <t>Fischer-Shain Research Conference 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Silicon Valley/Santa Clara, CA, USA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>USD 99.00</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Development of new financial and economic models and theories for decision making and risk taking in the post-efficient-markets world; decision making under risk and uncertainty (social-science-based and AI-based models; theoretical and empirical works); venture startups and exits (cognitive manufacturing, additive and smart manufacturing, digital twin, Industrial IoT); trust, financial and capital markets, social capital, moral sentiments and working of the markets economy; investment in and working of financial markets at all levels of functionality and capital allocation (public and private); financial management of companies (public and private entities; role of virtual assistants); entrepreneurship, innovation, and economic development; sustainable finance (efficient financial markets; market for human/social capital &amp; economic development); role of behavioral finance &amp; economics in personal finance, retirement saving &amp; planning; teaching, learning, and training (pedagogical issues; using AI or AGI); applications in behavioral finance in practice (empirical works using AI-generated data; evidence-based retirement planning; trading/investing brain/neuromorphic strategies; nudging clients and markets; trust in investment management, markets, policy, and regulation; behavioral/cognitive value investing; other socio-economic/legal endeavors involving decision making and risk taking)</t>
+          <t>financial intermediation, banking, financial services</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>65th Annual Meeting of the Southwestern Finance Association (SWFA)</t>
+          <t>ECB Money Market Conference 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dallas, TX</t>
+          <t>European Central Bank, Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2977,71 +2965,71 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>AI, Machine Learning, and Finance; Asset Pricing; Banking and Financial Institutions; Corporate Finance; Financial Markets and Investments; Behavioral Finance; ESG and Sustainable Finance; FinTech and Cryptocurrencies; International Finance; Risk Management and Derivatives</t>
+          <t>Money markets and monetary policy implementation, technological innovation in money markets (stable coins, CBDCs, etc.), the functioning of money markets including non-bank financial institutions, funding strategies, central clearing, and implications of monetary policy.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9th Commodity Markets Winter Workshop</t>
+          <t>Finance in the Digital Age (FiDA) Workshop</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Brand (Vorarlberg), Austria</t>
+          <t>Calgary, Canada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>€300 (Full-time PhD students €250)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Micro &amp; macroeconomic analysis of commodity markets; Portfolio allocation/optimization including commodities; Pricing, hedging, and risk analysis of commodity derivatives and derivatives portfolios; Financialization of commodity markets; The microstructure of commodity markets; Corporate finance and risk management related to commodity markets; Econometric/statistical analysis of commodity markets; Decision models (OR/MS models) applied to the commodity sector; Real option analysis investigating commodity project investment and production decisions; Financial market analysis (risk factor models etc.) for commodity markets; Managerial accounting &amp; economics for commodity related corporations; Global and regional trade of commodities; The role of commodity production and consumption for developing countries; Commodity markets in this context include the entire range of commodities, i.e. energy (including electricity and renewables), metals, agricultural products and fish, and also related markets such as markets for shipping and transportation services, emission quotas and weather derivatives.</t>
+          <t>AI, DeFi, robo-advisors, neurofinance</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WFEClear, the WFE Clearing and Derivatives Conference 2026</t>
+          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Toronto, Canada</t>
+          <t>Bank of Italy, Rome, Italy</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3051,51 +3039,51 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Innovations in collateral management (especially to cater for 24/7 trading); innovations in options trading; derivatives in emerging markets; clearing structures and incentives (auction design, corporate governance, client clearing, non-default losses (NDLs), impact of clearing regulations); market resilience (clearing networks, liquidity contagion, cyber threats, collateral flows); vertical integration and market consolidation; supervisory structures and data reporting standards; new clearing and risk models; operational risk (third party risk management, transitioning to the cloud); impact of new technologies (clearing of crypto assets, crypto derivatives, DLT applications, smart contracts, the use of AI); liquidity risk transmission (network models, procyclicality); the impacts and suitability of the clearing mandate; barriers impeding cross-border activity; climate-related issues (green derivatives, clearing carbon emissions, water futures, carbon markets derivatives, etc.)</t>
+          <t>Long-term investors’ strategies and behavior, financing of the real economy, government bond markets, sustainable investment strategies, equity market concentration, non-bank investors in credit intermediation, cryptocurrencies and fintech, asset allocation and risk management, shock transmission mechanisms, big data and AI in investment processes, innovations in financial markets, geopolitical risks, demographic transitions.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>The CUHK-RAPS-RCFS Conference on Asset Pricing and Corporate Finance</t>
+          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hong Kong (Hyatt Regency Sha Tin)</t>
+          <t>Madrid, Spain, and virtually</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€350 in person; €50 online option</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Asset pricing and corporate finance (including papers spanning both areas)</t>
+          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, and repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, and venture capital</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AlgoDefi25 Workshop</t>
+          <t>Fintech and Financial Institutions Research Conference</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3105,17 +3093,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Politecnico di Milano, Milano, Italy</t>
+          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3125,145 +3113,145 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Algo-trading &amp; DeFi Algorithmic Trading, Decentralized Finance, Artificial Intelligence in Capital Markets; related topics include machine learning techniques, automatic trading strategies, automatic market making, distributed ledger technologies, digital assets, smart contracts, cryptocurrencies</t>
+          <t>Interlinkages of the fintech sector and the broader financial system, economic consequences and impacts of fintech, regulatory implications of the fintech sector</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5th Frontiers of Factor Investing Conference 2026</t>
+          <t>Aarhus Finance Forum 2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>Aarhus, Denmark</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GBP 30</t>
+          <t>375 DKK</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Asset Pricing; Financial Econometrics; Investments; High-Frequency Finance; Factor Allocation; Volatility Modelling; Risk Management; News Sentiment; Sustainable Investing; Machine Learning; Climate Finance; Alternative Data; Fintech, DeFi &amp; Crypto; Extreme Event Modelling</t>
+          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026 Midwest Finance Association Annual Meeting</t>
+          <t>15th CDI Conference on Derivatives</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Radisson Blu Aqua Hotel, Chicago, IL</t>
+          <t>Montreal, Canada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>USD 75</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>corporate finance, financial institutions, asset pricing, asset management</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>The Tenth Annual Volatility Institute Conference at NYU Shanghai</t>
+          <t>Conference on CSR, the Economy and Financial Markets</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>NYU Shanghai, Shanghai, China</t>
+          <t>Düsseldorf, Germany</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€150 for regular participants, €100 for PhD students</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>asset pricing; corporate finance; capital markets; market microstructure; behavioral finance; macro-financial linkages; international finance; papers focusing on the financial implications of geopolitical risks</t>
+          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4th Bonn/Frankfurt/Mannheim Workshop on Digital Finance</t>
+          <t>2026 Vietnam Symposium on Global Economy (VSGE2026)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Frankfurt am Main, Germany</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3273,108 +3261,108 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>AI, digital currencies, decentralized finance (DeFi), FinTech</t>
+          <t>Geopolitical, macroeconomic policy, and development; Trade, foreign direct investment, and global value chain; Climate change, green transition, and public finance; Finance, stability, and sustainable investment; Digitalization, labor markets, and social protection; Urbanization, regional development and resilience; AI, growth, economic impacts, and government policies; Global governance, institutions, and international cooperation.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IV CEMLA / Dallas Fed Financial Stability Workshop</t>
+          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>San Antonio, Texas, USA</t>
+          <t>CONRAD Seoul</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0 USD (no registration or submission fees)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Monetary policy and financial stability: interactions and trade-offs; Global financial spillovers and the role of the US dollar; Macroprudential policy: design, transmission, and applications to housing and beyond; Non-bank financial intermediation, market liquidity, and funding fragilities; Emerging macro-financial risks and the digital transformation of finance</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>14th LaBS International Banking Workshop</t>
+          <t>India Finance Conference (IFC) 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HSE University (Moscow) and online</t>
+          <t>Indian Institute of Management Bangalore</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0 USD (free)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Banking; Household finance; Emerging and developing markets (issues in banking in emerging markets)</t>
+          <t>Theoretical and empirical asset pricing, Corporate finance, capital structure and dividend policy, Asset allocation and investment management, Financial crises, systemic risk and macro-finance, Quality of financial reporting and adoption of IFRS, Corporate governance, executive compensation and ownership structure, Computational finance and financial econometrics, Financial Econometrics, Financial risk analytics and management, Market microstructure and algorithmic trading, Financial policy choice, institutions and regulation, Financial Analytics, ESG, Climate Finance, Blended Finance, Insurance / Reinsurance / Pension Funds, Enhancing liquidity in commodity derivatives markets, Financial Literacy and Financial Education</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>International Conference in Banking and Financial Studies (ICBFS 2025)</t>
+          <t>Edinburgh Financial Technology Conference</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Milan (Piacenza), Italy</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3384,34 +3372,34 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Accounting, auditing, and taxation; Asset allocation and valuation; Banking regulation and financial services; Behavioral and experimental finance/economics; Big data in finance, artificial intelligence, and cybersecurity; Climate finance and sustainability; Corporate finance, IPOs, SEOs, M&amp;A, and crowdfunding; Corporate governance; Country funds, sovereign funds, and hedge funds; Debt issues; Digital finance, cryptocurrency finance, and blockchain; Emerging markets finance; Energy finance and environment issues; Entrepreneurial finance, venture capital, and private equity; Ethical finance, green finance, ESG, and CSR; Financial accounting and regulation; Financial crises, contagion, integration, and global risks interconnection; Financial engineering and derivatives; Foreign currency issue; Global imbalances &amp; sustainability; Household finance, real estate finance, and microfinance; Market behavior efficiency; Multinational financial management; Portfolio management and optimization; Risk management and compliance; Small business finance</t>
+          <t>The application of AI and Machine Learning in finance; The application of distributed ledger technologies in finance; Cryptofinance; Cyber risk in finance; The microstructure of modern financial markets: algorithmic/high frequency trading, dark trading, blockchain settlements; Behavioural economics in financial technology; Alternative data (structured and unstructured datasets); Crowdsourcing and investment strategy; New exchange traded financial derivatives; Financial stability risks from the development of FinTech; RegTech; Open banking</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025 (5th) “Innovation, Sustainability and Regeneration” International Conference</t>
+          <t>5th Conference in Sustainable Finance</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Universidade Católica Portuguesa, Porto campus, Porto, Portugal</t>
+          <t>University of Luxembourg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3421,71 +3409,71 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Innovation and business transformation; Circular economy; Bioeconomy; Leadership and governance for sustainability; Sustainable business strategy; Social entrepreneurship and responsible business; Sustainability literacy and education; Sustainable investment and financing; Challenges due to the impact of climate change; Climate risk management; Laws and regulations related to sustainability; Arts and sustainability; AI and analytics for sustainability</t>
+          <t>any topic in sustainable finance</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2nd Modern Finance Conference (MFC 2025)</t>
+          <t>7th CEAR-RSI Household Finance Workshop</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Warsaw, Poland</t>
+          <t>HEC Montréal</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation; Banking and financial services; Behavioral finance and decision making; Capital structure; Corporate finance; Corporate governance; Cryptocurrencies; Derivatives; Economic development; Exchange rates and currency markets; Finance and accounting standards; Financial econometrics and quantitative methods; Financial markets and instruments; Financial, management, and tax accounting; Financial regulation and supervisions; Financial stability; Fintech and financial innovation; Green finance; Investment and portfolio management; Insurance; Market microstructure; Mergers and acquisitions; Microfinance; Monetary policy and central banking; Risk management; Sustainable finance and responsible investment</t>
+          <t>Consumption-saving decisions and investment choices, Financial literacy and education, Pensions and retirement, Financial planning and advice, Financial delinquency and bankruptcy, Household insurance and risk management</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sustainable Finance Research Forum Paris 2025</t>
+          <t>Next-Gen AI and Autonomous Finance (NGAI) workshop</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>Rennes School of Business, Rennes, France</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3495,34 +3483,34 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Impact banking and financial products; Impact finance; Corporate responsibility; Climate finance; Corporate governance; Greenwashing; Corporate culture and values; Ratings; Social matters and education in firms; Responsible investments; Green banking; Long term performance and risks; Green and Social Bonds; Financial education and literacy</t>
+          <t>Autonomous agents &amp; decision-making in finance, AI-driven trading, portfolio optimization &amp; market microstructure, Risk, robustness, and model governance (validation, monitoring, compliance), Ethics, fairness, transparency &amp; societal impacts of financial AI, Financial decision making and AI, Bias and stereotyping in relation to AI driven finance, AI, money and financial value formation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025 Colorado Finance Summit</t>
+          <t>12th Annual ICGS Conference</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vail, Colorado</t>
+          <t>HEC Montréal, Quebec, Canada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3532,71 +3520,71 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Behavioral perspectives on governance, institutional and political approaches, implications of AI on governance mechanisms, evolving forms of activism, reconfiguration of governance systems, governance of state-firm relations</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>UTD 2025 Annual Finance Conference</t>
+          <t>Vienna Festival of Finance Theory 2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas, Dallas, TX</t>
+          <t>Vienna, Austria</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>USD 75</t>
+          <t>65 EUR</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Corporate finance theory and financial intermediation theory</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STARTUP CITIES: STRATEGIES, STAKEHOLDERS AND IMPACT</t>
+          <t>11th Cross Country Perspectives in Finance (CCPF) Conference</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Milan, Italy</t>
+          <t>both online and on-site (Nanjing, China)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3606,145 +3594,145 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Micro-geography of entrepreneurship; Relationship between urban contexts and entrepreneurship; Entrepreneurial finance and local impacts; Social inequality and entrepreneurship; Local public policies and entrepreneurship; Sustainability of startup ecosystems</t>
+          <t>credit, banking, asset pricing, market liquidity, corporate finance, corporate governance, entrepreneurial finance in an international context</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025 FMA Conference on Derivatives &amp; Volatility</t>
+          <t>Private Capital Symposium 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CBOE Global Markets, 433 W. Van Buren Street, Chicago, IL 60607, USA</t>
+          <t>London Business School, London</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>50 USD for members; 60 USD for non-members</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Derivatives and volatility; product innovations and industry trends</t>
+          <t>Research on private equity, venture capital, and broader private market themes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2025</t>
+          <t>6th Annual Bristol Financial Markets Conference</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Yunnan University of Finance and Economics, Kunming, China</t>
+          <t>Bristol, UK</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Environmental, Social, and Governance (ESG) topics; Climate finance and biodiversity finance; Artificial Intelligence (AI) and Machine Learning (ML); Big and unstructured data (e.g., voice and facial recognition) in accounting and finance; FinTech (Blockchain and Bitcoin); Other contemporary accounting and finance issues</t>
+          <t>Skill, performance, and evaluation in delegated portfolio management; The rise of passive investment and its effects on financial markets; New developments and trends in delegation: ESG / thematic/private markets; Machine learning and AI in asset management; Textual analysis and news coverage in delegated investment decisions; The role of index providers in delegated portfolio management</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>The 2025 Sydney Banking and Financial Stability Conference</t>
+          <t>Inaugural CEIBS-APS Centre for Financial Markets (CAC) Academic Conference</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Belinda Hutchinson Building H70, The University of Sydney Business School, Sydney, Australia</t>
+          <t>China Europe International Business School (CEIBS), Shanghai, China</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>No submission fee (0 USD)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Financial Intermediation; Financial Institutions and Markets; Fintech; Cryptocurrency and Central Bank Digital Currency; Financial system stability; Corporate Finance; Asset Pricing; Investment and Funds Management; Macro Finance</t>
+          <t>asset pricing, macro-finance, impact of institutional features on capital market dynamics</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>AI Empowering Business, Economics, Finance &amp; Healthcare 2024-2025 Academic Summit of the Digital Economy Open Research Platform</t>
+          <t>Dauphine Finance PhD Workshop</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Shenzhen, China</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3754,34 +3742,34 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ethics, governance, and regulation in AI applications; AI applications in financial markets; AI applications in management decisions; AI and sustainability; AI, emerging technologies, and digital economy; AI and healthcare; Cyber security and operational risks as sources of systemic risk; Economic policies in AI era</t>
+          <t>Papers in all areas of Finance and Financial Economics</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>The 2025 Massey Sustainable Finance Conference at Nanjing, China</t>
+          <t>14th Helsinki Finance Summit on Investor Behavior</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nanjing, China</t>
+          <t>Helsinki/Espoo, Finland</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3791,293 +3779,293 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Artificial intelligence and machine learning applications in Sustainable Finance; Alternative data on firms' digital transformation; Behavioral Finance/Economics and its implications to climate transition; Blue economy; Carbon market and carbon credit; Carbon price forecasting techniques; Circular economy; Corporate Social Responsibility; Climate Finance; Climate risks: assessment and management; Climate transition and portfolio management; Cryptocurrency and digital finance interactions with Sustainable Finance; Diversity, equity and inclusion in Finance; Digital finance, Fintech, and sustainability; Environmental, Social and Governance; Financial markets and climate transition; Green Finance; Green Finance and energy security; (Renewable) Energy Finance; Renewable Energy and Sustainability; Sustainable Finance and Accounting</t>
+          <t>Investor behavior, market microstructure, behavioral biases, household consumption, investor education, finance professionals' behavior, psychological foundations of investor behavior, influence of analysts and media, social influence in finance, impact on corporate policies</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4th Contemporary Issues in Financial Markets and Banking Online Conference</t>
+          <t>2026 Clemson Finance Research Conference</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Clemson, SC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>USD 175</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Corporate finance, corporate governance, international financial management, and investment; Financial resilience; liquidity management; crisis investment and crisis portfolio management; banking and financial sector stability and regulation; financial (dis)integration and Brexit; Green and sustainable finance; sustainable energy financing; alternative investments; financial inclusion; Islamic banking; Crowdfunding; decentralised finance; disruptive financial technologies; metaverse and blockchain technologies in finance; artificial intelligence; machine and deep learning applications in finance; Theoretical asset pricing; empirical asset pricing; risk management; behavioural finance; financial applications of game theory and decision theory; computational financial economics (including multi-agent models and econophysics); experimental economics with implications for financial theory and practice; Market microstructure; household finance; real estate and property markets.</t>
+          <t>corporate finance, asset pricing, investment, banking, asset management, household finance, labor economics, behavioral finance, Fintech, real estate</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MIT GCFP 12th Annual Conference</t>
+          <t>Politics in Finance 2026 Conference</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US</t>
+          <t>McDonough School of Business, Rafik B. Hariri Building 37th and O Streets, N.W Washington, D.C. 20057 USA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Evaluations of contingent financial, environmental and other liabilities; sovereign wealth funds; state-owned enterprises; public sector pension systems; mark-to-market and fair value accounting applications to government assets and liabilities; valuation and fiscal implications of opaque public assets (e.g., biodiversity and other environmental resources, research and other infrastructure); fiscal effects of monetary policy; government accounting and budgetary rule reform; the economics of privatization; international applications and comparisons; plus the conference tracks: Evaluation and Management of Government Financial Institutions; Regulation of Financial Markets and Institutions; Risk Measurement and Management in the Public Sector.</t>
+          <t>The role of political connections and political ideologies in shaping capital market forces, how political ideologies affect decision making by firms and workers, political connections and corruption in developing economies, the political economy of financial development, the interaction between government and financial institutions, implications of political uncertainty and political connections for asset prices and corporate policies, political economy of financial regulation and financial crises</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025 UNSW Asset Pricing Workshop</t>
+          <t>11th SDU Finance Workshop on Corporate Finance</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Coogee Beach, Sydney, Australia (Coogee Surf Life Saving Club)</t>
+          <t>University of Southern Denmark (SDU), Odense, Denmark</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>0 AUD</t>
+          <t>300 DKK</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>all areas of Finance with special focus on Asset Pricing; theoretical and empirical papers</t>
+          <t>Corporate Finance -- Dynamics, Uncertainty, and Strategic Decisions</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SFS Cavalcade Asia-Pacific 2025</t>
+          <t>Northern Finance Association 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tsinghua PBC School of Finance, Beijing, China</t>
+          <t>Quebec City, Canada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Canadian $75</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Asset pricing, corporate finance, financial intermediation, investments, Canadian financial markets, insurance, household finance, sustainable finance, fintech, and AI</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AI in Real Estate | Day 3 of the 2nd AI in Finance Conference</t>
+          <t>London Business School 2026 Summer Finance Symposium</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Montréal, Canada</t>
+          <t>London Business School</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CAD 400</t>
+          <t>£50 GBP</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>AI-driven property valuation and appraisal models; Machine learning for real estate market forecasting and trend analysis; AI applications in real estate development and land use planning; AI in real estate investment and portfolio management; AI for sustainable real estate and climate risk assessment; Urban analytics and smart-city applications in real estate; Natural language processing and large language models for real estate market analysis; Computer vision and geospatial analysis for property and neighborhood insights; AI-driven demand for real estate: Data centers and infrastructure; Ethics, fairness, and regulatory challenges in AI-driven real estate</t>
+          <t>Papers from all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>UTD 2025 Annual Finance Conference</t>
+          <t>Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF26)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>University of Texas at Dallas, Dallas, TX</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>75 USD per paper</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Climate Finance, Artificial Intelligence (AI) and Machine Learning in Finance and Accounting, Green Finance, Sustainable Finance, ESG Reporting, and Climate Risk, FinTech, Blockchain, and Digital Currencies, Corporate Governance and Technological Innovation, Big Data in Accounting and Finance, Green Accounting and Carbon Disclosure, RegTech and Financial Compliance, Data Analytics and Financial Decision-Making, Digital Transformation in Public Sector Accounting, Ethical Implications of AI and Automation in Financial Services, Evolving Accounting Standards in Response to Sustainability/Technology</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Academy of Behavioral Finance &amp; Economics Annual Conference (ABF&amp;E Annual Meeting)</t>
+          <t>11th International Conference on Accounting and Finance (ICOAF-2026)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, USA</t>
+          <t>Danang, Vietnam</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>$99.00 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics; Neuroscience/Neuromorphic Computing; Quantum Entanglement Political Economy; Biological Anthropology; Brain-Computer Interfaces; development of new financial and economic models and theories for decision making and risk taking in AI; decision making under risk and uncertainty; venture startups and exits; trust in financial markets and capital markets; investment in and functioning of financial markets; financial management of public and private companies; entrepreneurship, innovation, and economic development; sustainable finance; role of behavioral finance in personal finance, retirement saving and planning; teaching, learning, and training with AI/AGI; empirical/AI-generated data applications; behavioral/cognitive value investing; nudging clients and markets; trading/neuromorphic strategies.</t>
+          <t>All areas of Accounting, Finance, and Banking, encompassing both theoretical and empirical studies</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Inaugural RAPS/RCFS Europe Conference</t>
+          <t>Liechtenstein Workshop on AI in Finance 2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cambridge University, England</t>
+          <t>Vaduz, Liechtenstein</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4087,108 +4075,108 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Asset Pricing; Corporate Finance</t>
+          <t>forecasting financial variables with AI, asset allocation and asset management with AI, AI-based factor models, natural language processing and large language models in finance, AI applications in corporate finance</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025 FMA Asia/Pacific Conference</t>
+          <t>3rd Modern Finance Conference (MFC 2026)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>National Taiwan University, Taipei, Taiwan</t>
+          <t>Krakow, Poland</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>USD 50 (members); USD 60 (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Papers in all areas of finance; financial decision-making; financial management; related topics</t>
+          <t>Asset pricing and valuation, Banking and financial services, Behavioral finance and decision making, Capital structure, Corporate finance, Corporate governance, Cryptocurrencies, Derivatives, Economic development, Exchange rates and currency markets, Finance and accounting standards, Financial econometrics and quantitative methods, Financial markets and instruments, Financial, management, and tax accounting, Financial regulation and supervision, Financial stability, Fintech and financial innovation, Green finance, Investment and portfolio management, Insurance, Market microstructure, Mergers and acquisitions, Microfinance, Monetary policy and central banking, Risk management, Sustainable finance and responsible investment</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025 Vietnam Symposium in Climate Transition (VSCT-2025)</t>
+          <t>The First University of Maryland/Singapore Management University/UBS Quant Investment Forum: AI and Finance</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>The University of Danang - University of Economics, 71 Ngu Hanh Son street, Ngu Hanh Son district, Danang, Vietnam</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Free (no submission fee)</t>
+          <t>95 SGD</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Behavioral finance/economics and its implications to climate transition; Blue economy; Carbon market; Circular economy; Climate change: mitigation and adaptation; Climate change: policy and regulations; Climate finance; Climate risks: assessment and management; Climate transition and COVID-19 recovery; Climate transition and portfolio management; Corporate Social Responsibility (CSR); Energy and environmental issues; Energy markets and energy transition; Environmental, Social and Governance (ESG); Financial markets and climate transition; Geopolitical risk and climate change mitigation; Just climate transition; Low carbon technologies and innovation; Management of extractive industries; Responsible behaviors and sustainability in family business; Responsible business conduct and SDG goals; Role of management, business strategies, and SDG goals; Sustainable business model innovation; Sustainable entrepreneurship; Sustainable infrastructure investment; Sustainable production and consumption; Sustainable key performance indicators</t>
+          <t>AI for Investments &amp; Asset Pricing, Alternative Data and Investment Insights, Portfolio &amp; Risk Management, Algorithmic Trading &amp; Market Impact</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2025 FMA Annual Meeting - Innovation in Teaching Award</t>
+          <t>2026 City University of Hong Kong International Finance Conference</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4198,108 +4186,108 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Corporate Finance, Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2025 Inaugural China Future Scholars in Finance Forum</t>
+          <t>2026 Research Summer Workshop on Regulated Funds and Retail-oriented Investment Products at the Investment Company Institute</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Beijing, China</t>
+          <t>Washington, DC, USA</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>All areas of finance; preference for research related to China</t>
+          <t>Regulated funds, retail-oriented investment products, mutual fund industry</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sustainability at Crossroads: The Edinburgh and International Review of Finance Conference</t>
+          <t>2026 Vietnam Symposium in Entrepreneurship, Finance, and Innovation</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>University of Edinburgh, Edinburgh, Scotland, UK</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Free (no submission fee)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>The evolving regulatory landscape of ESG; Climate risk assessment and measurement; ESG integration in investment decision-making; The role of technology and AI in ESG analysis; Greenwashing and transparency challenges; ESG and corporate financial performance; The impact of ESG on emerging markets; Sustainable finance innovations and best practices</t>
+          <t>AI, Big Data, and Machine Learning Applications in Finance; Asset Pricing; Bankruptcy and Liquidation; Biodiversity Finance; Climate Finance; Corporate Finance and Governance; Corporate Responsibility and Sustainability; Crypto Assets, Blockchain, and Decentralized Finance; Electronic Markets, Trading Platforms, and Market Microstructure; ESG and Sustainable Finance; Financial Markets; Household Finance; Information Disclosure, Market Efficiency, and Transparency; Portfolio and Investment Decisions; FinTech, Alternative Finance, and Digital Financial Infrastructure; Tokenomics, Digital Currencies, and Payment Systems; Business Model Innovation and Corporate Digital Transformation; Digital Innovation, Knowledge Management, and Innovation Systems; Digital Human Resources and the Future of Work; Innovation Management and Growth Strategies; Innovation and Industrial Policy; Institutions, Regulation, and Innovation Systems; Science, R&amp;D, and the Economics of Knowledge Creation; Sustainability in the Digital Economy; Crowdfunding, Peer-to-Peer Lending, and Platform-Based Finance; Entrepreneurship, Intrapreneurship, and Innovation; Entrepreneurship in Emerging and Transition Markets; Family-Owned Businesses and Governance; Governance and Financing of High-Tech Firms; New Venture Creation and Performance; Social and Sustainable Entrepreneurship; Startups, SMEs, and Resource Allocation; Venture Financing and Entrepreneurial Growth</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>17th Annual Private Equity Research Consortium (PERC) Symposium</t>
+          <t>12th IWH-FIN-FIRE Workshop on “Challenges to Financial Stability”</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chapel Hill, North Carolina, USA</t>
+          <t>Halle Institute for Economic Research (IWH), Halle/Saale Germany</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4309,145 +4297,145 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Private equity, including buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, and real assets</t>
+          <t>regulation and financial intermediation, corporate finance, law, politics and finance, monetary policy, inflation and financial resilience, macroprudential policy and real estate, financial networks and systemic risk, pricing of climate risk in financial markets, ecological hazards and the behaviour of firms and households, governance of financial firms and markets, private credit and risk transfer</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IMRC 2025</t>
+          <t>Bridging Theory and Empirical Research in Finance</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Indian Institute of Management Ahmedabad</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Track 03: The Gold and Precious Metals: Business and Economic Policies — topics include sourcing of precious metals, mining, export–import trading, sales and market, exchanges, recycling, hallmarking, ethics and responsible business, logistics and supply chain, labor practices, formal/informal business models, investment products (gold, precious metals, gems), central banks, bullion banking, malpractices, regulations, governing policies, sustainability and green methods, and applications of technology such as blockchain and AI/ML in the gold supply chain; comparative global policy studies, heritage and cultural dimensions; empirical and modeling research on real-world sector challenges. Track 04/05: The Finance, Accounting, and Economics (FAE) Track — topics include asset pricing (theoretical and empirical), IFRS/financial reporting quality, market microstructure and algorithmic trading, insurance/reinsurance/pension funds, business cycles, corporate finance and capital structure, dividend policy, financial policy and regulation, liquidity in commodity derivatives markets, public economics, asset allocation and investment management, computational finance and econometrics, monetary policy and banking, financial risk analytics and management, financial analytics, FDI and portfolio capital flows, household finance, international trade and exchange rates, financial crises and systemic risk, and global value chains and firm performance.</t>
+          <t>corporate finance, corporate governance, financial intermediation, agency and delegation, information and securities, financial markets</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2nd AI in Finance Conference | FRL Special Issue Workshop on “AI in Corporate Finance”</t>
+          <t>11th Bank of Finland and European Systemic Risk Board Joint Conference on AI and Systemic Risk Analytics</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Montréal, Canada</t>
+          <t>Bank of Finland, Helsinki</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CAD 750 (50% discount for PhD students and online presenters)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>AI and machine learning in corporate finance; AI and machine learning in entrepreneurial innovation; AI and machine learning in entrepreneurial fundraising; AI and sustainability; AI applications in financial markets; AI, emerging technologies, and digital finance; Natural language processing, robo-advisory, fraud detection; Ethics, governance, and regulation in AI applications</t>
+          <t>Use of Large Language Models (LLM) and trustworthy AI, AI and changing interdependencies in the financial markets, Cyber security and operational risks as sources of systemic risk, AI and Quantum Computing as potential source of new systemic risks, Use of AI with big data for systemic risk analytics, Risks and opportunities stemming from disruptive innovations in financial technology (FinTech), Analysing emerging risks from interconnectedness of the financial system, Identifying risks from market-based finance, Modelling geopolitical risks, Using systemic risk analytics to support macro-prudential policy and regulation, Evidence of macroprudential policy measures</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PhD and Postdoc Workshop on Empirical AI in Finance at the 2nd AI in Finance Conference</t>
+          <t>Bank of Finland and CEPR Joint conference on Navigating Monetary Policy by the Northern Lights</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Montréal, Canada</t>
+          <t>Saariselkä, Lapland</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Empirical finance; machine learning / AI in finance; data-driven research; Matlab programming; WRDS data (CRSP, Compustat, IBES); replication of top-tier finance papers using ML; forecasting stock returns with ML; empirical asset pricing; replication of foundational asset pricing tests</t>
+          <t>Monetary Policy Transmission, Inflation Dynamics and Expectations; Heterogeneity in Macro and Monetary Economics Models; Monetary-Fiscal Interactions; Technological Advances, Financial Market Developments, and Central Banks; Geopolitical Shocks and Monetary Policy; Central bank credibility and independence</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2025 Wharton Conference on Liquidity and Financial Fragility</t>
+          <t>2026 FIRN/UQ Asset Management Meeting</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Brisbane, Australia</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4457,34 +4445,34 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Dysfunctions, frictions, and fragility in U.S. Treasury markets; Currency dominance, sovereign debt crises, and their link to the financial sector; Geopolitical tensions, trade conflicts, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies; FinTech, artificial intelligence (AI), and their implications for financial stability; New payment technologies, digital currencies, and their implications for the monetary system</t>
+          <t>asset management, FinTech, mutual funds, hedge funds, pension funds, ETFs, alternative investments, data assets/markets, digital finance, platform finance, financial technology, artificial intelligence, big data in asset management</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>The 2nd Global Conference on Sustainability in Economics, Business and Law</t>
+          <t>World Finance &amp; Banking Symposium</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>University of Latvia, Riga</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4494,71 +4482,71 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>sustainability in economics, business and law; twin transition (green transition and digital transformation); economic models, business strategies, and legal frameworks; theoretical, conceptual, empirical research in economics, business, management and law</t>
+          <t>All areas of finance, economics, and banking</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Warwick Business School Gillmore Centre Conference on DeFi &amp; Digital Currencies 2025</t>
+          <t>Research Symposium on Finance and Economics (RSFE) 2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Warwick Business School, The Shard, London, UK</t>
+          <t>Krea University, Andhra Pradesh, India</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>£45 (GBP)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DeFi protocol design/governance/market efficiency; Economics of the blockchain (mechanism design, security, welfare); Financial stability, macroeconomic, and political economy implications of stablecoins and CBDC designs;; All areas of DeFi and Digital Currencies</t>
+          <t>Finance and Economics</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Developments in Sustainable Finance: A New Era of Financial Innovation</t>
+          <t>Annual Meeting of the Central Bank Research Association CEBRA</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>American University of Sharjah, Sharjah, United Arab Emirates</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4568,67 +4556,71 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>sustainable finance developments; ESG integration; green and sustainability-linked bonds; ESG-focused investment portfolios; climate risk assessment; AI and emerging technologies in sustainable finance; regulatory frameworks (e.g., SFDR); policy and geopolitical influences on sustainability finance; innovative financial instruments for sustainability</t>
+          <t>Monetary Policy Transmission, Expectations, and Communication; Inflation and Price Dynamics; Macro-Finance and Financial Stability; Fiscal–Monetary Interactions and Policy Making; International Macroeconomics, Trade, and Geoeconomics; Firms, Productivity, and the Real Economy; Data, Methods, and Artificial Intelligence</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>C.r.e.d.i.t. 2025 (24th International Conference)</t>
+          <t>IBEFA Annual Meeting at the 2027 ASSA Conference</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>tical Risks and Global Financial Stability: Implications of geopolitical tensions on global financial markets; Risk management strategies for financial institutions navigating geopolitical uncertainty; The role of national and international economic policies shaping a new geopolitical and economic order</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Global Challenges: Macroeconomic Polarization and Financial Fragmentation; Economic bifurcation between advanced and emerging markets; Trade conflicts and their financial spillovers; Policy responses to maintain global economic stability</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Innovation in Finance and Insurance: Digital transformation in the insurance sector; Financing Deep Tech; Regulating innovation to balance opportunity and risk</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
+          <t>US$100 per paper; US$75 for papers solely authored by PhD students</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>banking; financial risk measurement and management; non-bank financial intermediation and private credit; FinTech; the role of AI in financial intermediation; geo-economic fragmentation and capital flows; sustainable finance; household finance; financial market structure and regulation; monetary policy</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2025 FMA Annual Meeting - Doctoral Student Consortium, Emerging Scholars Initiative and Innovation in Teaching Award</t>
+          <t>CSEF- CEPR Conference on Labor and Finance</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>Villa Orlandi Conference Centre, University of Naples Federico II, Capri (Italy)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4638,34 +4630,34 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Interaction between financial and labor markets, technological innovation, job-skill matches, firms’ employment policies, role of employees in governance and financing of companies, responses of wages and employment to shocks, risk-sharing arrangements between firms and workers</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2025 Global AI Finance Research Conference</t>
+          <t>Happy Valley Finance Conference</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4675,71 +4667,71 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI), Big data and Machine Learning; Blockchain and Cryptocurrencies; Initial Coin Offerings (ICOs) and Security Token Offerings (STOs); Decentralized Finance (DeFi); Peer-to-peer lending; FinTech regulation; High-frequency trading and market liquidity; Green FinTech</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Finance Research Letters Paper Development Workshop “Artificial Intelligence in Corporate Finance” and PhD / Postdoc Workshop</t>
+          <t>3rd CEPR-SAFE Frankfurt Hub Conference of RPNs</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Dresden, Germany</t>
+          <t>House of Finance, Campus Westend, Frankfurt, Germany</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Early-bird EUR 290 + VAT; Regular EUR 340 + VAT; 50% discount for scholars from low-income countries and PhD students presenting their single-author paper</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>AI and machine learning in firm valuation; AI and machine learning in mergers and acquisitions (M&amp;A); AI and machine learning in capital structure; AI and dividend policy; AI and agency theory; AI and ESG; AI and corporate governance and risk management; AI fraud detection; Natural language processing and corporate finance; AI applications and regulation</t>
+          <t>Fintech and Financial Institutions, Regulatory framework revisions, CBDC blockchains, and stablecoins, Sovereign bonds and sovereign bond capital regulation, Payment systems and European sovereignty, Safe assets and exchange rate dynamics under world polarization, Private credit and financial stability, Climate regulation U-turn and implications for climate finance, Defence policy needs and European financial architecture</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Federal Reserve Day-Ahead Conference on Financial Markets and Institutions</t>
+          <t>Conference on The Industrial Organization of Financial Markets</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA 10 N Independence Mall W, Philadelphia, PA 19106</t>
+          <t>SKEMA Business School, Sophia Antipolis (Nice) campus, France</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4749,108 +4741,108 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Monetary policy implementation, money markets and central bank balance sheets; Financial stability and the conduct of monetary policy; Maturity transformation, liquidity risk, and runs on financial institutions; Nonbank financial intermediation; Financial markets and the macroeconomy; Real estate and mortgage markets; Household finance and the transmission of monetary policy; Financial innovation and artificial intelligence; Effects of inflation on financial markets and institutions; Interconnectedness of global financial markets; Cryptocurrencies and stablecoins; Emerging risks to financial stability</t>
+          <t>market structure and competition, innovation and strategic behavior in the organization of the financial markets, payment card industry, lending and digital banking, primary and secondary markets for equity, government debt and corporate debt, financial regulation and competition policy, interbank lending markets, retail funding markets, credit markets, including mortgages</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>First Annual Corporate Governance Academic Forum</t>
+          <t>Fourteenth Oxford Financial Intermediation Theory Conference (OxFIT)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Toronto, Ontario, Canada</t>
+          <t>Saïd Business School, University of Oxford</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CAN$100 per paper</t>
+          <t>£65 GBP</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Boards of directors; executive compensation and incentives; mergers; ownership structure; shareholder activism; ESG and sustainability governance; governance of new technologies; political influences on governance</t>
+          <t>Financial crises, Governance of financial institutions, The role of central banks and regulators, Financial innovation, International regulatory coordination, Certification in financial markets</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2025 Derivative Markets Conference</t>
+          <t>University of Washington 7th Summer Finance Conference</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Queenstown, New Zealand</t>
+          <t>Seattle, Washington</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD $80 per paper</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>derivative markets and products</t>
+          <t>All areas of finance, particularly submissions from junior faculty and preliminary papers</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2025 New Zealand Finance Meeting</t>
+          <t>4th Tilburg Finance Summit</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Queenstown, New Zealand</t>
+          <t>Tilburg, Netherlands</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4860,71 +4852,71 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>All topics related to finance</t>
+          <t>Asset pricing and behavioral finance</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CEPR European Conference on Household Finance 2025</t>
+          <t>2026 PHBS–IER conference on “Technology, Innovation, Platforms, and Economic Performance”</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025-09-20</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stockholm, Sweden</t>
+          <t>Peking University HSBC Business School, Shenzhen, China</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>50 Euro (waived if all authors are PhD students)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Asset allocation and debt behaviour over the life cycle; Financing retirement and the demographic transition; Consumer indebtedness, financial distress, and default decisions; Behavioral approaches to household finance; Financial literacy and financial education programs; Trust, subjective expectations, pessimism, and financial decisions; International comparisons of household finances using micro-data; Financial advice and legal protection of investors and borrowers; Financial innovation and household finances; Households liquidity and risk management; Climate change, sustainability, and household finances</t>
+          <t>Innovation, Technology Emergence, and Technology Transfer; Technology Adoption, Diffusion, and Automation; Resource Reallocation, Productivity, and Aggregate Dynamics; Geoeconomics and Technology Policy: Fragmentation, Trade, and Innovation; Trading Platforms and Digital Markets: Design, Competition, and Information; Institutions, Finance, Digital Payments, and Regulation in the Digital Economy</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>12th Annual Conference on Financial Market Regulation (CFMR 2025)</t>
+          <t>7th Canadian Sustainable Finance Network Conference</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SEC Headquarters, Washington, DC</t>
+          <t>Alberta School of Business, University of Alberta, Edmonton, Canada</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4934,34 +4926,34 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>sustainable finance and the intersection of corporate governance and sustainability</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Haskell &amp; White Corporate Reporting and Governance Conference</t>
+          <t>2026 Global Finance Conference</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Fullerton, CA</t>
+          <t>University of Azores, Portugal</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4971,400 +4963,404 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>All areas of accounting and finance, including research that overlaps these disciplines; applications of machine learning, artificial intelligence, and big data in financial and accounting contexts</t>
+          <t>Energy, Sustainability, Fintech including AI, Climate change, Alternative Investments, Asset &amp; Wealth Management, Asset Allocation/Sovereign Funds/Hedge Funds/ETFs/SWFs, Banking &amp; Financial Services, Corporate Governance/Executive Compensation, Country Risk/Debt Issues/Insurance/Reinsurance, Derivatives/Financial Engineering, E-Business/E-Finance/Social Media, Emerging Markets/BRICS, Entrepreneurship/Venture Capital Global Perspectives, Ethics/Legal/Regulatory, Accounting, Auditing and Taxation Issues, Financial Crises and Bubbles, Financial Technology including AI, ML &amp; Financial Information Systems, Foreign Currency Issues, Future of Global Economy, Global Trade Issues, IPOs/SEOs/Stock buybacks/Privatization, Market Behavior Efficiency/Inefficiency, Mergers and Acquisitions, Non-Traditional Banking &amp; Financial Services, Portfolio Flows and Foreign Direct Investment, Private Equity, Real estate, Valuation, Portfolio Management and Managing Financial Risk</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2025 Federal Reserve Stress Testing Research Conference: Call for Papers</t>
+          <t>Bayes Junior Asset Management and Asset Pricing Workshop</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts</t>
+          <t>Bayes Business School, London</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>The economic and macroprudential effects of stress tests and bank regulation; Balancing the costs and benefits of bank regulation; The roles and risks of nonbank financial intermediaries and their interplay with the banking system; Financial instruments for risk transfer and their implications; Modeling bank revenues, credit, and counterparty risks; Interest-rate, liquidity, and inflation risk in the banking system; Design of macroeconomic and financial market scenarios; Regulatory and supervisory approaches to non-financial risks, such as cybersecurity and operational risk, and emerging technologies, such as AI</t>
+          <t>asset management, asset pricing, papers that bridge asset management and asset pricing</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Finance and Real Estate Conference 2025</t>
+          <t>Second Annual Notre Dame Investment Management Conference</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oxford, Ohio</t>
+          <t>University of Notre Dame, Notre Dame, Indiana</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>No submission fee</t>
+          <t>70 USD</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation; Corporate finance; Real estate markets and investment; Risk management and financial regulation; Urban economics and housing policy; Sustainable and green finance; Behavioral finance in real estate</t>
+          <t>Asset pricing, financial intermediation, investments, demand based asset pricing, inelastic markets hypothesis, new methods in asset pricing (machine learning, AI, unstructured data), time series and cross-sectional predictability, portfolio allocation for long term investors, retirement decisions and choices, behavioral finance</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Melbourne Asset Pricing Meeting</t>
+          <t>Future Finance Fest (3f)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>No submission fee</t>
+          <t>0 EUR</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Theoretical and empirical models of asset prices and returns; return predictability; empirical methodology; macro-finance; the study of financial institutions as related to asset prices; information and liquidity in asset markets; behavioural investment studies; asset market structure and microstructure; risk analysis; hedge funds; mutual funds; pension funds; ESG; the impact of COVID-19; and alternative investments</t>
+          <t>AI, asset pricing, banking, behavioral finance, big data, blockchain, CBDCs, compliance, crowdfunding, cryptocurrencies, cybersecurity, decentralized finance, digital finance, embedded finance, fintech, financial infrastructure, financial inclusion, financial innovation, financial intermediation, financial markets, household finance, insurtech, machine learning, market microstructure, payments, platforms, regulation, risk management, stablecoins, tokenization, text analytics.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
+          <t>2026 FMA Applied Finance Conference</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Pullman Paris Montparnasse Hotel (France)</t>
+          <t>St. John's University - Manhattan Campus, New York, NY</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>50€ (EUR)</t>
+          <t>$50 USD (FMA-members) and $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Inform practice and advance the frontiers of academic research in directions relevant to practice; Address issues that are relevant to contemporary issues globally and for policy formation and assessment; Introduce new hypotheses that have the potential to stimulate additional research</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2nd Knut Wicksell Conference on Crypto and Fintech</t>
+          <t>Exeter Sustainable Finance Conference 2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Lund, Sweden</t>
+          <t>University of Exeter Business School, Exeter, UK</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>No participation fee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Crypto and blockchain technology (asset pricing, systemic risk, market microstructure); Crypto markets, households, and the real economy; Environmental and social impact of crypto markets; Central Bank Digital Currencies (CBDCs); Financial technology (Fintech); Payment systems (payment firms, consumer experiences, bank competition); Interaction between traditional finance and decentralized finance</t>
+          <t>Unpublished research papers on any topic related to sustainable finance, interdisciplinary research</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2025 Vietnam Symposium in Banking and Finance (VSBF-2025)</t>
+          <t>9th Cryptocurrency Research Conference (CRC2026)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>regulation and financial services</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ricing and allocation</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>nance</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Cryptofinance, blockchain economics, digital finance, cryptocurrencies, financial economics, FinTech, AI for finance</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>The Second PHBS-IER Conference on "Demographic Change and Migration: Facts, Models and Policy Implications"</t>
+          <t>Accountability in a Sustainable World Conference</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School, Shenzhen, China</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$200 USD</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Driving factors of demographic change: empirics and modeling of fertility and mortality; Internal and international migration flows induced by demographic change; The impact of population aging on public finances and the future of social insurance systems (social security, health care, long-term care etc.); Demographic change, migration flows and national and local labor markets; Migration and the spatial distribution of economic activity; The interaction between demographic change, technological progress, and economic growth; The impact of demographic change on housing and financial asset prices and returns; Focus on Asian economies is encouraged</t>
+          <t>Non-academic-friendly summaries of research, pressing questions informed by academic research, sustainability issues</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Frontiers in Quantitative Finance Conference 2025</t>
+          <t>33rd Finance Forum</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>New York Marriott Marquis</t>
+          <t>Alicante, Spain</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 €</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Quantitative methods; asset pricing (including topics related to the work of Sanford J. Grossman)</t>
+          <t>Asset Pricing, Corporate Finance, Banking, Portfolio Choice and Asset Management, Microstructure, Regulation, Financial Stability, Macrofinance</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>NTU AI &amp; Business Forum: NTU Summer School &amp; Conference on AI for Finance</t>
+          <t>3rd Workshop on Recent Trends and New Developments in Sustainable, Green and International Finance</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Nanyang Business School, Nanyang Technological University (Singapore)</t>
+          <t>EDHEC Business School, Nice Campus, Nice, France</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>220 EUR (academics and professionals), 180 EUR (Ph.D. students)</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Algorithmic and high-frequency trading strategies; AI in Risk management and credit scoring; AI-based Portfolio optimization; Natural language processing in financial applications; Robo-advisory services and fraud detection; Financial forecasting and market sentiment analysis using AI/ML; Reinforcement learning for dynamic trading; AI regulations and ethical decision-making in Financial AI; Other AI-related research in finance</t>
+          <t>Sustainable finance, green finance, climate finance, international finance</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>International Society for the Advancement of Financial Economics 2025 Conference (ISAFE – China)</t>
+          <t>Alpine Finance Summit (AFS) 2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Beijing, China</t>
+          <t>Garmisch-Partenkirchen, Germany</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>50 EUR</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>AI and finance; Asset allocation and valuation; Central banking and monetary policy; Corporate finance and governance; Country funds and hedge funds; Emerging markets finance; Empirical assets pricing; Financial accounting, law, and regulation; Financial crises and contagion; Financial econometrics; Financial engineering and derivatives; Financial intermediation, institutions &amp; services; Financial markets and market microstructure; FinTech: Revealing Potential and Challenges; Foreign currency issues; International finance and capital markets; IPOs, SEOs, M&amp;As &amp; Divestitures; Market behavior efficiency; Multinational financial management; Personal finance and household finance; Portfolio management and optimization; Quantitative finance and financial econometrics; Real estate finance; Risk management; Small business and entrepreneurial finance; Sustainable finance, ethics, and CSR</t>
+          <t>Asset Pricing, Investments, Sustainable Finance, FinTech</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>8th Dauphine Finance PhD Workshop</t>
+          <t>The 22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>Park Hyatt Busan, Busan, Korea</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5374,71 +5370,71 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Papers in all areas of Finance and Financial Economics are welcome</t>
+          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>The 19th NYCU International Finance Conference</t>
+          <t>NBER-SAIF Conference on AI and Financial Markets</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>US$250</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>The impact of investment in AI and supporting technologies on corporate earnings and share prices, the effects of AI on portfolio choices and trading behavior of financial market participants, the role of AI in creating new measures of economic activity, the uses of AI in financial market regulation, consequences of AI for the financial advice industry, macroeconomic effects of AI on economy-wide discount rates</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Symposium on Financial Markets in the Era of Climate Change, Madrid</t>
+          <t>12th Workshop on Banking and Institutions</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Madrid, Spain</t>
+          <t>Bank of Finland, Helsinki</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5448,34 +5444,34 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Climate risks; Green financial products; Sustainable investing; Corporate green strategy; Environmental externalities; Climate-related regulation</t>
+          <t>geopolitics and banking, political economy of banking, banking and society, banking in emerging markets, climate and banking, monetary policy and institutions</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>The 38th Australasian Finance and Banking Conference</t>
+          <t>ENTFIN 2026 Conference</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>Kedge Business School, Marseille, France</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5485,71 +5481,71 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Opportunities and Risks of AI Technology in Finance; CBDCs, Fintech, and Digital Finance; Sustainable Investment</t>
+          <t>Venture capital; private equity; Business angels and early-stage financing; Crowdfunding; token offerings and digital finance; Entrepreneurial banking and credit relationships; Corporate governance; contracts and monitoring; Financial innovation; FinTech; AI in entrepreneurial finance; ESG; sustainability; impact finance; Entrepreneurial ecosystems; regional financing gaps; Entrepreneurial risk-taking; behavioral finance; Impact assessment for publicly supported financial instruments</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2025 GSU-MS AI and FinTech Conference</t>
+          <t>9th Short-Term Funding Markets Conference</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025-10-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Buckhead Center of Georgia State University, Atlanta, GA</t>
+          <t>Federal Reserve Board, Washington, D.C.</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>$100 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>AI Methods and Applications in Finance and Economics; Impact of AI and New Technologies; Risk and Regulation of AI and FinTech; Other AI and FinTech topics (Big Data, Digital Economy, DeFi, Cryptoeconomics, and additional relevant topics)</t>
+          <t>Maturity and liquidity transformation, Repo markets, Theories of frictions and fragility in short-term funding markets, Effects of regulation and central bank intervention, Securities lending, Money creation and the demand for safe assets, Fintech and encrypted currency</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2nd Financial Fraud, Misconduct and Market Manipulation Conference</t>
+          <t>21st Central Bank Conference on the Microstructure of Financial Markets</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>Eltville am Rhein, Germany</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5559,108 +5555,108 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Theoretical and empirical analysis of financial fraud; Case studies of recent instances of market misconduct; Insider trading; Implication of financial fraud/market manipulation for market efficiency, stability, and asset pricing; Market manipulation at a high-frequency (intraday) level; Fraudulent activities and crypto currency markets; Social networks, fake news, and their effect on financial markets; Money laundering and banking; Conflicts of interests and their implications for various stake holders and financial markets; Hedge funds/Mutual funds and their involvement in market misconduct; Statistical/ Machine Learning methods for fraud detection; Cyber security and cyber risk management; Regulatory response to financial misconduct; Unintended consequences of politics and regulations</t>
+          <t>Artificial intelligence and market microstructure, The functioning and resilience of sovereign bond and repo markets</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Future Finance Fest (3f)</t>
+          <t>2026 PRIVATE EQUITY RESEARCH CONSORTIUM (PERC) EUROPE SYMPOSIUM</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vilnius, Lithuania (Old Town Vilnius)</t>
+          <t>Oxford, England</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>No submission fee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Any work with practical implications for the future of finance.</t>
+          <t>Private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Finance Conference</t>
+          <t>Lake District Workshop in Corporate Finance</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Campus (100 International Drive, Baltimore, MD)</t>
+          <t>Windermere, Lake District, United Kingdom</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£60 GBP</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>All areas of finance; emphasis on early-stage papers</t>
+          <t>Corporate Finance</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>TSE Industrial Organisation &amp; Finance Conference</t>
+          <t>8th Annual Workshop on Financial Institutions Research</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Toulouse School of Economics</t>
+          <t>Gateway Conference Center, Federal Reserve Bank of St. Louis; St. Louis, MO USA</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5670,145 +5666,145 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Competition between financial service providers; Entry of new players in the financial intermediation chain (Fintechs, NBFIs); Integration between different financial services (e.g., payment and credit) or between financial services and other activities (e.g., social networks and payment); The role of data in the provision of financial services, Open Banking; The use of structural estimation techniques to analyze the demand for financial products and/or strategic interactions between financial firms; The impact of the organization of financial firms for product market competition</t>
+          <t>Bank Regulation, Supervision, and Compliance; Bank Risk-taking, Stability, and Financial Crises; Lending and Credit Allocation; Bank Governance, Ownership, and Compensation; Bank Disclosure, Accounting, and the Information Environment; Deposits, Funding Structure, and Liability Management; Financial Technology, Innovation, and Bank Competition</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2nd Exeter Sustainable Finance Conference</t>
+          <t>Southern Finance Association 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Exeter, United Kingdom</t>
+          <t>LaQuinta Resort, Palm Springs, CA</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Unpublished research papers on sustainable and responsible finance; interdisciplinary research that draws together approaches from different disciplines.</t>
+          <t>Papers on any area of finance, proposals for panel discussions, special sessions, or tutorials</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Hybrid Conference on Islamic Law and Finance</t>
+          <t>International Accounting &amp; Finance Doctoral Symposium (IAFDS)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Durham University Business School, Waterside Building Campus, UK</t>
+          <t>Cagliari, Sardinia, Italy</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£300</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Financial Innovation (including FinTech); Shaping Monetary Policy from a Maqasid perspective; Designing Fiscal Policy from a Maqasid perspective; Artificial Intelligence (AI) in Islamic Finance; Legal and Regulatory Frameworks; Access to Finance and Social Welfare; Corporate Governance and Shari’ah Compliance; Purpose-Based vs. Problem-Based Approaches; Cultural Dimensions in Islamic Finance; Islamic Finance for Global Challenges; Governance Mechanisms and Stakeholder Accountability</t>
+          <t>Original empirical and theoretical papers in accounting and finance (including banking), focusing on significant and impactful issues within these fields</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>21st Annual Conference of the Asia-Pacific Association of Derivatives (APAD)</t>
+          <t>13th Annual Conference on Risk Governance</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>Board-level decision-making in dynamic environments</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Busan, Korea (Online and In-Person)</t>
+          <t>- Risk Governance and the monitoring role of supervisory boards</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>US$200 (waived for presenters of accepted papers)</t>
+          <t>- Stakeholder influence and external pressure on board-level decision-making</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Corporate Governance; Market Microstructure; Banking; Personal and Household Finance; ESG and Climate Finance; AI and Big Data; Blockchain and Crypto Assets; Fintech; Regulation; Behavioral Finance; among others</t>
+          <t>- Risk Governance in the boardroom: How directors navigate uncertainty</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EBA's 14th Policy Research Workshop: Bridging capital and growth - the role of financial structures and intermediaries</t>
+          <t>SHoF Annual Conference on the Future of Private Capital Markets</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>EBA premises (Paris, France) and remotely</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5818,108 +5814,108 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>The impact of global capital flows on market efficiency and the role of financial intermediation; Access to finance by entrepreneurs ensuring that capital is used in the most productive ways; Provision of mechanisms for managing risk and contribution from regulatory frameworks on the functioning and stability of financial intermediaries; Incorporation of environmental, social, and governance (ESG) supporting sustainable development and growth; Advances in digital finance initiatives and better alignment with regulation and policies</t>
+          <t>Private equity and private credit market structure, Private capital strategies and performance, The interaction between private and public capital markets, Private capital and corporate investment, productivity, and innovation, Structured lending within the private market, Fund organization, governance, and incentives, Financing of infrastructure and energy transition, Risk-taking and financial stability implications, The role of private capital in downturns and periods of financial stress, Regulatory and policy implications of the growth of private markets, ESG, sustainability, and impact in private capital markets</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>5th CEPR-Stigler Center Conference on Political Economy of Finance: Governance in a Polarized World</t>
+          <t>CU Denver 9th Annual J.P. Morgan Center International Commodities Symposium</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>London, United Kingdom (Imperial College London)</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Political economy of finance in a polarized world; governance changes in private and public sectors; corporate governance under polarization; inequality and politicization; climate change and economic decline; trust and social cohesion; governance trade-offs faced by voters, businesses, and governments</t>
+          <t>Recent developments in commodity business, energy, metals and minerals, agriculture, commodity futures, derivatives, and related research topics</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Inaugural Finance Conference Vitznau 2025</t>
+          <t>Bocconi-Bristol Second Sustainability and Green Finance Research Workshop</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vitznau, Switzerland</t>
+          <t>Bocconi University, Milan (Italy)</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 EUR</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Machine learning for the cross-section of returns; Big data analysis; Large language models and unstructured data; Non-standard datasets for return predictions; Systematic expectations mistakes, and predictable returns; Feasible and implementable portfolios; Predictable turning points</t>
+          <t>New Global Challenges: Climate Change, Biodiversity Loss, and Geopolitical Risk</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2025 Canadian Derivatives Institute (CDI) Conference</t>
+          <t>Alliance for Research on Corporate Sustainability (ARCS) 18th Annual Research Conference</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Montréal, Canada</t>
+          <t>Nanyang Business School, Nanyang Technological University (Singapore)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5929,108 +5925,108 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Climate change/risk management, decarbonization challenges and opportunities, technology/AI-driven sustainability solutions, corporate impacts on biodiversity and nature-based business solutions, sustainability reporting and disclosure, sustainable/responsible supply chains, sustainable finance, green marketing, green entrepreneurship, renewable energy investments, cleantech innovation, sustainable natural resource management, business/NGO partnerships, sustainable mobility, social dimensions of sustainability such as inequality, fair wages and working conditions, social and environmental justice, cross-border impacts of geopolitical and regulatory dynamics, and “base of the pyramid” (BoP) development strategies.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>The Institute for Quantitative Investment Research, Residential Seminar, Autumn 2025</t>
+          <t>Finance Research Revolution Conference</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Eastwell Manor, Kent, United Kingdom</t>
+          <t>Weggis, Switzerland</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHF 75 per paper</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Factors and Macro Risks in a Changing World; Diversification in an inflationary environment; AI applications in investment management; Quantitative investing in private assets; Causality and models of expected returns</t>
+          <t>Machine learning for the cross-section of returns, Big data analysis, Large language models and unstructured data, Non-standard datasets for return predictions, Systematic expectations mistakes and predictable returns, Feasible and implementable portfolios, Predictable turning points</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>8th CEIBS Finance/Accounting Symposium</t>
+          <t>2026 FMA European Conference</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Braga, Portugal</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD (FMA-members) and $85 USD (non-members)</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Corporate Finance and Governance; Private Equity and Venture Capital; Fintech; Political Economy of Finance; related subfields of finance, accounting, and economics</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>12th SAFE Asset Pricing Workshop</t>
+          <t>40th Annual Mitsui Symposium: Private Capital Markets</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Theodor W. Adorno Platz 3, House of Finance, 60323 Frankfurt, Germany</t>
+          <t>Ann Arbor, Michigan</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6040,34 +6036,34 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>All areas of asset pricing (theoretical, empirical, intermediary, macrofinance etc.)</t>
+          <t>Technology and Private Markets, Private Markets and Real Economic Outcomes, Access to and Democratization of Private Markets, Private Equity and Venture Capital, Private Credit and Direct Lending, Private Real Assets, Entrepreneurship and Innovation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>9th SAFE Market Microstructure Conference</t>
+          <t>Third Chicago Booth Treasury Markets Conference</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Theodor W. Adorno Platz 3, House of Finance, 60323 Frankfurt, Germany</t>
+          <t>Chicago, Illinois</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6077,145 +6073,145 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>All areas of market microstructure</t>
+          <t>Debt sustainability and public finance, Interactions between monetary and fiscal policy, The international role of U.S. Treasuries and the U.S. dollar, Market structure and fragilities in Treasury markets, Treasury basis trades and leveraged intermediation, Interactions between funding markets and Treasury markets, Liquidity provision, market-making capacity, and regulatory constraints, Financial stability implications of Treasury market dynamics</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>14th Fixed Income and Financial Institutions (FIFI) Conference</t>
+          <t>Cambridge Corporate Finance Theory Symposium 2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025-11-08</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Columbia, South Carolina, USA</t>
+          <t>Cambridge, UK</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>USD 75</t>
+          <t>£50 GBP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fixed income; commercial and investment banks; asset management and mutual funds; short sellers; hedge funds; broker-dealers; insurance companies; private equity and venture capital; FinTech; and related topics.</t>
+          <t>Theoretical corporate finance, banking, market micro-structure, asset pricing, financial accounting</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>The 8th Cryptocurrency Research Conference (CRC2025)</t>
+          <t>Fifth Annual Conference on Financial Markets</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>National and Kapodistrian University of Athens, Athens, Greece</t>
+          <t>UCLA Anderson, Los Angeles, CA</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>£400</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>AI and Machine Learning in Crypto and Blockchain; Big Data in Fintech; Blockchain in Global Finance; Crypto Asset Efficiency and Market Behaviour; Central Bank Digital Currencies (CBDCs); Crowdfunding and P2P Lending; Cybercrime and Cybersecurity in Fintech; Digital Banking and the Digital Economy; Decentralized Autonomous Organizations (DAOs); Decentralized Finance (DeFi); DEXs vs. CEXs: Market Dynamics; Environmental Sustainability of Cryptocurrency; Fintech Regulation and Compliance; Cryptocurrency and Financial Stability; Media and Investor Attention on Fintech and DeFi; Non-Fungible Tokens (NFTs) and Digital Assets; Natural Language Processing (NLP) in Fintech; Blockchain Opportunities for Entrepreneurs; Russian Sanctions and the Fintech Industry; Stablecoins: Design and Risks; AI-Driven Innovation in Crypto Markets; Preparing for post-Quantum Blockchain; Other relevant topics.</t>
+          <t>Financial markets</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>6th CEAR-RSI Household Finance Workshop</t>
+          <t>2026 Global Entrepreneurship and Innovation Research Conference (GEIRC)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Montréal, Québec, Canada (HEC Montréal, 501, rue De La Gauchetière Ouest, Montréal, QC H2Z 1Z5, Canada)</t>
+          <t>Cambridge, United Kingdom</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$200 USD</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Consumption-saving decisions and investment choices; Financial literacy and education; Pensions and retirement; Financial planning and advice; Financial delinquency and bankruptcy; Household insurance and risk management</t>
+          <t>Entrepreneurship and innovation, Scaling frontier technologies, Industrial policy and innovation, University-industry collaboration, Global innovation networks, Innovation finance, and Universities, governments, and policy in the new geopolitical era.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Compensation of Top Executives: Determinants and Consequences</t>
+          <t>5th Annual Hong Kong Conference on FinTech and AI in Finance</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Cambridge, MA</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -6225,108 +6221,108 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>The effects of CEO pay on firm performance and behavior; The relationship between CEO pay and the market for executive talent; The role of institutional investors and other shareholders in setting CEO pay; Drivers of variation in CEO pay across time, firms, and countries; The optimal design of CEO pay contracts; The effects of regulation on CEO pay</t>
+          <t>Empirical finance with AI and Big Data applications, New empirical method development in machine learning and financial econometrics, Blockchain technology, digital assets, and frontier FinTech topics</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Research Symposium on Finance and Economics (RSFE) 2025 (Virtual)</t>
+          <t>2026 Annual International Journal of Central Banking Research Conference</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>IFMR GSB, Krea University, Andhra Pradesh, India (Virtual)</t>
+          <t>Swiss National Bank, Bern</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>0 USD (no submission fee)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Finance: Corporate Finance, Capital Structure and Dividend Policy, Emerging trends in Corporate Finance and Corporate Governance, Mergers and Acquisitions, Financial Reporting and Regulations, Behavioural Finance, Computational Finance and Financial Econometrics, Asset Pricing, Financial Markets, Derivatives Trading and Pricing, Market Microstructure and Algorithmic Trading, Banking and Risk Management, Digital Finance, Financial Tech, AI, and Machine Learning. Economics: Microeconomics, Applied Microeconomics, Macroeconomics, International Economics, International Trade, Development Economics, Energy Economics, Econometrics, Applied Econometrics, Public Finance, Political Economy, Game Theory, Economic Growth, Environmental Economics, and Labour Economics. The list of topics mentioned above is indicative and research papers on other topics of Finance and Economics are also welcome.</t>
+          <t>New Technologies and Their Implications for Monetary Policy and Financial Stability, AI and automation impact on inflation dynamics, risks to financial stability from technological developments, central banks' adaptation in an AI/automation driven economy, transformation of financial markets, macroprudential supervision risks and opportunities, effects on monetary policy transmission mechanism, AI optimization of monetary policy decision making</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ABF&amp;E Annual Meeting (Academy of Behavioral Finance &amp; Economics)</t>
+          <t>Research in Behavioral Finance Conference 2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Silicon Valley/Santa Clara, CA, USA</t>
+          <t>Amsterdam, the Netherlands</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>USD 99.00</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics; Neuroscience/Neuromorphic Computing; Quantum Entanglement Political Economy; Biological Anthropology; Brain-Computer Interfaces; Development of new financial &amp; economic models for decision making and risk taking; Decision making under risk and uncertainty (including AI-based models); Venture startups and exits; Trust in financial markets; Investment in and functioning of financial markets; Financial management of companies; Entrepreneurship, Innovation, and Economic Development; Sustainable Finance; Role of Behavioral Finance &amp; Economics in Personal Finance and Retirement Planning; Teaching, Learning, and Training using AI/AGI; Applications of behavioral finance in practice (empirical/impactful works); Nudging clients and markets.</t>
+          <t>All aspects of behavioral finance, including financial behavior of individuals, groups, organizations, market dynamics, and intersections of these areas</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>The 16th Annual Financial Markets and Liquidity (AFML) Conference</t>
+          <t>9th Annual GRASFI Conference</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Budapest, Hungary</t>
+          <t>Liège, Belgium</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6336,34 +6332,34 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>General finance topics (Corporate finance; Investments; Banking; Asset Pricing; Mathematical Finance; Systemic Risk; Regulations; ESG Investments and Sustainability; Climate Finance; Household Finance; AI and Machine Learning; Game Theoretic Aspects of Financial Markets); Liquidity-focused topics (Market and Funding Liquidity; Global Liquidity; Leverage and Macroeconomic Determinants; Market Microstructure; Illiquid Alternative Investments; Asset Innovations)</t>
+          <t>Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2025 Conference on Accounting and Finance Research and Education in the Era of Rapid Technological Advances</t>
+          <t>Red Rock Finance Conference 2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Suzhou, China (Xi’an Jiaotong-Liverpool University, Suzhou; online attendance available)</t>
+          <t>Zion National Park</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6373,71 +6369,71 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Artificial intelligence (AI), big data, and machine learning; Blockchain, cryptocurrencies, and digital finance; Fintech and financial inclusion; Cybersecurity in financial data management; Accounting for technology and innovation; Business ethics and corporate governance; Corporate social responsibility (CSR); Environmental, Social and Governance (ESG); Entrepreneurship, innovation and sustainability; Regulation and the roles of government; Risk management in the digital age; Green finance, green innovation and technology; Green supply chain analysis and social responsibility in global supply chains; Curriculum design and educational research; Pedagogy and case studies; Proposals for Panels, Workshops, and Tutorials</t>
+          <t>Any topic related to finance</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>4th Holden Conference in Finance and Real Estate</t>
+          <t>Inaugural Rutgers Finance Research Conference</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Bloomington, Indiana</t>
+          <t>Rutgers Business School – Newark &amp; New Brunswick, NJ</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>USD 95</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>All finance and real estate topics; empirical and theoretical papers</t>
+          <t>Innovative research across all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>The 2025 5th Global PhD Student Colloquium</t>
+          <t>AI in Finance Conference</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>University of Sydney Business School, Australia</t>
+          <t>Washington, DC, USA</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6447,145 +6443,145 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>All business disciplines; especially Finance and Accounting</t>
+          <t>Uses of AI by firms in corporate finance, AI in trading and asset management, AI use by banks, AI for financial forecasting, AI in understanding consumer financial behavior, labor replacement vs. augmentation, financial market implications of AI use, financial stability and disparities, frictions in AI adoption and regulatory solutions</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2025 UGA Fall Finance Conference</t>
+          <t>2026 UNSW Corporate Finance Workshop</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Athens, GA</t>
+          <t>Coogee Beach (Sydney, Australia)</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>$65 USD</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Papers in all areas of finance are welcome.</t>
+          <t>All areas of Finance with a special focus on Corporate Finance, including banking, household and entrepreneurial finance</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2025 FMA Annual Meeting</t>
+          <t>9th Bristol Workshop on Banking and Financial Intermediation</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Vancouver, BC, Canada</t>
+          <t>University of Bristol, Bristol UK</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>75 USD (current FMA members); 85 USD (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>All areas of finance; financial decision-making; financial management and related topics</t>
+          <t>theoretical and empirical papers in banking and financial intermediation</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>The Fifth Israel Conference in Behavioral Finance</t>
+          <t>CCA-ESCP Workshop on Financial Institutions and Corporate Finance</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Academic College of Tel Aviv-Yaffo, Israel</t>
+          <t>ESCP Business School - Turin Campus</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>All areas of behavioral finance, including applications to the theory of the firm, individual and professional investors, experimental finance, financial markets, international finance, and ESG investing; special emphasis on the intersection of behavioral finance and women, including how nudges via social networks or AI products may support women's involvement and improve their financial decisions.</t>
+          <t>Interactions among banks, non-bank intermediaries, and capital markets; Effects of technological innovation — including digital banking, fintech, big data, and AI; Consequences of bank regulatory and supervisory reforms; Determinants of financial fragility, liquidity transformation, and systemic risk; Climate, sustainability, and transition finance; Corporate investment, capital structure, and liquidity management; Governance, ownership structures, incentives, and diversity; Monetary-policy transmission through banks and non-banks; Household and entrepreneurial finance; Impacts of geopolitical, political-economy, and policy shocks in finance</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>NTU Summer School &amp; Conference on AI for Finance</t>
+          <t>Boulder Summer Conference on Consumer Financial Decision Making</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Nanyang Business School, Nanyang Technological University, Singapore</t>
+          <t>Boulder, Colorado (St. Julien Hotel and Spa)</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6595,71 +6591,71 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Overview of how ML/AI are transforming finance and accounting research; Financial forecasting; Advances in deep learning for asset pricing; Reinforcement learning for trading and portfolio management; ML tools for dynamic structural models; NLP in finance; AI in asset pricing, portfolio management, corporate finance, and financial accounting; Algorithmic and high-frequency trading; AI in risk management and credit scoring; AI-based portfolio optimization; Robo-advisory services and fraud detection; Market sentiment analysis using AI/ML; AI regulations and ethical decision-making in Financial AI</t>
+          <t>Financial behavior, consumer decision-making</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>The 32nd Annual Global Finance Conference</t>
+          <t>Oxford Saïd - VU SBE Macro-finance Conference</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Boston, MA</t>
+          <t>Saïd Business School, University of Oxford</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>₤45</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Accounting, Auditing, and Taxation; Banking, Financial Services, and Investment Banking; Behavioral and Experimental Finance/Economics; Big Data, AI, Machine Learning, and Fintech in Global Finance &amp; Banking; Emerging Markets (BRICS, MIST, MINT, Next 11, PIIGS, SANE); Corporate Finance, Investments &amp; Global Perspectives; Corporate Governance and Executive Compensation; Green Finance &amp; ESG Investments; Climate Risks and Financial Stability; Global Health Issues and Pandemic Impacts; Derivatives, Financial Engineering, and Real Options; Entrepreneurship and Venture Capital; Financial Market Integration, Linkages &amp; Segmentation; Foreign Exchange &amp; Monetary Economics; Global Energy and Environmental Finance; Financial Crises, Global Inequality &amp; Economic Imbalances; Household &amp; Micro Finance; IPOs, SEOs, Stock Buybacks &amp; Privatization; Mergers &amp; Acquisitions, Corporate &amp; State Sovereign Wealth Funds; Blockchain, Cryptocurrencies, and Digital Finance; Portfolio Management, Asset Allocation &amp; Foreign Direct Investments; Real Estate Finance, REITs, and Crowdfunding; Risk Management, Debt, Insurance &amp; Reinsurance; Sovereign Wealth Funds, Hedge Funds, ETFs &amp; Mutual Funds; Sustainability, Corporate Social Responsibility &amp; Ethics</t>
+          <t>Monetary policy, macroprudential policy, and fiscal policy; Credit, banks, bankruptcy and systemic risks; International finance, exchange rates, sovereign debt, and debt sustainability; Climate risks and macro-financial implications</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2025 International Symposium on Climate, Finance, and Sustainability (ISCFS-2025)</t>
+          <t>Labor &amp; Finance Group Spring 2026 Conference</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2025-04-20</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>House of Management Science, Paris Pantheon-Assas University, Paris, France</t>
+          <t>Vanderbilt University - Owen Graduate School of Management, Nashville, TN</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6669,71 +6665,71 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>All aspects of energy transition, environmental sustainability, banking, climate finance, financial markets, and the macroeconomy; includes Carbon Finance and Taxes; Climate Finance; Climate Negotiations and Scenarios; Climate Risk and Disclosures; Climate-resilient Economies; Energy Derivatives: Pricing and Hedging; Energy Markets: Modeling, and Forecasting; Energy, Environment, and Climate Models; Financial and Economic Analysis of Energy Markets; Financial Regulation of Energy and Environmental Markets; Green Finance and Sustainable Investment; Just Energy Transition; Macroeconomic Implications of Net-Zero Carbon Emissions; Natural Resources, Risk, Welfare and Social Preferences; Renewable Energy Regulation and Energy Governance; Role of Financial Institutions in Sustainability.</t>
+          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ESSEC-Luxembourg-CEPR Conference on Sustainable Financial Intermediation</t>
+          <t>CEPR 11th European Workshop on Household Finance</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Novotel Reims Tinqueux, Tinqueux, France (Route de Soissons, 51430 Tinqueux)</t>
+          <t>Deutsche Bundesbank Training Centre at Eltville am Rhein</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 euro</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>financial intermediation; household finance; corporate finance; green finance/assets financing; sustainability; housing markets</t>
+          <t>Patterns of asset allocation and debt behaviour over the life cycle, Financing retirement and the demographic transition, Consumer indebtedness, financial distress and default decisions, Behavioural approaches to household finances, Financial literacy and financial education programmes, Trust, subjective expectations, pessimism, and financial decisions, International comparisons of household finances using micro-data, Cognitive and genetic studies on individual financial performance, Financial advice and legal protection of investors and borrowers, The impact of technology on household financial behaviour</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>9th Shanghai-Edinburgh-London Conference Sustainable Finance in the Digital Era; and Special Issues of the British Accounting Review</t>
+          <t>The 10th Vietnam International Conference in Finance</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Shanghai and Online</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6743,71 +6739,71 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>The use of AI and machine learning in ESG investment strategies, sustainability disclosures, and climate risk modelling; Blockchain applications in carbon markets, green bonds and regulatory compliance; Corporate governance challenges, greenwashing detection and market responses to ESG commitments; The role of digital finance, decentralised finance (DeFi) and emerging technologies in supporting a low-carbon transition; Policy frameworks and regulatory challenges shaping the adoption of sustainable finance in developed and emerging markets</t>
+          <t>Corporate finance and governance, Asset pricing, investment, and portfolio management, Finance and sustainability, Financial markets and institutions, Financial technology, artificial intelligence, and big data, Banking and financial regulations, Behavioral finance, Risk management and quantitative finance, Household finance and financial consumer protection</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2025 Vietnam Symposium in Entrepreneurship, Finance, and Innovation (VSEFI2025)</t>
+          <t>Inaugural Rutgers Finance Research Conference</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam (Mövenpick Living West)</t>
+          <t>Rutgers Business School - Newark, NJ</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>0 USD (no submission fee)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>AI, Big Data, and Machine Learning Applications in Finance; Asset Pricing; Bankruptcy and Liquidation; Biodiversity Finance; Climate Finance; Corporate Finance and Governance; Corporate Responsibility and Sustainability; Crypto Assets and Decentralized Finance; Digital Finance; ESG and Sustainable Finance; Financial Markets; Green Cryptocurrencies; Household Finance; Information Disclosure, Market Efficiency, and Transparency; Portfolio and Investment Decisions; Business Model Innovation; Corporate Digital Transformation; Crowdfunding and P2P Lending; Entrepreneurship, Intrapreneurship, and Innovation; Entrepreneurship in Emerging and Transition Markets; Family-Owned Businesses and Governance; Governance and Financing of High-Tech Firms; New Venture Creation and Performance; Social and Sustainable Entrepreneurship; Startups, SMEs, and Resource Allocation; Venture Financing and Entrepreneurial Growth; Digital Human Resources; Digital Innovation, Knowledge Management, and Entrepreneurship; Electronic Markets and Trading Platforms; FinTech and Alternative Finance; Innovation Management and Growth Strategies; Sustainability in the Digital Economy</t>
+          <t>innovative research across all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>20th Central Bank Conference on the Microstructure of Financial Markets</t>
+          <t>2nd EDHEC AI and Finance Workshop</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>EDHEC Business School, Nice, France</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6817,145 +6813,145 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>AI and market microstructure (AI-driven trading algorithms and market quality; AI predictive analytics and their impact on market efficiency; Applications of AI in market making and liquidity provision; Implications of AI for market microstructure design); Financial Innovation and Settlement Cycles (technology and financial innovation shaping settlement cycles; alternative settlement cycles and financial stability; impact of alternative settlement cycles on liquidity, volatility, price efficiency and informativeness); Decentralised Finance and the Digital Asset Ecosystem (asset tokenisation and liquidity/price discovery implications; market fragmentation and information asymmetry in digital-asset markets; decentralised finance: market making, trading mechanisms, market efficiency, regulatory developments; price dynamics and liquidity in stablecoin markets; stablecoin design and peg stability)</t>
+          <t>NLP &amp; large language models; Speech and multimedia analysis; AI agents &amp; automation; Machine learning &amp; predictive analytics; Big data &amp; computational methods; The role of AI in corporate decision-making and other aspects of financial and labor markets; Ethics, policy, and regulation</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Financial Regulation and RegTech Forum</t>
+          <t>Journal of International Money and Finance Special Issue and Conference</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2025-05-16</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Beihang University (Xueyuan Road Campus), Beijing, China</t>
+          <t>Hitotsubashi University, Tokyo, Japan</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>RMB 2000 for non-students; RMB 1000 for students</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Methods and technologies for intelligent monitoring and discovery of abnormal trading behaviors in the securities market; Financial fraud detection methods; Methods for identifying and monitoring illicit financial activities and regulatory technologies; New approaches to financial risk assessment, such as the application of big data and AI methods in risk management; New measurement methods and early warning techniques for financial systemic risk; New methods and technologies for credit risk assessment and credit scoring; Liquidity risk measurement methodology; Supply chain finance in the era of big data; The development of fintech and its impact; Fintech product and institutional risk monitoring; Application and innovation of large language models and generative AI in the financial sector; Interpretable AI; Model risk and model risk assessment methodology; AI approaches in the financial sector and their impact on financial stability; Blockchain technology and its application in financial regulation; Risk identification and monitoring methods for virtual currencies; Key technical facilities in the banking industry; Finance of science and technology; Digital finance</t>
+          <t>Banks’ ESG and Climate Responsibilities, Banks as ESG and Climate Gatekeepers for Corporations, Banks, Climate Risk, and Financial Stability, Regulations, ESG, and Climate Risk, Central Banks, Banking Regulations, and Green Finance</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Northern Finance Association 2025 Annual Meeting</t>
+          <t>3rd Structured Retail Products and Derivatives Conference</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Calgary, Alberta, Canada</t>
+          <t>Hagen, Germany</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CAD 50 per paper (waived for papers authored exclusively by PhD students)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Any topic related to finance</t>
+          <t>behavioral aspects, hedging strategies, market microstructure, pricing policies, product innovations, product valuation, regulatory issues</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Fourth Oxford Sustainable Private Markets Conference</t>
+          <t>QRFE Workshop on Climate Change</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Saïd Business School, University of Oxford, Park End Street, Oxford, OX1 1HP, UK</t>
+          <t>Durham, United Kingdom</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0 USD (no submission fee)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>ESG in private markets (private equity, private debt, real assets)</t>
+          <t>Climate Risk Pricing &amp; Asset Valuation, Institutional Investors &amp; Climate Exposure, Green Finance, ESG, and Real Effects, Carbon Emissions, Disclosure, and Regulatory Policy, Climate Risk Transmission Across Markets, Innovation, Transition Technologies, and Real Economic Impact, Data and Methodological Frontiers</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>New Perspectives on Consumer Behavior in Credit and Payments Markets Conference</t>
+          <t>Commodity and Energy Markets Association (CEMA) 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>ESSEC Business School, France</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6965,34 +6961,34 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>household debt and default; fintech; financial literacy; regulation; linkages between consumer credit and the real economy; innovations in household payments</t>
+          <t>Financial and operational risk analysis, decision making, optimization for sustainable ecosystems, energy and commodity sourcing, processing, trading, and related services.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>6th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
+          <t>3rd QRFE Workshop on Quantitative Finance</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Collegio Carlo Alberto, Turin, Italy</t>
+          <t>Durham, United Kingdom</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -7002,118 +6998,229 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Long-term investors’ strategies and behavior in times of geopolitical fragmentation, rising protectionism and technological breakthroughs; Shifting equilibria in government bond markets driven by quantitative tightening, rising indebtedness and macroeconomic uncertainty; The evolution of sustainable investment strategies and greenlash risks; Challenges for long-term investors stemming from increasing equity market concentration; The rising importance of non-bank investors in credit intermediation and its consequences for the transmission of monetary policy; The rise of cryptocurrencies, emerging financial technologies (fintech) and their impact on investment strategies; Emerging trends in asset allocation and risk management for long-term investors, including insurance companies, pension funds, and mutual funds; Shock transmission mechanisms from the real economy to financial institutions and the amplification of shocks through credit chains, fire sales, and other procyclical processes; The use of big data and artificial intelligence to assess and manage exposure to risk factors; Innovations in financial markets and opportunities for financial institutions; The effects of the demographic transitions on financial markets and the role of long-term investors in tackling them</t>
+          <t>Big Data &amp; Information Efficiency, AI, Automation &amp; Liquidity, Modern Market Design, Blockchain &amp; Digital Market Microstructure, Stability, Systemic Risk &amp; Real Effects, Policy, Regulation &amp; SupTech</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Politics in Finance 2025 Conference</t>
+          <t>19th Annual Corporate Governance Academic Conference</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Georgetown University campus, Washington DC</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>100 USD</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>The role of political connections and political ideologies in shaping capital market forces; How political ideologies affect the decision making by firms and workers; Political connections and corruption in developing economies; The political economy of financial development; The interaction between government and financial institutions; Implications of political uncertainty and political connections for asset prices and corporate policies; Political economy of financial regulation and financial crises</t>
+          <t>corporate governance, board of directors, executive compensation, ownership structure, shareholder activism, institutional investors, mergers and acquisitions, private equity, sustainable finance, regulation, talent management</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>10th RiskLab Finland, Bank of Finland and European Systemic Risk Board Joint Conference on AI and Systemic Risk Analytics</t>
+          <t>11th Conference on Professional Asset Management</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Bank of Finland, Helsinki</t>
+          <t>EDHEC Business School, Nice, France</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Free of charge</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Use of Large Language Models (LLM) and trustworthy AI; AI and changing interdependencies in the financial markets; Cyber security and operational risks as sources of systemic risk; AI and Quantum Computing as potential source of new systemic risks; Use of AI with big data for systemic risk analytics; Risks and opportunities stemming from disruptive innovations in FinTech; Using systemic risk analytics to support macro-prudential policy and regulation; Analysing emerging risks from interconnectedness of the financial system; Identifying risks from market-based finance; Evidence of macroprudential policy measures; Economic policies in the turbulent and uncertain times</t>
+          <t>Performance measurement, attribution, and liquidity in asset valuation; Investor (client) and manager behavior; Conflicts of interest in asset management; Institutional trading strategies and investment styles; Governance and regulation of investment companies; Financial innovation in asset management; The role and influence of financial advisors; Risk management and sector allocation</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2025 USTC Alumni Finance Conference</t>
+          <t>42nd International Conference of the French Finance Association (AFFI)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Hefei, China</t>
+          <t>Clermont-Ferrand</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>No submission fee</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Finance related topics</t>
+          <t>AI and Finance, Agricultural Finance and Insurance, Asset Pricing and Risk Premia, Banking and Financial Intermediation, Banking and Financial Regulations, Behavioral Finance, Blockchain/Cryptocurrencies and Protocols, Climate Change and Climate Risks in Finance, Commodities, Conscious and Mindful Finance, Corporate Finance, Corporate Governance, Development Finance and Microfinance, Ecological Finance, Entrepreneurial Finance, Epistemology of Finance, Ethics in Finance, Experimental Finance, Family Business Finance, Financial Distress and Bankruptcy, Financial Econometrics, Financial Markets, Financial Risk Management, Fintech and Financial Innovations, Geographical Finance, Green Finance, Historical Finance, Household and Personal Finance, Information and Market Efficiency, Insurance, International Finance, Macro Finance, Market Microstructure, Portfolio &amp; Asset Management, Quantitative Finance, Real Estate Finance, Risk Management, Social, Sustainable and Responsible Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Third Annual UIC Finance Conference</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>working papers in all areas of finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>IBEFA Summer Meeting at the 2026 WEAI Conference</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>US$100 (US$50 for papers solely authored by PhD. students)</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>financial intermediation; securitization and shadow banking; financial risk measurement and management; financial stability and macroprudential policies; payments systems; household finance; financial market structure and regulation; monetary policy; financial intermediation and global fragmentation; sustainable finance; FinTech</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Esade Spring Workshop 2026</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Barcelona, Spain</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Asset Pricing and Financial Markets, Corporate Finance and Banking</t>
         </is>
       </c>
     </row>

--- a/public/conference_list.xlsx
+++ b/public/conference_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,27 +456,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026 Global AI Finance Research Conference</t>
+          <t>2026 Climate Finance &amp; Policy (CFP-2026)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Taipei, Taiwan</t>
+          <t>Bari, Italy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -486,51 +486,51 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
+          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
+          <t>2026 Global AI Finance Research Conference</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>99.00 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, decision making under risk and uncertainty, venture startups &amp; exits, trust in financial markets, sustainable finance, behavioral finance in retirement saving &amp; planning, and nudging clients and markets.</t>
+          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colorado Finance Summit 2026</t>
+          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -540,34 +540,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vail, Colorado</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$99.00 USD</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>All areas of finance, theoretical and empirical contributions</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026 UNSW Asset Pricing Workshop</t>
+          <t>Colorado Finance Summit 2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -577,165 +577,165 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sydney (NSW, Australia)</t>
+          <t>Vail, Colorado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0 AUD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>All areas of Finance, with a special focus on Asset Pricing</t>
+          <t>All areas of finance, theoretical and empirical contributions</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
+          <t>2026 UNSW Asset Pricing Workshop</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Venice, Italy</t>
+          <t>Sydney (NSW, Australia)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 AUD</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Credit Risk and Advanced Analytics, Financial Innovation and Digital Transformation, Artificial Intelligence, Data Governance and Ethical Risk, Sustainability and Long-Term Value Creation, Systemic Risk, Resilience and Policy</t>
+          <t>All areas of Finance, with a special focus on Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
+          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Toronto, Ontario (Canada)</t>
+          <t>Venice, Italy</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100 CAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Financial economics and accounting</t>
+          <t>Credit Risk and Advanced Analytics, Financial Innovation and Digital Transformation, Artificial Intelligence, Data Governance and Ethical Risk, Sustainability and Long-Term Value Creation, Systemic Risk, Resilience and Policy</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
+          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lugano, Switzerland</t>
+          <t>Toronto, Ontario (Canada)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100 CAD</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>real estate finance, urban economics, real estate economics, regional economics</t>
+          <t>Financial economics and accounting</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Santiago Finance Workshop 2026</t>
+          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
+          <t>Lugano, Switzerland</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -745,34 +745,34 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Any topic in finance or financial economics</t>
+          <t>Real estate finance, urban economics, regional economics</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
+          <t>Santiago Finance Workshop 2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EM Normandie Business School, Caen campus, France</t>
+          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -782,34 +782,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
+          <t>Any topic in finance or financial economics</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Climate Finance &amp; Sustainability Conference</t>
+          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>EM Normandie Business School, Caen campus, France</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -819,34 +819,34 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Strategy and management, Accounting and finance, Entrepreneurship and innovation, Marketing and responsible consumption, Supply chain and operations management</t>
+          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
+          <t>Climate Finance &amp; Sustainability Conference</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -856,103 +856,103 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ESG in the AI Era: Challenges and Opportunities, AI-Driven ESG Reporting and Assurance, Algorithmic Bias, Ethics, and Fairness in ESG Analytics, Regulatory Responses to AI-Enabled ESG Practices, AI, Greenwashing, and Corporate Accountability, AI for Sustainable Finance and Investment Decision-Making</t>
+          <t>Strategy and management, Accounting and finance, Entrepreneurship and innovation, Marketing and responsible consumption, Supply chain and operations management</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026 FMA Asia/Pacific Conference</t>
+          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Massey University, Auckland, New Zealand</t>
+          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>$50 USD (FMA members), $60 USD (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Financial decision-making, financial management, related topics</t>
+          <t>ESG in the AI Era: Challenges and Opportunities, AI-Driven ESG Reporting and Assurance, Algorithmic Bias, Ethics, and Fairness in ESG Analytics, Regulatory Responses to AI-Enabled ESG Practices, AI, Greenwashing, and Corporate Accountability, AI for Sustainable Finance and Investment Decision-Making</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sixth Biennial Conference on Auto Lending</t>
+          <t>2026 FMA Asia/Pacific Conference</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Massey University, Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, the role of alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, and spillovers from monetary policy and macroeconomic shocks</t>
+          <t>Financial decision-making, financial management, related topics</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
+          <t>Sixth Biennial Conference on Auto Lending</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -967,34 +967,34 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Methodological advances in analyzing complex and high-dimensional data sets, Methodological advances in natural language processing, particularly with respect to causal inference, Innovative applications of generative AI, The societal impacts of AI and algorithmic decision-making</t>
+          <t>Auto lending and consumer finance, consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, spillovers from monetary policy and macroeconomic shocks.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Workshop on Innovations in Credit Scoring</t>
+          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1004,34 +1004,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Innovations in credit scoring, alternative data, fairness, transparency, data privacy, artificial intelligence, machine learning</t>
+          <t>Methodological advances in analyzing complex and high-dimensional data sets; Methodological advances in natural language processing, particularly with respect to causal inference; Innovative applications of generative AI; The societal impacts of AI and algorithmic decision-making</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
+          <t>Workshop on Innovations in Credit Scoring</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1041,34 +1041,34 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>monitoring and forecasting of economic and financial developments; using preliminary and revised data in economic policy formulation and analysis; machine learning applications in real-time macroeconomics; probabilistic forecasts and assessments of crisis risks; related innovative data sets and toolboxes; seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
+          <t>Innovations in credit scoring, alternative data, fairness, transparency, data privacy, artificial intelligence, machine learning</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
+          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1078,93 +1078,93 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>quantitative methods and asset pricing</t>
+          <t>monitoring and forecasting of economic and financial developments, high-frequency data, survey data, text as data, transactions data, granular data, preliminary and revised data in economic policy formulation and analysis, machine learning applications in real-time macroeconomics, probabilistic forecasts and assessments of crisis risks, innovative data sets and toolboxes, seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
+          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Quantitative methods and asset pricing</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026 AIM Investment Conference</t>
+          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austin, Texas</t>
+          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>mutual funds, hedge funds, pension funds, investment management</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
+          <t>2026 AIM Investment Conference</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1179,44 +1179,44 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Austin, Texas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
+          <t>mutual funds, hedge funds, pension funds, investment management</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
+          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Online Conference from Durham University, England, UK</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1226,34 +1226,34 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Islamic finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
+          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
+          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Casa de Campo, La Romana, Dominican Republic</t>
+          <t>Online Conference from Durham University, England, UK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1263,34 +1263,34 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
+          <t>Islamic finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
+          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Australian National University (ANU), Canberra, Australia</t>
+          <t>Casa de Campo, La Romana, Dominican Republic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1300,34 +1300,34 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
+          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
+          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>Australian National University (ANU), Canberra, Australia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1337,29 +1337,29 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Municipal bond markets, primary market frictions, secondary market frictions, role of retail investors, government policies affecting bond price formation, effect of state and federal policies on access to external finance</t>
+          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Inaugural Annual Conference on Insurance</t>
+          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1374,34 +1374,34 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Life insurance, Property &amp; Casualty insurance, Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities, and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
+          <t>Unpublished and highly policy-relevant research papers on municipal bond markets, primary market frictions, secondary market frictions, the role of retail investors, government policies targeting investors for bond price formation, state and federal policies on state and local government access to external finance</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
+          <t>Inaugural Annual Conference on Insurance</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Imperial Business School, London</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1411,34 +1411,34 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
+          <t>life insurance, Property &amp; Casualty insurance, reinsurance and risk transfer, mergers and other ownership changes, private equity ownership and impact on industry, indexed and variable annuities, household insurance choices, insurances’ investment and funding strategies, catastrophe risk, impact of insurance regulation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026 Conference on Auditing and Capital Markets</t>
+          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Imperial Business School, London</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1448,34 +1448,34 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Economic impact of auditing, audit regulation, audit oversight, auditing issuers and brokers and dealers</t>
+          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Future Scholars in Finance Forum</t>
+          <t>2026 Conference on Auditing and Capital Markets</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Beijing, China</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1485,34 +1485,34 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Audit-related topics, economic impact of auditing, audit regulation, audit oversight</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
+          <t>2026 Future Scholars in Finance Forum</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Beijing, China</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1522,34 +1522,34 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>15th LaBS International Banking Workshop</t>
+          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HSE University and online</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Banking in Emerging Markets: Challenges and Opportunities, theoretical and empirical research in banking or household finance, current issues concerning banking in emerging and developing markets</t>
+          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026 Federal Reserve Stress Testing Research Conference</t>
+          <t>15th LaBS International Banking Workshop</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts</t>
+          <t>HSE University and online</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1596,108 +1596,108 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>The economic and macroprudential effects of stress tests and bank regulation, Novel approaches to modeling bank profitability, financial risks, and operational risks, Design and applications of stress scenarios and reverse stress testing, Nonbank credit intermediation, Financial instruments for risk transfer, Recent developments in bank regulation, The impact of emerging technologies on banks and their regulators</t>
+          <t>Banking in Emerging Markets, Household finance</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
+          <t>2026 Federal Reserve Stress Testing Research Conference</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pullman Paris Montparnasse Hotel</t>
+          <t>Boston, Massachusetts</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>75€</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Economic and macroprudential effects of stress tests and bank regulation, novel approaches to modeling bank profitability, financial risks, and operational risks, design and applications of stress scenarios and reverse stress testing, nonbank credit intermediation, financial instruments for risk transfer, recent developments in bank regulation, impact of emerging technologies on banks and their regulators</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EBA's 15th Policy Research Workshop</t>
+          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EBA premises (Paris, France) and remotely</t>
+          <t>Pullman Paris Montparnasse Hotel</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75€</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience; Impacts of efficiency and proportionality; Competition, innovation, market entry, cross border growth and new areas under financial supervision; Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3rd Financial Fraud, Misconduct and Market Manipulation Conference</t>
+          <t>EBA's 15th Policy Research Workshop</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>EBA premises (Paris, France) and remotely</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1707,34 +1707,34 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Theoretical and empirical analysis of financial fraud, Case studies of recent instances of market misconduct, Insider trading, Implication of financial fraud/market manipulation for market efficiency, stability, and asset pricing, Market manipulation at a high-frequency (intraday) level, Fraudulent activities and crypto currency markets, Social networks, fake news, and their effect on financial markets, Money laundering and banking, Conflicts of interests and their implications for various stakeholders and financial markets, Hedge funds/Mutual funds and their involvement in market misconduct, Statistical/ Machine Learning methods for fraud detection, Cyber security and cyber risk management, Regulatory response to financial misconduct, Unintended consequences of politics and regulations</t>
+          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience; Impacts of efficiency and proportionality; Competition, innovation, market entry, cross border growth and new areas under financial supervision; Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
+          <t>3rd Financial Fraud, Misconduct and Market Manipulation Conference</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>California State University, Fullerton</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1744,34 +1744,34 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>All areas of accounting and finance, including research that overlaps these disciplines, corporate reporting, governance, and financial markets.</t>
+          <t>Theoretical and empirical analysis of financial fraud, case studies of recent instances of market misconduct, insider trading, implications of financial fraud/market manipulation for market efficiency, stability, and asset pricing, market manipulation at a high-frequency (intraday) level, fraudulent activities and cryptocurrency markets, social networks, fake news and their effect on financial markets, money laundering and banking, conflicts of interest and their implications for various stakeholders and financial markets, hedge funds/mutual funds and their involvement in market misconduct, statistical/machine learning methods for fraud detection, cyber security and cyber risk management, regulatory response to financial misconduct, unintended consequences of politics and regulations</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>25th Annual Bank Research Conference</t>
+          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
+          <t>California State University, Fullerton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1781,125 +1781,125 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
+          <t>All areas of accounting and finance, including interdisciplinary research related to corporate reporting, governance, and financial markets</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
+          <t>25th Annual Bank Research Conference</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>$99.00 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Trust in Financial/Capital Markets, Financial Markets functionality, Personal Finance, Pedagogy, Evidence-Based Financial Planning, Behavioral/Cognitive Value Investing</t>
+          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>17th Emerging Markets Conference</t>
+          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$99.00 USD</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>The sources of economic success or failure in EMs, Finance in EMs (households, financial markets, financial intermediaries, firms and finance, finance and growth), Political economy, law, public administration, regulation in EMs, The impact of populism upon the possibility of sustained growth, Insights into large EMs that matter in and of themselves, Insights from narrow research projects that illuminate EMs in general, The new phase of globalisation and its consequences for international trade, international finance and the nature of the EM firm, Features of a society that enable or disable convergence into the “normal” package of high levels of freedom and prosperity, The puzzles faced by all kinds of decision makers: individuals, civil society actors, firms, all levels of government, Grand challenges such as climate change: implications for EMs and ramifications of choices made in EMs, State capability in EMs, The interplay of military affairs, foreign policy and economics for EMs</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under conditions of risk and uncertainty, Venture Startups &amp; Exits, Markets &amp; Capital, Investment &amp; Management, Entrepreneurship, Innovation, Economic Development, Sustainable Finance, Personal Finance, Teaching, Learning, and Training using AI or AGI, Empirical Works, Evidence-Based Financial and Retirement Planning Best Practices, Behavioral/Cognitive Value Investing.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026 International Forum on Financial Regulation and RegTech</t>
+          <t>17th Emerging Markets Conference</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Beihang University, Beijing, China</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2000 CNY (Regular / Faculty), 1000 CNY (Student)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Financial regulation, Regulatory Technology (RegTech), FinTech, financial security, AI applications in finance, risk assessment and management, algorithmic bias, data privacy, systemic vulnerabilities</t>
+          <t>The sources of economic success or failure in EMs; Finance in EMs; Political economy, law, public administration, regulation in EMs; The impact of populism upon sustained growth; Insights into large EMs; Insights from narrow research projects; The new phase of globalization; Features of a society that enable or disable convergence; Grand challenges such as climate change; State capability in EMs; The interplay of military affairs, foreign policy and economics for EMs</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
+          <t>2026 International Forum on Financial Regulation and RegTech</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1909,17 +1909,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>House of Management Science, Paris Pantheon-Assas University, 1 rue Guy-de-la-Brosse 75005 Paris, France</t>
+          <t>Beihang University, Beijing, China</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1929,108 +1929,108 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Energy transition, environmental sustainability, banking, climate finance, financial markets, macroeconomy, Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives, Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
+          <t>Financial regulation, Regulatory Technology (RegTech), FinTech, financial security, algorithmic bias, data privacy, financial fraud detection, systemic financial risk, AI applications in finance, and risk assessment methodologies.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
+          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>The Shard, London, UK</t>
+          <t>House of Management Science, Paris Pantheon-Assas University, 1 rue Guy-de-la-Brosse 75005 Paris, France</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>£45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges (DEXs), Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
+          <t>Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Finance, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives: Pricing and Hedging, Energy Markets: Modeling and Forecasting, Energy, Environment, and Climate Models, Financial and Economic Analysis of Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Natural Resources, Risk, Welfare, and Social Preferences, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
+          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lund, Sweden</t>
+          <t>The Shard, London, UK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£45</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crypto and blockchain technology (asset pricing, systemic risk, market microstructure), Crypto markets, households, and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems (payment firms, consumer experiences, bank competition), Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
+          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges (DEXs), Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
+          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
+          <t>Lund, Sweden</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2040,34 +2040,34 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>New risks in a changing political environment, innovative research papers relevant to investment practitioners</t>
+          <t>Crypto and blockchain technology, Crypto markets, households, and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
+          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Shanghai and online</t>
+          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2077,34 +2077,34 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sustainable finance, AI, blockchain, ESG integration, financial development, financial inclusion, regulatory challenges, corporate governance, greenwashing detection, ESG backlash, climate risk modelling, big data, natural language processing, carbon markets, digital finance, decentralized finance, green lending, climate insurance, impact investing</t>
+          <t>New risks in a changing political environment, investment management excellence, innovative and high-quality research related to investment practitioners</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
+          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Park Hyatt Busan, Busan, Korea</t>
+          <t>Shanghai and online</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2114,34 +2114,34 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
+          <t>Financial development, financial inclusion, policy frameworks and regulatory challenges in sustainable finance, cross-border sustainable finance flows, corporate governance and greenwashing detection, ESG backlash and anti-ESG movements, AI and machine learning applications in ESG, big data and natural language processing for ESG, blockchain applications in carbon markets and green bonds, digital finance and decentralised finance in low-carbon transition, fintech-enabled green lending and climate insurance</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FIRN Melbourne Asset Pricing Meeting</t>
+          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Park Hyatt Busan, Busan, Korea</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2151,145 +2151,145 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments</t>
+          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Finance Conference</t>
+          <t>FIRN Melbourne Asset Pricing Meeting</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
+          <t>Melbourne, Australia</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 AUD</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>All areas of finance, particularly early-stage papers that would benefit from feedback and discussion</t>
+          <t>Theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5th Holden Conference in Finance and Real Estate</t>
+          <t>Johns Hopkins Carey Finance Conference</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bloomington, IN</t>
+          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>95 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Empirical and theoretical papers in all finance and real estate areas</t>
+          <t>All areas of finance, particularly early-stage papers that would benefit from feedback and discussion</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
+          <t>5th Holden Conference in Finance and Real Estate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Bloomington, IN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$95 USD</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
+          <t>Empirical and theoretical papers in all finance and real estate areas</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026 New Zealand Finance Meeting</t>
+          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2299,34 +2299,34 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>All topics related to the field of finance</t>
+          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026 Annual Community Bank Research Conference</t>
+          <t>2026 New Zealand Finance Meeting</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis in St. Louis, MO</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2336,145 +2336,145 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Community banking's role in the U.S. financial system; provision of financial services to households, small businesses, and small farms; impact of community banks on local/state economic activity; community banks’ response to financial and economic shocks; effects of regulatory policy on community banks; challenges and opportunities faced by community banks; advantages and disadvantages of the community bank business model</t>
+          <t>All topics related to the field of finance</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
+          <t>2026 Annual Community Bank Research Conference</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gleacher Center - Chicago</t>
+          <t>Federal Reserve Bank of St. Louis in St. Louis, MO</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crony capitalism in 21st century America, political economy, interplay between economic and political power</t>
+          <t>The role of community banks in the U.S. financial system, impact of community banks on local/state economic activity, community banks’ response to financial and economic shocks, effects of regulatory policy on community banks, challenges and opportunities faced by community banks, advantages and disadvantages of the community bank business model</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
+          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>University of South Carolina in Columbia, SC</t>
+          <t>Gleacher Center - Chicago</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>fixed income, commercial and investment banks, asset management and mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
+          <t>Crony capitalism in 21st century America, political economy, business and political elite interactions, economic power and political influence</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Higher Education Finance Research Conference</t>
+          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>University of South Carolina in Columbia, SC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Financial aid, student debt, higher education finance</t>
+          <t>fixed income, commercial and investment banks, asset management and mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026 Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
+          <t>Higher Education Finance Research Conference</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2484,34 +2484,34 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
+          <t>financial aid, student debt, higher education finance</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Financial Decision-Making Conference 2026</t>
+          <t>Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bozeman, MT</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2521,34 +2521,34 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, financial inclusion</t>
+          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>39th Australasian Finance and Banking Conference</t>
+          <t>Financial Decision-Making Conference 2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>Bozeman, MT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2558,145 +2558,145 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
+          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, financial inclusion</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Finance and Real Estate Conference 2026</t>
+          <t>39th Australasian Finance and Banking Conference</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Miami University, Oxford, OH</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
+          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>UGA Fall Finance Conference</t>
+          <t>Finance and Real Estate Conference 2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Athens, GA</t>
+          <t>Miami University, Oxford, OH</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>70 USD</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
+          <t>UGA Fall Finance Conference 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Prague, Czech Republic</t>
+          <t>Athens, GA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>70 USD</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Expectations and Asset Prices; deviations from rational expectations and their implications; optimism and pessimism in asset valuations and market dynamics; investment strategies and anomalies; factor investing; strategic and tactical asset allocation; portfolio choice under model and parameter uncertainty; short selling; institutional investing and asset management.</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>WFE’s Sustainability Conference 2026</t>
+          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Prague, Czech Republic</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2706,108 +2706,108 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Transition finance and market design, Regulatory fragmentation and divergence, Sustainability reporting, data and assurance, Nature and biodiversity in capital markets, Just transition, social and gender finance, Proportionality for SMEs and emerging markets, Carbon market architecture</t>
+          <t>deviations from rational expectations and their implications; optimism and pessimism in asset valuations and market dynamics; investment strategies and anomalies; factor investing; strategic and tactical asset allocation; portfolio choice under model and parameter uncertainty; and short selling</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026 FMA Annual Meeting</t>
+          <t>WFE’s Sustainability Conference 2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>$75 (current FMA members); $85 (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Financial decision-making, financial management, all areas of finance</t>
+          <t>Transition finance and market design, Regulatory fragmentation and divergence, Sustainability reporting, data and assurance, Nature and biodiversity in capital markets, Just transition, social and gender finance, Proportionality for SMEs and emerging markets, Carbon market architecture</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3rd AI in Finance Conference</t>
+          <t>2026 FMA Annual Meeting</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 (current FMA members); $85 (non-members)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics; Portfolio management, trading strategies, and risk management using AI; Large language models (LLMs), NLP, and textual analysis in finance; Corporate finance applications including M&amp;A and investment decisions; Banking, credit markets, and financial intermediation; Cryptocurrency, digital assets, and decentralized finance; ESG, sustainability, and climate finance; Financial regulation, policy analysis, and central bank communication; Real estate finance and urban economics; Alternative data and high-dimensional financial datasets; Investor behavior, sentiment, and attention; Macroeconomic and financial risk forecasting</t>
+          <t>Financial decision-making, financial management, all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026 Summer Research Conference, Centre for Analytical Finance, Indian School of Business</t>
+          <t>AI in Finance Conference</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Indian School of Business, Hyderabad Campus</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2817,34 +2817,34 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Recent Advances in Finance, corporate finance, asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
+          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics; Portfolio management, trading strategies, and risk management using AI; Large language models (LLMs), NLP, and textual analysis in finance; Corporate finance applications including M&amp;A and investment decisions; Banking, credit markets, and financial intermediation; Cryptocurrency, digital assets, and decentralized finance; ESG, sustainability, and climate finance; Financial regulation, policy analysis, and central bank communication; Real estate finance and urban economics; Alternative data and high-dimensional financial datasets; Investor behavior, sentiment, and attention; Macroeconomic and financial risk forecasting; AI in Sustainability and Climate Finance; AI and Real Estate</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>International Risk Management Conference 2026</t>
+          <t>2026 Summer Research Conference</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Warsaw, Poland</t>
+          <t>Indian School of Business, Hyderabad Campus</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2854,51 +2854,51 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology</t>
+          <t>Recent Advances in Finance, corporate finance, asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>The Second USTC Frontiers in Finance Conference</t>
+          <t>International Risk Management Conference 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R.China</t>
+          <t>Warsaw, Poland</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0 CNY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>All topics of finance</t>
+          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Fischer-Shain Research Conference 2026</t>
+          <t>Second USTC Frontiers in Finance Conference</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2908,91 +2908,91 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R. China</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>financial intermediation, banking, financial services</t>
+          <t>All topics of finance</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ECB Money Market Conference 2026</t>
+          <t>Fischer-Shain Research Conference 2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>European Central Bank, Frankfurt am Main, Germany</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Money markets and monetary policy implementation, technological innovation in money markets (stable coins, CBDCs, etc.), the functioning of money markets including non-bank financial institutions, funding strategies, central clearing, and implications of monetary policy.</t>
+          <t>financial intermediation, banking, and financial services</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Finance in the Digital Age (FiDA) Workshop</t>
+          <t>ECB Money Market Conference 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Calgary, Canada</t>
+          <t>European Central Bank, Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3002,34 +3002,34 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>AI, DeFi, robo-advisors, neurofinance</t>
+          <t>Money markets and monetary policy implementation, technological innovation in money markets such as stable coins, CBDCs, instant payments, functioning of money markets including roles of non-bank financial institutions and dealer intermediation, macroeconomic implications of short-term rate volatility and geopolitical developments</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
+          <t>Finance in the Digital Age (FiDA) Workshop</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bank of Italy, Rome, Italy</t>
+          <t>Calgary, Canada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Long-term investors’ strategies and behavior, financing of the real economy, government bond markets, sustainable investment strategies, equity market concentration, non-bank investors in credit intermediation, cryptocurrencies and fintech, asset allocation and risk management, shock transmission mechanisms, big data and AI in investment processes, innovations in financial markets, geopolitical risks, demographic transitions.</t>
+          <t>AI, DeFi, robo-advisors, neurofinance, decentralized finance</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
+          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3056,239 +3056,239 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Madrid, Spain, and virtually</t>
+          <t>Bank of Italy, Rome, Italy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>€350 in person; €50 online option</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, and repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, and venture capital</t>
+          <t>Long-term investors’ strategies and behavior, long-term investors’ role in financing the real economy, shifting equilibria in government bond markets, sustainable investment strategies, challenges for long-term investors, non-bank investors in credit intermediation, rise of cryptocurrencies and fintech, emerging trends in asset allocation and risk management, shock transmission mechanisms, use of big data and AI in investment, innovations in financial markets, geopolitical risks, demographic transitions effects on financial markets.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Fintech and Financial Institutions Research Conference</t>
+          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
+          <t>Madrid, Spain, and virtually</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€350 in person (for conference dinner, lunches, and coffee breaks), €50 online option (for administrative / tech support)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Interlinkages of the fintech sector and the broader financial system, economic consequences and impacts of fintech, regulatory implications of the fintech sector</t>
+          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, and repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, and venture capital</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Aarhus Finance Forum 2026</t>
+          <t>Fintech and Financial Institutions Research Conference</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aarhus, Denmark</t>
+          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>375 DKK</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
+          <t>Interlinkages of the fintech sector and the broader financial system, economic consequences and impacts, regulatory implications of the fintech sector</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>15th CDI Conference on Derivatives</t>
+          <t>Aarhus Finance Forum 2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Montreal, Canada</t>
+          <t>Aarhus, Denmark</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>375 DKK (approx. 50 Euros)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Conference on CSR, the Economy and Financial Markets</t>
+          <t>15th CDI Conference on Derivatives</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Düsseldorf, Germany</t>
+          <t>Montreal, Canada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>€150 for regular participants, €100 for PhD students</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026 Vietnam Symposium on Global Economy (VSGE2026)</t>
+          <t>Conference on CSR, the Economy and Financial Markets</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Düsseldorf, Germany</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€ 150 for regular participants; € 100 for PhD students</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Geopolitical, macroeconomic policy, and development; Trade, foreign direct investment, and global value chain; Climate change, green transition, and public finance; Finance, stability, and sustainable investment; Digitalization, labor markets, and social protection; Urbanization, regional development and resilience; AI, growth, economic impacts, and government policies; Global governance, institutions, and international cooperation.</t>
+          <t>Climate risk and pricing; Role of financial markets, banks, institutional investors in CSR; Effects of CSR on valuation, performance, cost of capital, funding and capital structure; Socio-economic aspects and their implications for companies and financial markets; Corporate governance and CSR; Risk management and CSR; CSR reporting and disclosure; ESG backlash and politicization; Sustainability strategy under new constraints; Measurement: information content and reliability of ESG indices; CSR activities and the economy</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
+          <t>2026 Vietnam Symposium on Global Economy (VSGE2026)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CONRAD Seoul</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3298,34 +3298,34 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Geopolitical, macroeconomic policy, and development; trade, foreign direct investment, and global value chain; climate change, green transition, and public finance; finance, stability, and sustainable investment; digitalization, labor markets, and social protection; urbanization, regional development and resilience; AI, growth, economic impacts, and government policies; global governance, institutions, and international cooperation.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>India Finance Conference (IFC) 2026</t>
+          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Indian Institute of Management Bangalore</t>
+          <t>CONRAD Seoul</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3335,34 +3335,34 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Theoretical and empirical asset pricing, Corporate finance, capital structure and dividend policy, Asset allocation and investment management, Financial crises, systemic risk and macro-finance, Quality of financial reporting and adoption of IFRS, Corporate governance, executive compensation and ownership structure, Computational finance and financial econometrics, Financial Econometrics, Financial risk analytics and management, Market microstructure and algorithmic trading, Financial policy choice, institutions and regulation, Financial Analytics, ESG, Climate Finance, Blended Finance, Insurance / Reinsurance / Pension Funds, Enhancing liquidity in commodity derivatives markets, Financial Literacy and Financial Education</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Edinburgh Financial Technology Conference</t>
+          <t>India Finance Conference (IFC) 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Indian Institute of Management Bangalore</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3372,34 +3372,34 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>The application of AI and Machine Learning in finance; The application of distributed ledger technologies in finance; Cryptofinance; Cyber risk in finance; The microstructure of modern financial markets: algorithmic/high frequency trading, dark trading, blockchain settlements; Behavioural economics in financial technology; Alternative data (structured and unstructured datasets); Crowdsourcing and investment strategy; New exchange traded financial derivatives; Financial stability risks from the development of FinTech; RegTech; Open banking</t>
+          <t>Theoretical and empirical asset pricing, Corporate finance, capital structure and dividend policy, Asset allocation and investment management, Financial crises, systemic risk and macro-finance, Quality of financial reporting and adoption of IFRS, Corporate governance, executive compensation and ownership structure, Computational finance and financial econometrics, Financial Econometrics, Financial risk analytics and management, Market microstructure and algorithmic trading, Financial policy choice, institutions and regulation, Financial Analytics, ESG, Climate Finance, Blended Finance, Insurance / Reinsurance / Pension Funds, Enhancing liquidity in commodity derivatives markets, Financial Literacy and Financial Education</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5th Conference in Sustainable Finance</t>
+          <t>Edinburgh Financial Technology Conference</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>University of Luxembourg</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3409,34 +3409,34 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>any topic in sustainable finance</t>
+          <t>The application of AI and Machine Learning in finance, The application of distributed ledger technologies in finance, Cryptofinance, Cyber risk in finance, The microstructure of modern financial markets (algorithmic/high frequency trading, dark trading, blockchain settlements etc.), Behavioural economics in financial technology, Alternative data (structured and unstructured datasets), Crowdsourcing and investment strategy, New exchange traded financial derivatives, Financial stability risks from the development of FinTech, RegTech, Open banking</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>7th CEAR-RSI Household Finance Workshop</t>
+          <t>5th Conference in Sustainable Finance</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>HEC Montréal</t>
+          <t>University of Luxembourg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3446,34 +3446,34 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Consumption-saving decisions and investment choices, Financial literacy and education, Pensions and retirement, Financial planning and advice, Financial delinquency and bankruptcy, Household insurance and risk management</t>
+          <t>Any topic in sustainable finance</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Next-Gen AI and Autonomous Finance (NGAI) workshop</t>
+          <t>7th CEAR-RSI Household Finance Workshop</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rennes School of Business, Rennes, France</t>
+          <t>HEC Montréal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3483,34 +3483,34 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Autonomous agents &amp; decision-making in finance, AI-driven trading, portfolio optimization &amp; market microstructure, Risk, robustness, and model governance (validation, monitoring, compliance), Ethics, fairness, transparency &amp; societal impacts of financial AI, Financial decision making and AI, Bias and stereotyping in relation to AI driven finance, AI, money and financial value formation</t>
+          <t>Consumption-saving decisions and investment choices, Financial literacy and education, Pensions and retirement, Financial planning and advice, Financial delinquency and bankruptcy, Household insurance and risk management</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>12th Annual ICGS Conference</t>
+          <t>Next-Gen AI and Autonomous Finance (NGAI) workshop</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HEC Montréal, Quebec, Canada</t>
+          <t>Rennes School of Business, Rennes, France</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3520,108 +3520,108 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Behavioral perspectives on governance, institutional and political approaches, implications of AI on governance mechanisms, evolving forms of activism, reconfiguration of governance systems, governance of state-firm relations</t>
+          <t>Autonomous agents &amp; decision-making in finance, AI-driven trading, portfolio optimization &amp; market microstructure, Risk, robustness, and model governance (validation, monitoring, compliance), Ethics, fairness, transparency &amp; societal impacts of financial AI, Financial decision making and AI, Bias and stereotyping in relation to AI driven finance, AI, money and financial value formation</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Vienna Festival of Finance Theory 2026</t>
+          <t>12th Annual ICGS Conference</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Vienna, Austria</t>
+          <t>HEC Montréal (Quebec, Canada)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>65 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Corporate finance theory and financial intermediation theory</t>
+          <t>Behavioral perspectives on executives, boards, investors, and other governance actors; Institutional and political approaches in governance; Implications of AI adoption for governance; Evolving forms of activism/engagement from investors and stakeholders; Reconfiguration of governance systems under geopolitical crises; Governance mechanisms for managing state-firm relations.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11th Cross Country Perspectives in Finance (CCPF) Conference</t>
+          <t>Vienna Festival of Finance Theory 2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>both online and on-site (Nanjing, China)</t>
+          <t>Vienna, Austria</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>65 EUR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>credit, banking, asset pricing, market liquidity, corporate finance, corporate governance, entrepreneurial finance in an international context</t>
+          <t>Corporate finance theory, financial intermediation theory</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Private Capital Symposium 2026</t>
+          <t>Cross Country Perspectives in Finance (CCPF) Conference</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>London Business School, London</t>
+          <t>both online and on-site (Nanjing, China)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3631,34 +3631,34 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Research on private equity, venture capital, and broader private market themes</t>
+          <t>credit, banking, asset pricing, market liquidity, corporate finance, corporate governance, entrepreneurial finance</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6th Annual Bristol Financial Markets Conference</t>
+          <t>Private Capital Symposium 2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bristol, UK</t>
+          <t>London Business School, London</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3668,34 +3668,34 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Skill, performance, and evaluation in delegated portfolio management; The rise of passive investment and its effects on financial markets; New developments and trends in delegation: ESG / thematic/private markets; Machine learning and AI in asset management; Textual analysis and news coverage in delegated investment decisions; The role of index providers in delegated portfolio management</t>
+          <t>Research on private equity, venture capital, and broader private market themes</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Inaugural CEIBS-APS Centre for Financial Markets (CAC) Academic Conference</t>
+          <t>6th Annual Bristol Financial Markets Conference</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>China Europe International Business School (CEIBS), Shanghai, China</t>
+          <t>Bristol, UK</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3705,34 +3705,34 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>asset pricing, macro-finance, impact of institutional features on capital market dynamics</t>
+          <t>Skill, performance, and evaluation in delegated portfolio management; The rise of passive investment and its effects on financial markets; New developments and trends in delegation: ESG / thematic/private markets; Machine learning and AI in asset management; Textual analysis and news coverage in delegated investment decisions; The role of index providers in delegated portfolio management</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Dauphine Finance PhD Workshop</t>
+          <t>Inaugural CEIBS-APS Centre for Financial Markets (CAC) Academic Conference</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>China Europe International Business School (CEIBS), Shanghai, China</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3742,34 +3742,34 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Papers in all areas of Finance and Financial Economics</t>
+          <t>Asset pricing, macro-finance, impact of institutional features on capital market dynamics</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>14th Helsinki Finance Summit on Investor Behavior</t>
+          <t>Dauphine Finance PhD Workshop</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Helsinki/Espoo, Finland</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3779,256 +3779,256 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Investor behavior, market microstructure, behavioral biases, household consumption, investor education, finance professionals' behavior, psychological foundations of investor behavior, influence of analysts and media, social influence in finance, impact on corporate policies</t>
+          <t>Papers in all areas of Finance and Financial Economics</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026 Clemson Finance Research Conference</t>
+          <t>14th Helsinki Finance Summit on Investor Behavior</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Clemson, SC</t>
+          <t>Helsinki/Espoo, Finland</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>corporate finance, asset pricing, investment, banking, asset management, household finance, labor economics, behavioral finance, Fintech, real estate</t>
+          <t>Investor behavior, behavior of different investor types, market microstructure and investor trading behavior, behavioral biases and performance of investment strategies, household consumption, borrowing, saving, and portfolio choice, investor education, financial literacy and sophistication, behavior of finance professionals and impact of professional advice, biological, psychological, and cultural foundations of investor behavior, influence of analysts, media, and news coverage on investment decisions, social influence and networks in finance, impact of investor behavior on corporate policies and decision-making</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Politics in Finance 2026 Conference</t>
+          <t>2026 Clemson Finance Research Conference</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>McDonough School of Business, Rafik B. Hariri Building 37th and O Streets, N.W Washington, D.C. 20057 USA</t>
+          <t>Clemson, SC</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>The role of political connections and political ideologies in shaping capital market forces, how political ideologies affect decision making by firms and workers, political connections and corruption in developing economies, the political economy of financial development, the interaction between government and financial institutions, implications of political uncertainty and political connections for asset prices and corporate policies, political economy of financial regulation and financial crises</t>
+          <t>corporate finance, asset pricing, investment, banking, asset management, household finance, labor economics, behavioral finance, Fintech, real estate</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>11th SDU Finance Workshop on Corporate Finance</t>
+          <t>Politics in Finance 2026 Conference</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU), Odense, Denmark</t>
+          <t>McDonough School of Business, Rafik B. Hariri Building 37th and O Streets, N.W Washington, D.C. 20057 USA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>300 DKK</t>
+          <t>$75</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Corporate Finance -- Dynamics, Uncertainty, and Strategic Decisions</t>
+          <t>The role of political connections and political ideologies in shaping capital market forces; How political ideologies affect the decision making by firms and workers; Political connections and corruption in developing economies; The political economy of financial development; The interaction between government and financial institutions; Implications of political uncertainty and political connections for asset prices and corporate policies; Political economy of financial regulation and financial crises</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Northern Finance Association 2026 Annual Meeting</t>
+          <t>11th SDU Finance Workshop on Corporate Finance</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Quebec City, Canada</t>
+          <t>University of Southern Denmark (SDU), Odense, Denmark</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Canadian $75</t>
+          <t>300 DKK (approx. 40 EUR)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Asset pricing, corporate finance, financial intermediation, investments, Canadian financial markets, insurance, household finance, sustainable finance, fintech, and AI</t>
+          <t>Corporate Finance -- Dynamics, Uncertainty, and Strategic Decisions</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>London Business School 2026 Summer Finance Symposium</t>
+          <t>Northern Finance Association 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>London Business School</t>
+          <t>Quebec City, Canada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>£50 GBP</t>
+          <t>Canadian $75 (about US $55)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Papers from all areas of finance</t>
+          <t>topics from all areas of finance including asset pricing, corporate finance, financial intermediation, investments, Canadian financial markets, insurance, household finance, sustainable finance, fintech, and AI</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF26)</t>
+          <t>London Business School 2026 Summer Finance Symposium</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>London Business School</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Climate Finance, Artificial Intelligence (AI) and Machine Learning in Finance and Accounting, Green Finance, Sustainable Finance, ESG Reporting, and Climate Risk, FinTech, Blockchain, and Digital Currencies, Corporate Governance and Technological Innovation, Big Data in Accounting and Finance, Green Accounting and Carbon Disclosure, RegTech and Financial Compliance, Data Analytics and Financial Decision-Making, Digital Transformation in Public Sector Accounting, Ethical Implications of AI and Automation in Financial Services, Evolving Accounting Standards in Response to Sustainability/Technology</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>11th International Conference on Accounting and Finance (ICOAF-2026)</t>
+          <t>Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF26)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Danang, Vietnam</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4038,34 +4038,34 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>All areas of Accounting, Finance, and Banking, encompassing both theoretical and empirical studies</t>
+          <t>Climate Finance, Artificial Intelligence (AI) and Machine Learning in Finance and Accounting, Green Finance, Sustainable Finance, ESG Reporting, and Climate Risk, FinTech, Blockchain, and Digital Currencies, Corporate Governance and Technological Innovation, Big Data in Accounting and Finance, Green Accounting and Carbon Disclosure, RegTech and Financial Compliance, Data Analytics and Financial Decision-Making, Digital Transformation in Public Sector Accounting, Ethical Implications of AI and Automation in Financial Services, Evolving Accounting Standards in Response to Sustainability/Technology</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Liechtenstein Workshop on AI in Finance 2026</t>
+          <t>11th International Conference on Accounting and Finance (ICOAF-2026)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Vaduz, Liechtenstein</t>
+          <t>Danang, Vietnam</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4075,34 +4075,34 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>forecasting financial variables with AI, asset allocation and asset management with AI, AI-based factor models, natural language processing and large language models in finance, AI applications in corporate finance</t>
+          <t>Accounting, Finance, Banking (theoretical and empirical studies)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>3rd Modern Finance Conference (MFC 2026)</t>
+          <t>Liechtenstein Workshop on AI in Finance 2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Krakow, Poland</t>
+          <t>Vaduz, Liechtenstein</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4112,182 +4112,182 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation, Banking and financial services, Behavioral finance and decision making, Capital structure, Corporate finance, Corporate governance, Cryptocurrencies, Derivatives, Economic development, Exchange rates and currency markets, Finance and accounting standards, Financial econometrics and quantitative methods, Financial markets and instruments, Financial, management, and tax accounting, Financial regulation and supervision, Financial stability, Fintech and financial innovation, Green finance, Investment and portfolio management, Insurance, Market microstructure, Mergers and acquisitions, Microfinance, Monetary policy and central banking, Risk management, Sustainable finance and responsible investment</t>
+          <t>forecasting financial variables with AI, asset allocation and asset management with AI, AI-based factor models, natural language processing and large language models in finance, and AI applications in corporate finance</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>The First University of Maryland/Singapore Management University/UBS Quant Investment Forum: AI and Finance</t>
+          <t>3rd Modern Finance Conference (MFC 2026)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Krakow, Poland</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>95 SGD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>AI for Investments &amp; Asset Pricing, Alternative Data and Investment Insights, Portfolio &amp; Risk Management, Algorithmic Trading &amp; Market Impact</t>
+          <t>Asset pricing and valuation, Banking and financial services, Behavioral finance and decision making, Capital structure, Corporate finance, Corporate governance, Cryptocurrencies, Derivatives, Economic development, Exchange rates and currency markets, Finance and accounting standards, Financial econometrics and quantitative methods, Financial markets and instruments, Financial, management, and tax accounting, Financial regulation and supervisions, Financial stability, Fintech and financial innovation, Green finance, Investment and portfolio management, Insurance, Market microstructure, Mergers and acquisitions, Microfinance, Monetary policy and central banking, Risk management, Sustainable finance and responsible investment</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026 City University of Hong Kong International Finance Conference</t>
+          <t>First University of Maryland/Singapore Management University/UBS Quant Investment Forum: AI and Finance</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>95 SGD</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Corporate Finance, Asset Pricing</t>
+          <t>AI for Investments &amp; Asset Pricing, Alternative Data and Investment Insights, Portfolio &amp; Risk Management, Algorithmic Trading &amp; Market Impact</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026 Research Summer Workshop on Regulated Funds and Retail-oriented Investment Products at the Investment Company Institute</t>
+          <t>2026 City University of Hong Kong International Finance Conference</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Washington, DC, USA</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Regulated funds, retail-oriented investment products, mutual fund industry</t>
+          <t>Corporate Finance, Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026 Vietnam Symposium in Entrepreneurship, Finance, and Innovation</t>
+          <t>2026 Research Summer Workshop on Regulated Funds and Retail-oriented Investment Products</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Washington, DC, USA</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>AI, Big Data, and Machine Learning Applications in Finance; Asset Pricing; Bankruptcy and Liquidation; Biodiversity Finance; Climate Finance; Corporate Finance and Governance; Corporate Responsibility and Sustainability; Crypto Assets, Blockchain, and Decentralized Finance; Electronic Markets, Trading Platforms, and Market Microstructure; ESG and Sustainable Finance; Financial Markets; Household Finance; Information Disclosure, Market Efficiency, and Transparency; Portfolio and Investment Decisions; FinTech, Alternative Finance, and Digital Financial Infrastructure; Tokenomics, Digital Currencies, and Payment Systems; Business Model Innovation and Corporate Digital Transformation; Digital Innovation, Knowledge Management, and Innovation Systems; Digital Human Resources and the Future of Work; Innovation Management and Growth Strategies; Innovation and Industrial Policy; Institutions, Regulation, and Innovation Systems; Science, R&amp;D, and the Economics of Knowledge Creation; Sustainability in the Digital Economy; Crowdfunding, Peer-to-Peer Lending, and Platform-Based Finance; Entrepreneurship, Intrapreneurship, and Innovation; Entrepreneurship in Emerging and Transition Markets; Family-Owned Businesses and Governance; Governance and Financing of High-Tech Firms; New Venture Creation and Performance; Social and Sustainable Entrepreneurship; Startups, SMEs, and Resource Allocation; Venture Financing and Entrepreneurial Growth</t>
+          <t>Regulated funds, retail-oriented investment products, mutual fund industry</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>12th IWH-FIN-FIRE Workshop on “Challenges to Financial Stability”</t>
+          <t>2026 Vietnam Symposium in Entrepreneurship, Finance, and Innovation</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Halle Institute for Economic Research (IWH), Halle/Saale Germany</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4297,88 +4297,88 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>regulation and financial intermediation, corporate finance, law, politics and finance, monetary policy, inflation and financial resilience, macroprudential policy and real estate, financial networks and systemic risk, pricing of climate risk in financial markets, ecological hazards and the behaviour of firms and households, governance of financial firms and markets, private credit and risk transfer</t>
+          <t>AI, Big Data, and Machine Learning Applications in Finance; Asset Pricing; Bankruptcy and Liquidation; Biodiversity Finance; Climate Finance; Corporate Finance and Governance; Corporate Responsibility and Sustainability; Crypto Assets, Blockchain, and Decentralized Finance; Electronic Markets, Trading Platforms, and Market Microstructure; ESG and Sustainable Finance; Financial Markets; Household Finance; Information Disclosure, Market Efficiency, and Transparency; Portfolio and Investment Decisions; FinTech, Alternative Finance, and Digital Financial Infrastructure; Tokenomics, Digital Currencies, and Payment Systems; Business Model Innovation and Corporate Digital Transformation; Digital Innovation, Knowledge Management, and Innovation Systems; Digital Human Resources and the Future of Work; Innovation Management and Growth Strategies; Innovation and Industrial Policy; Institutions, Regulation, and Innovation Systems; Science, R&amp;D, and the Economics of Knowledge Creation; Sustainability in the Digital Economy; Crowdfunding, Peer-to-Peer Lending, and Platform-Based Finance; Entrepreneurship, Intrapreneurship, and Innovation; Entrepreneurship in Emerging and Transition Markets; Family-Owned Businesses and Governance; Governance and Financing of High-Tech Firms; New Venture Creation and Performance; Social and Sustainable Entrepreneurship; Startups, SMEs, and Resource Allocation; Venture Financing and Entrepreneurial Growth</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bridging Theory and Empirical Research in Finance</t>
+          <t>12th IWH-FIN-FIRE Workshop on “Challenges to Financial Stability”</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Boston College</t>
+          <t>Halle/Saale, Germany</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>corporate finance, corporate governance, financial intermediation, agency and delegation, information and securities, financial markets</t>
+          <t>regulation and financial intermediation, corporate finance, law, politics and finance, monetary policy, inflation and financial resilience, macroprudential policy and real estate, financial networks and systemic risk, pricing of climate risk in financial markets, ecological hazards and the behaviour of firms and households, governance of financial firms and markets, private credit and risk transfer</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>11th Bank of Finland and European Systemic Risk Board Joint Conference on AI and Systemic Risk Analytics</t>
+          <t>Bridging Theory and Empirical Research in Finance</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bank of Finland, Helsinki</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Use of Large Language Models (LLM) and trustworthy AI, AI and changing interdependencies in the financial markets, Cyber security and operational risks as sources of systemic risk, AI and Quantum Computing as potential source of new systemic risks, Use of AI with big data for systemic risk analytics, Risks and opportunities stemming from disruptive innovations in financial technology (FinTech), Analysing emerging risks from interconnectedness of the financial system, Identifying risks from market-based finance, Modelling geopolitical risks, Using systemic risk analytics to support macro-prudential policy and regulation, Evidence of macroprudential policy measures</t>
+          <t>corporate finance, corporate governance, financial intermediation, agency and delegation, information and securities, financial markets</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Bank of Finland and CEPR Joint conference on Navigating Monetary Policy by the Northern Lights</t>
+          <t>11th Bank of Finland and European Systemic Risk Board Joint Conference on AI and Systemic Risk Analytics</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4388,17 +4388,17 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Saariselkä, Lapland</t>
+          <t>Bank of Finland, Helsinki</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4408,34 +4408,34 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Monetary Policy Transmission, Inflation Dynamics and Expectations; Heterogeneity in Macro and Monetary Economics Models; Monetary-Fiscal Interactions; Technological Advances, Financial Market Developments, and Central Banks; Geopolitical Shocks and Monetary Policy; Central bank credibility and independence</t>
+          <t>Use of Large Language Models (LLM) and trustworthy AI, AI and changing interdependencies in the financial markets, Cyber security and operational risks as sources of systemic risk, AI and Quantum Computing as potential source of new systemic risks, Use of AI with big data for systemic risk analytics, Risks and opportunities stemming from disruptive innovations in financial technology (FinTech), Analysing emerging risks from interconnectedness of the financial system, Identifying risks from market-based finance, Modelling geopolitical risks, Using systemic risk analytics to support macro-prudential policy and regulation, Evidence of macroprudential policy measures</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026 FIRN/UQ Asset Management Meeting</t>
+          <t>Bank of Finland and CEPR Joint conference on Navigating Monetary Policy by the Northern Lights</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Brisbane, Australia</t>
+          <t>Saariselkä, Lapland</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4445,34 +4445,34 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>asset management, FinTech, mutual funds, hedge funds, pension funds, ETFs, alternative investments, data assets/markets, digital finance, platform finance, financial technology, artificial intelligence, big data in asset management</t>
+          <t>Monetary Policy Transmission, Inflation Dynamics and Expectations; Heterogeneity in Macro and Monetary Economics Models; Monetary-Fiscal Interactions; Technological Advances, Financial Market Developments, and Central Banks; Geopolitical Shocks and Monetary Policy; Central bank credibility and independence</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>World Finance &amp; Banking Symposium</t>
+          <t>2026 FIRN/UQ Asset Management Meeting</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>University of Latvia, Riga</t>
+          <t>Brisbane, Australia</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4482,34 +4482,34 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>All areas of finance, economics, and banking</t>
+          <t>asset management, FinTech, mutual funds, hedge funds, pension funds, ETFs, alternative investments, data assets/markets, digital finance, platform finance, financial technology, artificial intelligence, big data in asset management</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Research Symposium on Finance and Economics (RSFE) 2026</t>
+          <t>World Finance &amp; Banking Symposium</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Krea University, Andhra Pradesh, India</t>
+          <t>University of Latvia, Riga</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4519,34 +4519,34 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Finance and Economics</t>
+          <t>All areas of finance, economics, and banking</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Annual Meeting of the Central Bank Research Association CEBRA</t>
+          <t>Research Symposium on Finance and Economics (RSFE) 2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>Krea University, Andhra Pradesh, India</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4556,108 +4556,108 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Monetary Policy Transmission, Expectations, and Communication; Inflation and Price Dynamics; Macro-Finance and Financial Stability; Fiscal–Monetary Interactions and Policy Making; International Macroeconomics, Trade, and Geoeconomics; Firms, Productivity, and the Real Economy; Data, Methods, and Artificial Intelligence</t>
+          <t>Finance and Economics</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>IBEFA Annual Meeting at the 2027 ASSA Conference</t>
+          <t>Annual Meeting of the Central Bank Research Association CEBRA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>US$100 per paper; US$75 for papers solely authored by PhD students</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>banking; financial risk measurement and management; non-bank financial intermediation and private credit; FinTech; the role of AI in financial intermediation; geo-economic fragmentation and capital flows; sustainable finance; household finance; financial market structure and regulation; monetary policy</t>
+          <t>Monetary Policy Transmission, Expectations, and Communication; Inflation and Price Dynamics; Macro-Finance and Financial Stability; Fiscal–Monetary Interactions and Policy Making; International Macroeconomics, Trade, and Geoeconomics; Firms, Productivity, and the Real Economy; Data, Methods, and Artificial Intelligence</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CSEF- CEPR Conference on Labor and Finance</t>
+          <t>IBEFA Annual Meeting at the 2027 ASSA Conference</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Villa Orlandi Conference Centre, University of Naples Federico II, Capri (Italy)</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>US$100 per paper; US$75 for papers solely authored by PhD students</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Interaction between financial and labor markets, technological innovation, job-skill matches, firms’ employment policies, role of employees in governance and financing of companies, responses of wages and employment to shocks, risk-sharing arrangements between firms and workers</t>
+          <t>banking; financial risk measurement and management; non-bank financial intermediation and private credit; FinTech; the role of AI in financial intermediation; geo-economic fragmentation and capital flows; sustainable finance; household finance; financial market structure and regulation; monetary policy</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Happy Valley Finance Conference</t>
+          <t>CSEF- CEPR Conference on Labor and Finance</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>Villa Orlandi Conference Centre, University of Naples Federico II, Capri (Italy)</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4667,14 +4667,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Interaction between financial and labor markets, technological innovation, job-skill matches, firms’ employment policies, role of employees in governance and financing of companies, responses of wages and employment to shocks, risk-sharing arrangements between firms and workers</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>3rd CEPR-SAFE Frankfurt Hub Conference of RPNs</t>
+          <t>Happy Valley Finance Conference</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4684,17 +4684,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>House of Finance, Campus Westend, Frankfurt, Germany</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4704,34 +4704,34 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Fintech and Financial Institutions, Regulatory framework revisions, CBDC blockchains, and stablecoins, Sovereign bonds and sovereign bond capital regulation, Payment systems and European sovereignty, Safe assets and exchange rate dynamics under world polarization, Private credit and financial stability, Climate regulation U-turn and implications for climate finance, Defence policy needs and European financial architecture</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Conference on The Industrial Organization of Financial Markets</t>
+          <t>3rd CEPR-SAFE Frankfurt Hub Conference of RPNs</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SKEMA Business School, Sophia Antipolis (Nice) campus, France</t>
+          <t>House of Finance, Campus Westend, Frankfurt, Germany</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4741,145 +4741,145 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>market structure and competition, innovation and strategic behavior in the organization of the financial markets, payment card industry, lending and digital banking, primary and secondary markets for equity, government debt and corporate debt, financial regulation and competition policy, interbank lending markets, retail funding markets, credit markets, including mortgages</t>
+          <t>Fintech and Financial Institutions, Regulatory framework revisions, CBDC blockchains, and stablecoins, Sovereign bonds and sovereign bond capital regulation, Payment systems and European sovereignty, Safe assets and exchange rate dynamics under world polarization, Private credit and financial stability, Climate regulation U-turn and implications for climate finance, Defence policy needs and European financial architecture</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Fourteenth Oxford Financial Intermediation Theory Conference (OxFIT)</t>
+          <t>Conference on The Industrial Organization of Financial Markets</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Saïd Business School, University of Oxford</t>
+          <t>SKEMA Business School, Sophia Antipolis (Nice) campus, France</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>£65 GBP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Financial crises, Governance of financial institutions, The role of central banks and regulators, Financial innovation, International regulatory coordination, Certification in financial markets</t>
+          <t>market structure and competition, innovation and strategic behavior in the organization of the financial markets, payment card industry, lending and digital banking, primary and secondary markets for equity, government debt and corporate debt, financial regulation and competition policy, interbank lending markets, retail funding markets, credit markets, including mortgages</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>University of Washington 7th Summer Finance Conference</t>
+          <t>Fourteenth Oxford Financial Intermediation Theory Conference (OxFIT)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Seattle, Washington</t>
+          <t>Saïd Business School, University of Oxford</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>USD $80 per paper</t>
+          <t>£65</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>All areas of finance, particularly submissions from junior faculty and preliminary papers</t>
+          <t>Financial crises, Governance of financial institutions, The role of central banks and regulators, Financial innovation, International regulatory coordination, Certification in financial markets</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4th Tilburg Finance Summit</t>
+          <t>University of Washington 7th Summer Finance Conference</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tilburg, Netherlands</t>
+          <t>Seattle, Washington | UW Foster School of Business</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD $80 per paper</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Asset pricing and behavioral finance</t>
+          <t>All areas of finance, particularly submissions from junior faculty and preliminary papers</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026 PHBS–IER conference on “Technology, Innovation, Platforms, and Economic Performance”</t>
+          <t>4th Tilburg Finance Summit</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School, Shenzhen, China</t>
+          <t>Tilburg, Netherlands</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4889,34 +4889,34 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Innovation, Technology Emergence, and Technology Transfer; Technology Adoption, Diffusion, and Automation; Resource Reallocation, Productivity, and Aggregate Dynamics; Geoeconomics and Technology Policy: Fragmentation, Trade, and Innovation; Trading Platforms and Digital Markets: Design, Competition, and Information; Institutions, Finance, Digital Payments, and Regulation in the Digital Economy</t>
+          <t>Asset Pricing, Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>7th Canadian Sustainable Finance Network Conference</t>
+          <t>2026 PHBS–IER conference on “Technology, Innovation, Platforms, and Economic Performance”</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Alberta School of Business, University of Alberta, Edmonton, Canada</t>
+          <t>Peking University HSBC Business School, Shenzhen, China</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4926,14 +4926,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>sustainable finance and the intersection of corporate governance and sustainability</t>
+          <t>Innovation, Technology Emergence, and Technology Transfer; Technology Adoption, Diffusion, and Automation; Resource Reallocation, Productivity, and Aggregate Dynamics; Geoeconomics and Technology Policy: Fragmentation, Trade, and Innovation; Trading Platforms and Digital Markets: Design, Competition, and Information; Institutions, Finance, Digital Payments, and Regulation in the Digital Economy</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026 Global Finance Conference</t>
+          <t>7th Canadian Sustainable Finance Network Conference</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4943,17 +4943,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>University of Azores, Portugal</t>
+          <t>Alberta School of Business, University of Alberta, Edmonton, Canada</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4963,219 +4963,219 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Energy, Sustainability, Fintech including AI, Climate change, Alternative Investments, Asset &amp; Wealth Management, Asset Allocation/Sovereign Funds/Hedge Funds/ETFs/SWFs, Banking &amp; Financial Services, Corporate Governance/Executive Compensation, Country Risk/Debt Issues/Insurance/Reinsurance, Derivatives/Financial Engineering, E-Business/E-Finance/Social Media, Emerging Markets/BRICS, Entrepreneurship/Venture Capital Global Perspectives, Ethics/Legal/Regulatory, Accounting, Auditing and Taxation Issues, Financial Crises and Bubbles, Financial Technology including AI, ML &amp; Financial Information Systems, Foreign Currency Issues, Future of Global Economy, Global Trade Issues, IPOs/SEOs/Stock buybacks/Privatization, Market Behavior Efficiency/Inefficiency, Mergers and Acquisitions, Non-Traditional Banking &amp; Financial Services, Portfolio Flows and Foreign Direct Investment, Private Equity, Real estate, Valuation, Portfolio Management and Managing Financial Risk</t>
+          <t>sustainable finance, corporate governance, sustainability</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Bayes Junior Asset Management and Asset Pricing Workshop</t>
+          <t>2026 Global Finance Conference</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bayes Business School, London</t>
+          <t>University of Azores, Portugal</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>£50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>asset management, asset pricing, papers that bridge asset management and asset pricing</t>
+          <t>Energy, Sustainability, Fintech including AI, Climate change, Alternative Investments, Asset &amp; Wealth Management, Asset Allocation, Sovereign Funds, Hedge Funds, ETFs, SWFs, Banking &amp; Financial Services, Corporate Governance, Executive Compensation, Country Risk, Debt Issues, Insurance, Reinsurance, Derivatives, Financial Engineering, E-Business, E-Finance, Social Media, Emerging Markets, Entrepreneurship, Venture Capital, Ethics, Legal, Regulatory Issues, Financial Crises, Financial Technology, Foreign Currency Issues, Future of Global Economy, Global Trade Issues, IPOs, SEOs, Stock Buybacks, Mergers and Acquisitions, Non-Traditional Banking, Portfolio Flows, Private Equity, Real Estate, Valuation, Portfolio Management, and Managing Financial Risk.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Second Annual Notre Dame Investment Management Conference</t>
+          <t>Bayes Junior Asset Management and Asset Pricing Workshop</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>University of Notre Dame, Notre Dame, Indiana</t>
+          <t>Bayes Business School, London</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>70 USD</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Asset pricing, financial intermediation, investments, demand based asset pricing, inelastic markets hypothesis, new methods in asset pricing (machine learning, AI, unstructured data), time series and cross-sectional predictability, portfolio allocation for long term investors, retirement decisions and choices, behavioral finance</t>
+          <t>Asset management, Asset pricing, Papers that bridge asset management and asset pricing</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Future Finance Fest (3f)</t>
+          <t>Second Annual Notre Dame Investment Management Conference</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>University of Notre Dame - Notre Dame, Indiana</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>0 EUR</t>
+          <t>70 USD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>AI, asset pricing, banking, behavioral finance, big data, blockchain, CBDCs, compliance, crowdfunding, cryptocurrencies, cybersecurity, decentralized finance, digital finance, embedded finance, fintech, financial infrastructure, financial inclusion, financial innovation, financial intermediation, financial markets, household finance, insurtech, machine learning, market microstructure, payments, platforms, regulation, risk management, stablecoins, tokenization, text analytics.</t>
+          <t>Asset pricing, financial intermediation, investments, Demand Based Asset Pricing, Inelastic Markets Hypothesis, New Methods in Asset Pricing (Machine Learning, AI, unstructured data), Time series and Cross-Sectional Predictability, Portfolio Allocation for Long Term Investors, Retirement decisions and choices, Behavioral finance</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026 FMA Applied Finance Conference</t>
+          <t>Future Finance Fest (3f)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>St. John's University - Manhattan Campus, New York, NY</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>$50 USD (FMA-members) and $60 USD (non-members)</t>
+          <t>0 EUR</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Inform practice and advance the frontiers of academic research in directions relevant to practice; Address issues that are relevant to contemporary issues globally and for policy formation and assessment; Introduce new hypotheses that have the potential to stimulate additional research</t>
+          <t>AI, asset pricing, banking, behavioral finance, big data, blockchain, CBDCs, compliance, crowdfunding, cryptocurrencies, cybersecurity, decentralized finance, digital finance, embedded finance, fintech, financial infrastructure, financial inclusion, financial innovation, financial intermediation, financial markets, household finance, insurtech, machine learning, market microstructure, payments, platforms, regulation, risk management, stablecoins, tokenization, text analytics</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Exeter Sustainable Finance Conference 2026</t>
+          <t>2026 FMA Applied Finance Conference</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>University of Exeter Business School, Exeter, UK</t>
+          <t>St. John's University - Manhattan Campus, New York, NY</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD (FMA-members) / $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Unpublished research papers on any topic related to sustainable finance, interdisciplinary research</t>
+          <t>High-quality papers in the fields of finance and accounting that inform practice, advance academic research, address contemporary global issues, and introduce new hypotheses.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>9th Cryptocurrency Research Conference (CRC2026)</t>
+          <t>Exeter Sustainable Finance Conference 2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>University of Exeter Business School, Exeter, UK</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -5185,219 +5185,219 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cryptofinance, blockchain economics, digital finance, cryptocurrencies, financial economics, FinTech, AI for finance</t>
+          <t>Sustainable finance, interdisciplinary research</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Accountability in a Sustainable World Conference</t>
+          <t>9th Cryptocurrency Research Conference (CRC2026)</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>$200 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Non-academic-friendly summaries of research, pressing questions informed by academic research, sustainability issues</t>
+          <t>Cryptofinance, cryptocurrencies, digital finance, blockchain economics, AI for finance, corporate finance, alternative investments</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>33rd Finance Forum</t>
+          <t>Accountability in a Sustainable World Conference</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Alicante, Spain</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>50 €</t>
+          <t>$200 USD</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance, Banking, Portfolio Choice and Asset Management, Microstructure, Regulation, Financial Stability, Macrofinance</t>
+          <t>Non-academic-friendly summaries of research, pressing questions informed by academic research, sustainability issues</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3rd Workshop on Recent Trends and New Developments in Sustainable, Green and International Finance</t>
+          <t>33rd Finance Forum</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>EDHEC Business School, Nice Campus, Nice, France</t>
+          <t>Alicante, Spain</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>220 EUR (academics and professionals), 180 EUR (Ph.D. students)</t>
+          <t>50 €</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sustainable finance, green finance, climate finance, international finance</t>
+          <t>Asset Pricing, Corporate Finance, Banking, Portfolio Choice and Asset Management, Microstructure, Regulation, Financial Stability, Macrofinance</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Alpine Finance Summit (AFS) 2026</t>
+          <t>3rd Workshop on Recent Trends and New Developments in Sustainable, Green and International Finance</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Garmisch-Partenkirchen, Germany</t>
+          <t>EDHEC Business School, Nice Campus, Nice, France</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>50 EUR</t>
+          <t>220 EUR (academics and professionals), 180 EUR (Ph.D. students)</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Asset Pricing, Investments, Sustainable Finance, FinTech</t>
+          <t>sustainable finance, green finance, climate finance, international finance</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>The 22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
+          <t>Alpine Finance Summit (AFS) 2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Park Hyatt Busan, Busan, Korea</t>
+          <t>Garmisch-Partenkirchen, Germany</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 EUR</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
+          <t>Asset Pricing, Investments, Sustainable Finance, FinTech</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NBER-SAIF Conference on AI and Financial Markets</t>
+          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Busan, Korea</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5407,34 +5407,34 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>The impact of investment in AI and supporting technologies on corporate earnings and share prices, the effects of AI on portfolio choices and trading behavior of financial market participants, the role of AI in creating new measures of economic activity, the uses of AI in financial market regulation, consequences of AI for the financial advice industry, macroeconomic effects of AI on economy-wide discount rates</t>
+          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>12th Workshop on Banking and Institutions</t>
+          <t>NBER-SAIF Conference on AI and Financial Markets</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Bank of Finland, Helsinki</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5444,34 +5444,34 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>geopolitics and banking, political economy of banking, banking and society, banking in emerging markets, climate and banking, monetary policy and institutions</t>
+          <t>The impact of investment in AI and supporting technologies on corporate earnings and share prices; the effects of AI on portfolio choices and trading behavior; the role of AI in creating new measures of economic activity; the uses of AI in financial market regulation; the consequences of AI for the financial advice industry; the macroeconomic effects of AI on economy-wide discount rates</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ENTFIN 2026 Conference</t>
+          <t>12th Workshop on Banking and Institutions</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kedge Business School, Marseille, France</t>
+          <t>Bank of Finland, Helsinki</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5481,71 +5481,71 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Venture capital; private equity; Business angels and early-stage financing; Crowdfunding; token offerings and digital finance; Entrepreneurial banking and credit relationships; Corporate governance; contracts and monitoring; Financial innovation; FinTech; AI in entrepreneurial finance; ESG; sustainability; impact finance; Entrepreneurial ecosystems; regional financing gaps; Entrepreneurial risk-taking; behavioral finance; Impact assessment for publicly supported financial instruments</t>
+          <t>geopolitics and banking, political economy of banking, banking and society, banking in emerging markets, climate and banking, monetary policy and institutions</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>9th Short-Term Funding Markets Conference</t>
+          <t>ENTFIN 2026 Conference</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Federal Reserve Board, Washington, D.C.</t>
+          <t>Kedge Business School, Marseille, France</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>450 euros</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Maturity and liquidity transformation, Repo markets, Theories of frictions and fragility in short-term funding markets, Effects of regulation and central bank intervention, Securities lending, Money creation and the demand for safe assets, Fintech and encrypted currency</t>
+          <t>Venture capital; private equity and buyouts; Business angels and early-stage financing; Crowdfunding; token offerings and digital finance; Entrepreneurial banking and credit relationships; Corporate governance, contracts, and monitoring; Financial innovation; FinTech and AI in entrepreneurial finance; ESG, sustainability, and impact finance; Entrepreneurial ecosystems and regional financing gaps; Entrepreneurial risk-taking and behavioral finance; Impact assessment for publicly supported financial instruments and their real effects and societal outcomes.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>21st Central Bank Conference on the Microstructure of Financial Markets</t>
+          <t>9th Short-Term Funding Markets Conference</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Eltville am Rhein, Germany</t>
+          <t>Federal Reserve Board, Washington, D.C.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5555,34 +5555,34 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Artificial intelligence and market microstructure, The functioning and resilience of sovereign bond and repo markets</t>
+          <t>Maturity and liquidity transformation by banks, broker-dealers, money market mutual funds, and other financial intermediaries; Repo markets and their clearing institutions; Theories of frictions and fragility in short-term funding markets; Effects of regulation and central bank intervention on funding markets; Securities lending; Money creation and the demand for safe assets; Fintech and encrypted currency</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026 PRIVATE EQUITY RESEARCH CONSORTIUM (PERC) EUROPE SYMPOSIUM</t>
+          <t>21st Central Bank Conference on the Microstructure of Financial Markets</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Oxford, England</t>
+          <t>Eltville am Rhein, Germany</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5592,219 +5592,219 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
+          <t>Artificial intelligence and market microstructure, The functioning and resilience of sovereign bond and repo markets</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Lake District Workshop in Corporate Finance</t>
+          <t>2026 PRIVATE EQUITY RESEARCH CONSORTIUM (PERC) EUROPE SYMPOSIUM</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Windermere, Lake District, United Kingdom</t>
+          <t>Oxford, England</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>£60 GBP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>Buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>8th Annual Workshop on Financial Institutions Research</t>
+          <t>Lake District Workshop in Corporate Finance</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Gateway Conference Center, Federal Reserve Bank of St. Louis; St. Louis, MO USA</t>
+          <t>Windermere, Lake District, United Kingdom</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£60 GBP</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Bank Regulation, Supervision, and Compliance; Bank Risk-taking, Stability, and Financial Crises; Lending and Credit Allocation; Bank Governance, Ownership, and Compensation; Bank Disclosure, Accounting, and the Information Environment; Deposits, Funding Structure, and Liability Management; Financial Technology, Innovation, and Bank Competition</t>
+          <t>Corporate Finance, including mergers and acquisitions, corporate governance, and financial institutions</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Southern Finance Association 2026 Annual Meeting</t>
+          <t>8th Annual Workshop on Financial Institutions Research</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>LaQuinta Resort, Palm Springs, CA</t>
+          <t>Gateway Conference Center, Federal Reserve Bank of St. Louis; St. Louis, MO USA</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Papers on any area of finance, proposals for panel discussions, special sessions, or tutorials</t>
+          <t>Bank Regulation, Supervision, and Compliance; Bank Risk-taking, Stability, and Financial Crises; Lending and Credit Allocation; Bank Governance, Ownership, and Compensation; Bank Disclosure, Accounting, and the Information Environment; Deposits, Funding Structure, and Liability Management; Financial Technology, Innovation, and Bank Competition</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>International Accounting &amp; Finance Doctoral Symposium (IAFDS)</t>
+          <t>Southern Finance Association 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cagliari, Sardinia, Italy</t>
+          <t>LaQuinta Resort, Palm Springs, CA</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>£300</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Original empirical and theoretical papers in accounting and finance (including banking), focusing on significant and impactful issues within these fields</t>
+          <t>Papers on any area of finance, panel discussions, special sessions, tutorials</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>13th Annual Conference on Risk Governance</t>
+          <t>International Accounting &amp; Finance Doctoral Symposium (IAFDS)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Board-level decision-making in dynamic environments</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>- Risk Governance and the monitoring role of supervisory boards</t>
+          <t>Cagliari, Sardinia, Italy</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>- Stakeholder influence and external pressure on board-level decision-making</t>
+          <t>£300</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>- Risk Governance in the boardroom: How directors navigate uncertainty</t>
+          <t>Original empirical and theoretical papers in accounting and finance, including banking, with a focus on significant and impactful issues within these fields</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SHoF Annual Conference on the Future of Private Capital Markets</t>
+          <t>13th Annual Conference on Risk Governance</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>University of Siegen, Siegen/Germany</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5814,34 +5814,34 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Private equity and private credit market structure, Private capital strategies and performance, The interaction between private and public capital markets, Private capital and corporate investment, productivity, and innovation, Structured lending within the private market, Fund organization, governance, and incentives, Financing of infrastructure and energy transition, Risk-taking and financial stability implications, The role of private capital in downturns and periods of financial stress, Regulatory and policy implications of the growth of private markets, ESG, sustainability, and impact in private capital markets</t>
+          <t>Risk Governance in the boardroom, Risk Governance and the monitoring role of supervisory boards, Balancing risk and opportunity, Stakeholder influence on decision-making, Sustainability and Risk Governance, Understanding black swans in decision-making, Strategic resilience, Risk strategies on bank boards, Tackling digitalization-related risks, Role of artificial intelligence in decisions, Machine learning in decision-making</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CU Denver 9th Annual J.P. Morgan Center International Commodities Symposium</t>
+          <t>SHoF Annual Conference on the Future of Private Capital Markets</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5851,219 +5851,219 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Recent developments in commodity business, energy, metals and minerals, agriculture, commodity futures, derivatives, and related research topics</t>
+          <t>Private equity and private credit market structure, Private capital strategies and performance, The interaction between private and public capital markets, Private capital and corporate investment, productivity, and innovation, Structured lending within the private market, Fund organization, governance, and incentives, Financing of infrastructure and energy transition, Risk-taking and financial stability implications, The role of private capital in downturns and periods of financial stress, Regulatory and policy implications of the growth of private markets, ESG, sustainability, and impact in private capital markets</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Bocconi-Bristol Second Sustainability and Green Finance Research Workshop</t>
+          <t>9th Annual J.P. Morgan Center International Commodities Symposium</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bocconi University, Milan (Italy)</t>
+          <t>Denver, CO</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>0 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>New Global Challenges: Climate Change, Biodiversity Loss, and Geopolitical Risk</t>
+          <t>Commodity business, energy, metals and minerals, agriculture, commodity futures, derivatives</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Alliance for Research on Corporate Sustainability (ARCS) 18th Annual Research Conference</t>
+          <t>Bocconi-Bristol Second Sustainability and Green Finance Research Workshop</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Nanyang Business School, Nanyang Technological University (Singapore)</t>
+          <t>Bocconi University, Milan (Italy)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 EUR</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Climate change/risk management, decarbonization challenges and opportunities, technology/AI-driven sustainability solutions, corporate impacts on biodiversity and nature-based business solutions, sustainability reporting and disclosure, sustainable/responsible supply chains, sustainable finance, green marketing, green entrepreneurship, renewable energy investments, cleantech innovation, sustainable natural resource management, business/NGO partnerships, sustainable mobility, social dimensions of sustainability such as inequality, fair wages and working conditions, social and environmental justice, cross-border impacts of geopolitical and regulatory dynamics, and “base of the pyramid” (BoP) development strategies.</t>
+          <t>New Global Challenges: Climate Change, Biodiversity Loss, and Geopolitical Risk</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Finance Research Revolution Conference</t>
+          <t>Alliance for Research on Corporate Sustainability (ARCS) 18th Annual Research Conference</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Weggis, Switzerland</t>
+          <t>Nanyang Business School, Nanyang Technological University (Singapore)</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CHF 75 per paper</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Machine learning for the cross-section of returns, Big data analysis, Large language models and unstructured data, Non-standard datasets for return predictions, Systematic expectations mistakes and predictable returns, Feasible and implementable portfolios, Predictable turning points</t>
+          <t>Climate change/risk management, decarbonization challenges and opportunities, technology/AI-driven sustainability solutions, corporate impacts on biodiversity and nature-based business solutions, sustainability reporting and disclosure, sustainable/responsible supply chains, sustainable finance, green marketing, green entrepreneurship, renewable energy investments, cleantech innovation, sustainable natural resource management, business/NGO partnerships, sustainable mobility, social dimensions of sustainability such as inequality, fair wages and working conditions, social and environmental justice, cross-border impacts of geopolitical and regulatory dynamics, and “base of the pyramid” (BoP) development strategies.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026 FMA European Conference</t>
+          <t>Finance Research Revolution Conference</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Braga, Portugal</t>
+          <t>Weggis, Switzerland</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>$75 USD (FMA-members) and $85 USD (non-members)</t>
+          <t>CHF 75 per paper</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Machine learning for the cross-section of returns, Big data analysis, Large language models and unstructured data, Non-standard datasets for return predictions, Systematic expectations mistakes and predictable returns, Feasible and implementable portfolios, Predictable turning points</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>40th Annual Mitsui Symposium: Private Capital Markets</t>
+          <t>2026 FMA European Conference</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Ann Arbor, Michigan</t>
+          <t>Braga, Portugal</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD (FMA-members) and $85 USD (non-members)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Technology and Private Markets, Private Markets and Real Economic Outcomes, Access to and Democratization of Private Markets, Private Equity and Venture Capital, Private Credit and Direct Lending, Private Real Assets, Entrepreneurship and Innovation</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Third Chicago Booth Treasury Markets Conference</t>
+          <t>40th Annual Mitsui Symposium: Private Capital Markets</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Chicago, Illinois</t>
+          <t>Ann Arbor, Michigan</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6073,182 +6073,182 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Debt sustainability and public finance, Interactions between monetary and fiscal policy, The international role of U.S. Treasuries and the U.S. dollar, Market structure and fragilities in Treasury markets, Treasury basis trades and leveraged intermediation, Interactions between funding markets and Treasury markets, Liquidity provision, market-making capacity, and regulatory constraints, Financial stability implications of Treasury market dynamics</t>
+          <t>Technology and Private Markets, Private Markets and Real Economic Outcomes, Access to and Democratization of Private Markets, Private Equity and Venture Capital, Private Credit and Direct Lending, Private Real Assets, Entrepreneurship and Innovation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Cambridge Corporate Finance Theory Symposium 2026</t>
+          <t>Third Chicago Booth Treasury Markets Conference</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cambridge, UK</t>
+          <t>Chicago, Illinois</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>£50 GBP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Theoretical corporate finance, banking, market micro-structure, asset pricing, financial accounting</t>
+          <t>Debt sustainability and public finance, Interactions between monetary and fiscal policy, The international role of U.S. Treasuries and the U.S. dollar, Market structure and fragilities in Treasury markets, Treasury basis trades and leveraged intermediation, Interactions between funding markets and Treasury markets, Liquidity provision, market-making capacity, and regulatory constraints, Financial stability implications of Treasury market dynamics</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Fifth Annual Conference on Financial Markets</t>
+          <t>Cambridge Corporate Finance Theory Symposium 2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>UCLA Anderson, Los Angeles, CA</t>
+          <t>Cambridge, UK</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£50 GBP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Financial markets</t>
+          <t>Theoretical corporate finance, banking, market micro-structure, asset pricing, financial accounting</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026 Global Entrepreneurship and Innovation Research Conference (GEIRC)</t>
+          <t>Fifth Annual Conference on Financial Markets</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Cambridge, United Kingdom</t>
+          <t>UCLA Anderson, Los Angeles, CA</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>$200 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Entrepreneurship and innovation, Scaling frontier technologies, Industrial policy and innovation, University-industry collaboration, Global innovation networks, Innovation finance, and Universities, governments, and policy in the new geopolitical era.</t>
+          <t>Financial markets</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>5th Annual Hong Kong Conference on FinTech and AI in Finance</t>
+          <t>2026 Global Entrepreneurship and Innovation Research Conference (GEIRC)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Hong Kong SAR</t>
+          <t>Cambridge, United Kingdom</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>200 USD</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Empirical finance with AI and Big Data applications, New empirical method development in machine learning and financial econometrics, Blockchain technology, digital assets, and frontier FinTech topics</t>
+          <t>Entrepreneurship and innovation, Scaling frontier technologies, Industrial policy and innovation, University-industry collaboration, Global innovation networks, Innovation finance, Universities, governments, and policy in the new geopolitical era</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026 Annual International Journal of Central Banking Research Conference</t>
+          <t>5th Annual Hong Kong Conference on FinTech and AI in Finance</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Swiss National Bank, Bern</t>
+          <t>Hong Kong SAR</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -6258,34 +6258,34 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>New Technologies and Their Implications for Monetary Policy and Financial Stability, AI and automation impact on inflation dynamics, risks to financial stability from technological developments, central banks' adaptation in an AI/automation driven economy, transformation of financial markets, macroprudential supervision risks and opportunities, effects on monetary policy transmission mechanism, AI optimization of monetary policy decision making</t>
+          <t>(1) Empirical finance with AI and Big Data applications (e.g., alternative data) (2) New empirical method development in machine learning and financial econometrics (3) Blockchain technology, digital assets, and frontier FinTech topics</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Research in Behavioral Finance Conference 2026</t>
+          <t>2026 Annual International Journal of Central Banking Research Conference</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Amsterdam, the Netherlands</t>
+          <t>Swiss National Bank, Bern</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6295,34 +6295,34 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>All aspects of behavioral finance, including financial behavior of individuals, groups, organizations, market dynamics, and intersections of these areas</t>
+          <t>New Technologies and Their Implications for Monetary Policy and Financial Stability, AI and automation impact on inflation dynamics, risks to financial stability from technological developments, adaptation of central banks' toolkits, transformation of financial markets, macroprudential supervision, monetary policy transmission mechanism, optimization of monetary policy decision-making using AI</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>9th Annual GRASFI Conference</t>
+          <t>Research in Behavioral Finance Conference 2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Liège, Belgium</t>
+          <t>Amsterdam, the Netherlands</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6332,34 +6332,34 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Sustainable Finance</t>
+          <t>All aspects of behavioral finance, including financial behavior of individuals, groups, and organizations, market dynamics, and intersection of these areas</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Red Rock Finance Conference 2026</t>
+          <t>9th Annual GRASFI Conference</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Zion National Park</t>
+          <t>Liège, Belgium</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6369,182 +6369,182 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Any topic related to finance</t>
+          <t>Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Inaugural Rutgers Finance Research Conference</t>
+          <t>Red Rock Finance Conference 2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rutgers Business School – Newark &amp; New Brunswick, NJ</t>
+          <t>Zion National Park</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Innovative research across all areas of finance</t>
+          <t>Any topic related to finance</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AI in Finance Conference</t>
+          <t>Inaugural Rutgers Finance Research Conference</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Washington, DC, USA</t>
+          <t>Rutgers Business School – Newark &amp; New Brunswick, NJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Uses of AI by firms in corporate finance, AI in trading and asset management, AI use by banks, AI for financial forecasting, AI in understanding consumer financial behavior, labor replacement vs. augmentation, financial market implications of AI use, financial stability and disparities, frictions in AI adoption and regulatory solutions</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026 UNSW Corporate Finance Workshop</t>
+          <t>AI in Finance Conference</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Coogee Beach (Sydney, Australia)</t>
+          <t>Washington, DC, USA</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>All areas of Finance with a special focus on Corporate Finance, including banking, household and entrepreneurial finance</t>
+          <t>Uses of AI by firms in corporate finance, AI use in trading and asset management, AI use by banks and other credit providers, AI use in financial forecasting, AI use for understanding consumer financial behavior, AI and labor replacement vs. augmentation, Financial market and macroeconomic implications of AI use, AI, financial stability, and disparities, Frictions and market failures in AI adoption/use and regulatory solutions</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>9th Bristol Workshop on Banking and Financial Intermediation</t>
+          <t>2026 UNSW Corporate Finance Workshop</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>University of Bristol, Bristol UK</t>
+          <t>Coogee Beach (Sydney, Australia)</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>theoretical and empirical papers in banking and financial intermediation</t>
+          <t>All areas of Finance with a special focus on Corporate Finance, including banking, household and entrepreneurial finance</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CCA-ESCP Workshop on Financial Institutions and Corporate Finance</t>
+          <t>9th Bristol Workshop on Banking and Financial Intermediation</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>ESCP Business School - Turin Campus</t>
+          <t>University of Bristol, Bristol UK</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6554,34 +6554,34 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Interactions among banks, non-bank intermediaries, and capital markets; Effects of technological innovation — including digital banking, fintech, big data, and AI; Consequences of bank regulatory and supervisory reforms; Determinants of financial fragility, liquidity transformation, and systemic risk; Climate, sustainability, and transition finance; Corporate investment, capital structure, and liquidity management; Governance, ownership structures, incentives, and diversity; Monetary-policy transmission through banks and non-banks; Household and entrepreneurial finance; Impacts of geopolitical, political-economy, and policy shocks in finance</t>
+          <t>Theoretical and empirical papers in banking and financial intermediation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Boulder Summer Conference on Consumer Financial Decision Making</t>
+          <t>CCA-ESCP Workshop on Financial Institutions and Corporate Finance</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Boulder, Colorado (St. Julien Hotel and Spa)</t>
+          <t>ESCP Business School - Turin Campus</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6591,182 +6591,182 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Financial behavior, consumer decision-making</t>
+          <t>Interactions among banks, non-bank intermediaries, and capital markets; Effects of technological innovation; Consequences of bank regulatory and supervisory reforms; Determinants of financial fragility, liquidity transformation, and systemic risk; Climate, sustainability, and transition finance; Corporate investment, capital structure, and liquidity management; Governance, ownership structures, incentives, and diversity; Monetary-policy transmission through banks and non-banks; Household and entrepreneurial finance; Impacts of geopolitical, political-economy, and policy shocks in finance</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Oxford Saïd - VU SBE Macro-finance Conference</t>
+          <t>Boulder Summer Conference on Consumer Financial Decision Making</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Saïd Business School, University of Oxford</t>
+          <t>Boulder, Colorado (St. Julien Hotel and Spa)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>₤45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Monetary policy, macroprudential policy, and fiscal policy; Credit, banks, bankruptcy and systemic risks; International finance, exchange rates, sovereign debt, and debt sustainability; Climate risks and macro-financial implications</t>
+          <t>Financial behavior and consumer decision-making</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Labor &amp; Finance Group Spring 2026 Conference</t>
+          <t>Oxford Saïd - VU SBE Macro-finance Conference</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Vanderbilt University - Owen Graduate School of Management, Nashville, TN</t>
+          <t>Saïd Business School, University of Oxford</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>₤45</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
+          <t>Monetary policy, macroprudential policy, and fiscal policy; Credit, banks, bankruptcy and systemic risks; International finance, exchange rates, sovereign debt, and debt sustainability; Climate risks and macro-financial implications</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CEPR 11th European Workshop on Household Finance</t>
+          <t>Labor &amp; Finance Group Spring 2026 Conference</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Deutsche Bundesbank Training Centre at Eltville am Rhein</t>
+          <t>Vanderbilt University - Owen Graduate School of Management, Nashville, TN</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>50 euro</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Patterns of asset allocation and debt behaviour over the life cycle, Financing retirement and the demographic transition, Consumer indebtedness, financial distress and default decisions, Behavioural approaches to household finances, Financial literacy and financial education programmes, Trust, subjective expectations, pessimism, and financial decisions, International comparisons of household finances using micro-data, Cognitive and genetic studies on individual financial performance, Financial advice and legal protection of investors and borrowers, The impact of technology on household financial behaviour</t>
+          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>The 10th Vietnam International Conference in Finance</t>
+          <t>CEPR 11th European Workshop on Household Finance</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Deutsche Bundesbank Training Centre at Eltville am Rhein</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 euro</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Corporate finance and governance, Asset pricing, investment, and portfolio management, Finance and sustainability, Financial markets and institutions, Financial technology, artificial intelligence, and big data, Banking and financial regulations, Behavioral finance, Risk management and quantitative finance, Household finance and financial consumer protection</t>
+          <t>Patterns of asset allocation and debt behaviour over the life cycle, Financing retirement and the demographic transition, Consumer indebtedness, financial distress and default decisions, Behavioural approaches to household finances, Financial literacy and financial education programmes, Trust, subjective expectations, pessimism, and financial decisions, International comparisons of household finances using micro-data, Cognitive and genetic studies on individual financial performance, Financial advice and legal protection of investors and borrowers, The impact of technology on household financial behaviour</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Inaugural Rutgers Finance Research Conference</t>
+          <t>10th Vietnam International Conference in Finance</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Rutgers Business School - Newark, NJ</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6776,34 +6776,34 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>innovative research across all areas of finance</t>
+          <t>Corporate finance and governance, Asset pricing, investment, and portfolio management, Finance and sustainability, Financial markets and institutions, Financial technology, artificial intelligence, and big data, Banking and financial regulations, Behavioral finance, Risk management and quantitative finance, Household finance and financial consumer protection</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2nd EDHEC AI and Finance Workshop</t>
+          <t>Inaugural Rutgers Finance Research Conference</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>EDHEC Business School, Nice, France</t>
+          <t>Rutgers Business School - Newark, NJ</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6813,34 +6813,34 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>NLP &amp; large language models; Speech and multimedia analysis; AI agents &amp; automation; Machine learning &amp; predictive analytics; Big data &amp; computational methods; The role of AI in corporate decision-making and other aspects of financial and labor markets; Ethics, policy, and regulation</t>
+          <t>all areas of finance, financial economics</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Journal of International Money and Finance Special Issue and Conference</t>
+          <t>2nd EDHEC AI and Finance Workshop</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Hitotsubashi University, Tokyo, Japan</t>
+          <t>EDHEC Business School, Nice, France</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6850,34 +6850,34 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Banks’ ESG and Climate Responsibilities, Banks as ESG and Climate Gatekeepers for Corporations, Banks, Climate Risk, and Financial Stability, Regulations, ESG, and Climate Risk, Central Banks, Banking Regulations, and Green Finance</t>
+          <t>NLP &amp; large language models; Speech and multimedia analysis; AI agents &amp; automation; Machine learning &amp; predictive analytics; Big data &amp; computational methods; The role of AI in corporate decision-making and other aspects of financial and labor markets; Ethics, policy, and regulation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>3rd Structured Retail Products and Derivatives Conference</t>
+          <t>Journal of International Money and Finance Special Issue and Conference</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Hagen, Germany</t>
+          <t>Hitotsubashi University, Tokyo, Japan</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6887,34 +6887,34 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>behavioral aspects, hedging strategies, market microstructure, pricing policies, product innovations, product valuation, regulatory issues</t>
+          <t>Banks’ ESG and Climate Responsibilities; Banks as ESG and Climate Gatekeepers for Corporations; Banks, Climate Risk, and Financial Stability; Regulations, ESG, and Climate Risk; Central Banks, Banking Regulations, and Green Finance</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>QRFE Workshop on Climate Change</t>
+          <t>3rd Structured Retail Products and Derivatives Conference</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Durham, United Kingdom</t>
+          <t>Hagen, Germany</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6924,34 +6924,34 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Climate Risk Pricing &amp; Asset Valuation, Institutional Investors &amp; Climate Exposure, Green Finance, ESG, and Real Effects, Carbon Emissions, Disclosure, and Regulatory Policy, Climate Risk Transmission Across Markets, Innovation, Transition Technologies, and Real Economic Impact, Data and Methodological Frontiers</t>
+          <t>behavioral aspects, hedging strategies, market microstructure, pricing policies, product innovations, product valuation, regulatory issues</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Commodity and Energy Markets Association (CEMA) 2026 Annual Meeting</t>
+          <t>QRFE Workshop on Climate Change</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>ESSEC Business School, France</t>
+          <t>Durham, United Kingdom</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Financial and operational risk analysis, decision making, optimization for sustainable ecosystems, energy and commodity sourcing, processing, trading, and related services.</t>
+          <t>Climate Risk Pricing &amp; Asset Valuation, Institutional Investors &amp; Climate Exposure, Green Finance, ESG, and Real Effects, Carbon Emissions, Disclosure, and Regulatory Policy, Climate Risk Transmission Across Markets, Innovation, Transition Technologies, and Real Economic Impact, Data and Methodological Frontiers</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3rd QRFE Workshop on Quantitative Finance</t>
+          <t>Commodity and Energy Markets Association (CEMA) 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Durham, United Kingdom</t>
+          <t>ESSEC Business School, France</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6998,71 +6998,71 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Big Data &amp; Information Efficiency, AI, Automation &amp; Liquidity, Modern Market Design, Blockchain &amp; Digital Market Microstructure, Stability, Systemic Risk &amp; Real Effects, Policy, Regulation &amp; SupTech</t>
+          <t>Energy and commodity finance, financial and operational risk analysis, decision making, optimization for sustainable ecosystems</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>19th Annual Corporate Governance Academic Conference</t>
+          <t>3rd QRFE Workshop on Quantitative Finance</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Durham, United Kingdom</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>100 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>corporate governance, board of directors, executive compensation, ownership structure, shareholder activism, institutional investors, mergers and acquisitions, private equity, sustainable finance, regulation, talent management</t>
+          <t>Big Data &amp; Information Efficiency, AI, Automation &amp; Liquidity, Modern Market Design, Blockchain &amp; Digital Market Microstructure, Stability, Systemic Risk &amp; Real Effects, Policy, Regulation &amp; SupTech</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>11th Conference on Professional Asset Management</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>EDHEC Business School, Nice, France</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7072,34 +7072,34 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Performance measurement, attribution, and liquidity in asset valuation; Investor (client) and manager behavior; Conflicts of interest in asset management; Institutional trading strategies and investment styles; Governance and regulation of investment companies; Financial innovation in asset management; The role and influence of financial advisors; Risk management and sector allocation</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>42nd International Conference of the French Finance Association (AFFI)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Clermont-Ferrand</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -7109,118 +7109,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>AI and Finance, Agricultural Finance and Insurance, Asset Pricing and Risk Premia, Banking and Financial Intermediation, Banking and Financial Regulations, Behavioral Finance, Blockchain/Cryptocurrencies and Protocols, Climate Change and Climate Risks in Finance, Commodities, Conscious and Mindful Finance, Corporate Finance, Corporate Governance, Development Finance and Microfinance, Ecological Finance, Entrepreneurial Finance, Epistemology of Finance, Ethics in Finance, Experimental Finance, Family Business Finance, Financial Distress and Bankruptcy, Financial Econometrics, Financial Markets, Financial Risk Management, Fintech and Financial Innovations, Geographical Finance, Green Finance, Historical Finance, Household and Personal Finance, Information and Market Efficiency, Insurance, International Finance, Macro Finance, Market Microstructure, Portfolio &amp; Asset Management, Quantitative Finance, Real Estate Finance, Risk Management, Social, Sustainable and Responsible Finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Third Annual UIC Finance Conference</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>working papers in all areas of finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>IBEFA Summer Meeting at the 2026 WEAI Conference</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>2026-07-03</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Denver, CO</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>US$100 (US$50 for papers solely authored by PhD. students)</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>financial intermediation; securitization and shadow banking; financial risk measurement and management; financial stability and macroprudential policies; payments systems; household finance; financial market structure and regulation; monetary policy; financial intermediation and global fragmentation; sustainable finance; FinTech</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Esade Spring Workshop 2026</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Barcelona, Spain</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>Asset Pricing and Financial Markets, Corporate Finance and Banking</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/public/conference_list.xlsx
+++ b/public/conference_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,64 +456,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026 Climate Finance &amp; Policy (CFP-2026)</t>
+          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bari, Italy</t>
+          <t>Pullman Paris Montparnasse Hotel</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75€</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026 Global AI Finance Research Conference</t>
+          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Taipei, Taiwan</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -523,71 +523,71 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
+          <t>Unpublished and policy-relevant research papers on municipal bond markets, primary market frictions, secondary market frictions, role of retail investors, government policies affecting bond price formation, effects of state and federal policies on government access to external finance</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
+          <t>SFS Cavalcade Asia-Pacific 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$99.00 USD</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces</t>
+          <t>Financial studies, Asset pricing, Corporate finance</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Colorado Finance Summit 2026</t>
+          <t>2026 CLIMATE FINANCE &amp; POLICY (CFP-2026)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vail, Colorado</t>
+          <t>Bari, Italy</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -597,182 +597,182 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>All areas of finance, theoretical and empirical contributions</t>
+          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026 UNSW Asset Pricing Workshop</t>
+          <t>2026 Global AI Finance Research Conference</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sydney (NSW, Australia)</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0 AUD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>All areas of Finance, with a special focus on Asset Pricing</t>
+          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
+          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Venice, Italy</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$99.00 USD</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Credit Risk and Advanced Analytics, Financial Innovation and Digital Transformation, Artificial Intelligence, Data Governance and Ethical Risk, Sustainability and Long-Term Value Creation, Systemic Risk, Resilience and Policy</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Investment &amp; Management, Entrepreneurship, Personal Finance, Behavioral Finance applications.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
+          <t>Colorado Finance Summit 2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Toronto, Ontario (Canada)</t>
+          <t>Vail, Colorado</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100 CAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Financial economics and accounting</t>
+          <t>All areas of finance, theoretical and empirical contributions</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
+          <t>2026 UNSW Asset Pricing Workshop</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lugano, Switzerland</t>
+          <t>Sydney (NSW, Australia)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 AUD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Real estate finance, urban economics, regional economics</t>
+          <t>All areas of Finance with a special focus on Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Santiago Finance Workshop 2026</t>
+          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
+          <t>Venice, Italy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -782,71 +782,71 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Any topic in finance or financial economics</t>
+          <t>Credit Risk and Advanced Analytics, Financial Innovation and Digital Transformation, Artificial Intelligence, Data Governance and Ethical Risk, Sustainability and Long-Term Value Creation, Systemic Risk, Resilience and Policy</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
+          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EM Normandie Business School, Caen campus, France</t>
+          <t>Toronto, Ontario (Canada)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100 CAD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
+          <t>Financial economics and accounting</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Climate Finance &amp; Sustainability Conference</t>
+          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Lugano, Switzerland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -856,34 +856,34 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Strategy and management, Accounting and finance, Entrepreneurship and innovation, Marketing and responsible consumption, Supply chain and operations management</t>
+          <t>Real estate finance, urban economics, regional economics</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
+          <t>Santiago Finance Workshop 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
+          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -893,71 +893,47 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ESG in the AI Era: Challenges and Opportunities, AI-Driven ESG Reporting and Assurance, Algorithmic Bias, Ethics, and Fairness in ESG Analytics, Regulatory Responses to AI-Enabled ESG Practices, AI, Greenwashing, and Corporate Accountability, AI for Sustainable Finance and Investment Decision-Making</t>
+          <t>Any topic in finance or financial economics</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026 FMA Asia/Pacific Conference</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-12-02</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Massey University, Auckland, New Zealand</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Financial decision-making, financial management, related topics</t>
-        </is>
-      </c>
+          <t>Please provide the text of the announcement so I can extract the required information.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sixth Biennial Conference on Auto Lending</t>
+          <t>Climate Finance &amp; Sustainability Conference</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -967,34 +943,34 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Auto lending and consumer finance, consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, spillovers from monetary policy and macroeconomic shocks.</t>
+          <t>Multi-stakeholder governance of sustainability initiatives, Managing business impacts on planetary boundaries, Inter- and intra-connectivity of environmental, social, and governance (ESG) factors, From disclosure to decision-usefulness in sustainability reporting, Regulatory competition in sustainability reporting and standard setting, ESG, sustainability, and climate finance, The role of artificial intelligence in advancing business sustainability, Design, scaling, and diffusion of sustainable business models, Social entrepreneurship and impact-driven ventures, Multi-dimensional sustainability claims and brand perceptions/performance, Stakeholder responses to corporate sustainability communication, Responsible consumption and consumer engagement in the circular economy, Operational resilience in the context of natural disasters and climate change, Technology adoption and implementation in sustainable supply chain management, Scope 3 emissions: measurement and management across the supply chain</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
+          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1004,66 +980,66 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Methodological advances in analyzing complex and high-dimensional data sets; Methodological advances in natural language processing, particularly with respect to causal inference; Innovative applications of generative AI; The societal impacts of AI and algorithmic decision-making</t>
+          <t>ESG in the AI Era: Challenges and Opportunities, AI-Driven ESG Reporting and Assurance, Algorithmic Bias, Ethics, and Fairness in ESG Analytics, Regulatory Responses to AI-Enabled ESG Practices, AI, Greenwashing, and Corporate Accountability, AI for Sustainable Finance and Investment Decision-Making</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Workshop on Innovations in Credit Scoring</t>
+          <t>2026 FMA Asia/Pacific Conference</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Massey University, Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Innovations in credit scoring, alternative data, fairness, transparency, data privacy, artificial intelligence, machine learning</t>
+          <t>Financial decision-making, financial management, related topics</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
+          <t>Sixth Biennial Conference on Auto Lending</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1078,34 +1054,34 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>monitoring and forecasting of economic and financial developments, high-frequency data, survey data, text as data, transactions data, granular data, preliminary and revised data in economic policy formulation and analysis, machine learning applications in real-time macroeconomics, probabilistic forecasts and assessments of crisis risks, innovative data sets and toolboxes, seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
+          <t>Auto lending, consumer finance, consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, role of alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, spillovers from monetary policy and macroeconomic shocks.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
+          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2023-07-12</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1115,51 +1091,51 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Quantitative methods and asset pricing</t>
+          <t>Methodological advances in analyzing complex and high-dimensional data sets, Methodological advances in natural language processing, particularly with respect to causal inference, Innovative applications of generative AI, The societal impacts of AI and algorithmic decision-making</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
+          <t>Workshop on Innovations in Credit Scoring</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Innovations in credit scoring, alternative data, fairness, transparency, data privacy, artificial intelligence, machine learning</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026 AIM Investment Conference</t>
+          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1179,44 +1155,44 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austin, Texas</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>mutual funds, hedge funds, pension funds, investment management</t>
+          <t>monitoring and forecasting of economic and financial developments, machine learning applications in real-time macroeconomics, probabilistic forecasts and assessments of crisis risks, using preliminary and revised data in economic policy formulation and analysis, related innovative data sets and toolboxes, seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
+          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1226,108 +1202,108 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
+          <t>quantitative methods and asset pricing</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
+          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Online Conference from Durham University, England, UK</t>
+          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Islamic finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
+          <t>2026 AIM Investment Conference</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Casa de Campo, La Romana, Dominican Republic</t>
+          <t>Austin, Texas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
+          <t>mutual funds, hedge funds, pension funds, investment management</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
+          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Australian National University (ANU), Canberra, Australia</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1337,34 +1313,34 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
+          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
+          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>Online Conference from Durham University, England, UK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1374,34 +1350,34 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Unpublished and highly policy-relevant research papers on municipal bond markets, primary market frictions, secondary market frictions, the role of retail investors, government policies targeting investors for bond price formation, state and federal policies on state and local government access to external finance</t>
+          <t>Islamic law and finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Inaugural Annual Conference on Insurance</t>
+          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>Casa de Campo, La Romana, Dominican Republic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1411,34 +1387,34 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>life insurance, Property &amp; Casualty insurance, reinsurance and risk transfer, mergers and other ownership changes, private equity ownership and impact on industry, indexed and variable annuities, household insurance choices, insurances’ investment and funding strategies, catastrophe risk, impact of insurance regulation</t>
+          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
+          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Imperial Business School, London</t>
+          <t>Australian National University (ANU), Canberra, Australia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1448,34 +1424,34 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
+          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026 Conference on Auditing and Capital Markets</t>
+          <t>Inaugural Annual Conference on Insurance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1485,34 +1461,34 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Audit-related topics, economic impact of auditing, audit regulation, audit oversight</t>
+          <t>Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026 Future Scholars in Finance Forum</t>
+          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Beijing, China</t>
+          <t>Imperial Business School, London</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1522,34 +1498,34 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
+          <t>2026 Conference on Auditing and Capital Markets</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1559,34 +1535,34 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
+          <t>Audit-related topics, economic impact of auditing, audit regulation, audit oversight</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>15th LaBS International Banking Workshop</t>
+          <t>Future Scholars in Finance Forum</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HSE University and online</t>
+          <t>Beijing, China</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1596,34 +1572,34 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Banking in Emerging Markets, Household finance</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026 Federal Reserve Stress Testing Research Conference</t>
+          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1633,71 +1609,71 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Economic and macroprudential effects of stress tests and bank regulation, novel approaches to modeling bank profitability, financial risks, and operational risks, design and applications of stress scenarios and reverse stress testing, nonbank credit intermediation, financial instruments for risk transfer, recent developments in bank regulation, impact of emerging technologies on banks and their regulators</t>
+          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
+          <t>15th LaBS International Banking Workshop</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pullman Paris Montparnasse Hotel</t>
+          <t>HSE University and online</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>75€</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Banking in Emerging Markets: Challenges and Opportunities, theoretical and empirical research in Banking or Household finance</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EBA's 15th Policy Research Workshop</t>
+          <t>2026 Federal Reserve Stress Testing Research Conference</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EBA premises (Paris, France) and remotely</t>
+          <t>Boston, Massachusetts</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1707,34 +1683,34 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience; Impacts of efficiency and proportionality; Competition, innovation, market entry, cross border growth and new areas under financial supervision; Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
+          <t>The economic and macroprudential effects of stress tests and bank regulation; Novel approaches to modeling bank profitability, financial risks, and operational risks; Design and applications of stress scenarios and reverse stress testing; Nonbank credit intermediation; Financial instruments for risk transfer; Recent developments in bank regulation; The impact of emerging technologies on banks and their regulators</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3rd Financial Fraud, Misconduct and Market Manipulation Conference</t>
+          <t>EBA's 15th Policy Research Workshop</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>EBA premises (Paris, France) and remotely</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1744,34 +1720,34 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Theoretical and empirical analysis of financial fraud, case studies of recent instances of market misconduct, insider trading, implications of financial fraud/market manipulation for market efficiency, stability, and asset pricing, market manipulation at a high-frequency (intraday) level, fraudulent activities and cryptocurrency markets, social networks, fake news and their effect on financial markets, money laundering and banking, conflicts of interest and their implications for various stakeholders and financial markets, hedge funds/mutual funds and their involvement in market misconduct, statistical/machine learning methods for fraud detection, cyber security and cyber risk management, regulatory response to financial misconduct, unintended consequences of politics and regulations</t>
+          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience, impacts of efficiency and proportionality, competition, innovation, market entry, cross border growth and new areas under financial supervision, proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
+          <t>Financial Fraud, Misconduct and Market Manipulation Conference</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>California State University, Fullerton</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1781,34 +1757,34 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>All areas of accounting and finance, including interdisciplinary research related to corporate reporting, governance, and financial markets</t>
+          <t>Theoretical and empirical analysis of financial fraud, Case studies of recent instances of market misconduct, Insider trading, Implication of financial fraud/market manipulation for market efficiency, stability, and asset pricing, Market manipulation at a high-frequency (intraday) level, Fraudulent activities and crypto currency markets, Social networks, fake news, and their effect on financial markets, Money laundering and banking, Conflicts of interests and their implications for various stakeholders and financial markets, Hedge funds/Mutual funds and their involvement in market misconduct, Statistical/ Machine Learning methods for fraud detection, Cyber security and cyber risk management, Regulatory response to financial misconduct, Unintended consequences of politics and regulations</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>25th Annual Bank Research Conference</t>
+          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
+          <t>California State University, Fullerton</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1818,108 +1794,108 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
+          <t>All areas of accounting and finance, interdisciplinary research related to corporate reporting, governance, and financial markets</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
+          <t>25th Annual Bank Research Conference</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>$99.00 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under conditions of risk and uncertainty, Venture Startups &amp; Exits, Markets &amp; Capital, Investment &amp; Management, Entrepreneurship, Innovation, Economic Development, Sustainable Finance, Personal Finance, Teaching, Learning, and Training using AI or AGI, Empirical Works, Evidence-Based Financial and Retirement Planning Best Practices, Behavioral/Cognitive Value Investing.</t>
+          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>17th Emerging Markets Conference</t>
+          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$99.00 USD</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>The sources of economic success or failure in EMs; Finance in EMs; Political economy, law, public administration, regulation in EMs; The impact of populism upon sustained growth; Insights into large EMs; Insights from narrow research projects; The new phase of globalization; Features of a society that enable or disable convergence; Grand challenges such as climate change; State capability in EMs; The interplay of military affairs, foreign policy and economics for EMs</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Financial/Capital Markets, Investment &amp; Management, Entrepreneurship, Personal Finance, Pedagogy, Behavioral Finance in Practice</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026 International Forum on Financial Regulation and RegTech</t>
+          <t>17th Emerging Markets Conference</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Beihang University, Beijing, China</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1929,14 +1905,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Financial regulation, Regulatory Technology (RegTech), FinTech, financial security, algorithmic bias, data privacy, financial fraud detection, systemic financial risk, AI applications in finance, and risk assessment methodologies.</t>
+          <t>The sources of economic success or failure in EMs, Finance in EMs (households, financial markets, financial intermediaries, firms and finance, finance and growth), Political economy, law, public administration, regulation in EMs, The impact of populism upon the possibility of sustained growth, Insights into large EMs that matter in and of themselves, Insights from narrow research projects that illuminate EMs in general, The new phase of globalisation and its consequences for international trade, international finance and the nature of the EM firm, Features of a society that enable or disable convergence into the “normal” package of high levels of freedom and prosperity, The puzzles faced by all kinds of decision makers: individuals, civil society actors, firms, all levels of government, Grand challenges such as climate change: implications for EMs and ramifications of choices made in EMs, State capability in EMs, The interplay of military affairs, foreign policy and economics for EMs</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
+          <t>2026 International Forum on Financial Regulation and RegTech</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1946,17 +1922,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>House of Management Science, Paris Pantheon-Assas University, 1 rue Guy-de-la-Brosse 75005 Paris, France</t>
+          <t>Beihang University, Beijing, China</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1966,108 +1942,108 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Finance, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives: Pricing and Hedging, Energy Markets: Modeling and Forecasting, Energy, Environment, and Climate Models, Financial and Economic Analysis of Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Natural Resources, Risk, Welfare, and Social Preferences, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
+          <t>Financial Regulation &amp; RegTech Innovation, Risk Assessment &amp; Management, AI, LLMs &amp; Financial Infrastructure</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
+          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>The Shard, London, UK</t>
+          <t>House of Management Science, Paris Pantheon-Assas University, 1 rue Guy-de-la-Brosse 75005 Paris, France</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>£45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges (DEXs), Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
+          <t>Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Finance, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives: Pricing and Hedging, Energy Markets: Modeling and Forecasting, Energy, Environment, and Climate Models, Financial and Economic Analysis of Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Natural Resources, Risk, Welfare, and Social Preferences, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
+          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lund, Sweden</t>
+          <t>The Shard, London, UK</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£45</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crypto and blockchain technology, Crypto markets, households, and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
+          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges, Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
+          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
+          <t>Lund, Sweden</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2077,34 +2053,34 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>New risks in a changing political environment, investment management excellence, innovative and high-quality research related to investment practitioners</t>
+          <t>Crypto and blockchain technology, Crypto markets, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
+          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shanghai and online</t>
+          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2114,34 +2090,34 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Financial development, financial inclusion, policy frameworks and regulatory challenges in sustainable finance, cross-border sustainable finance flows, corporate governance and greenwashing detection, ESG backlash and anti-ESG movements, AI and machine learning applications in ESG, big data and natural language processing for ESG, blockchain applications in carbon markets and green bonds, digital finance and decentralised finance in low-carbon transition, fintech-enabled green lending and climate insurance</t>
+          <t>New risks in a changing political environment, innovative research related to investment management</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
+          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Park Hyatt Busan, Busan, Korea</t>
+          <t>Shanghai and online</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2151,182 +2127,182 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
+          <t>Financial development, financial inclusion, and their role in sustainable economic growth; Policy frameworks and regulatory challenges shaping sustainable finance adoption in developed and emerging markets; Cross-border sustainable finance flows and international regulatory coordination; Corporate governance, greenwashing detection, and market responses to ESG commitments; ESG backlash, anti-ESG movements, and the political economy of sustainable finance; AI and machine learning applications in ESG investment strategies, sustainability disclosure, and climate risk modelling; Big data and natural language processing in measuring and monitoring ESG performance; Blockchain applications in carbon markets, green bonds, and regulatory compliance; Digital finance, decentralised finance (DeFi), and emerging technologies in supporting a low-carbon transition; Fintech-enabled green lending, climate insurance, and impact investing</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FIRN Melbourne Asset Pricing Meeting</t>
+          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Busan, Korea</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0 AUD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments.</t>
+          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Finance Conference</t>
+          <t>FIRN Melbourne Asset Pricing Meeting</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
+          <t>Melbourne, Australia</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 AUD</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>All areas of finance, particularly early-stage papers that would benefit from feedback and discussion</t>
+          <t>theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5th Holden Conference in Finance and Real Estate</t>
+          <t>Johns Hopkins Carey Finance Conference</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bloomington, IN</t>
+          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>$95 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Empirical and theoretical papers in all finance and real estate areas</t>
+          <t>All areas of finance, particularly early-stage papers</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
+          <t>5th Holden Conference in Finance and Real Estate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Bloomington, IN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$95 USD</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
+          <t>empirical and theoretical papers in all finance and real estate areas</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026 New Zealand Finance Meeting</t>
+          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2336,182 +2312,182 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>All topics related to the field of finance</t>
+          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026 Annual Community Bank Research Conference</t>
+          <t>2026 New Zealand Finance Meeting</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis in St. Louis, MO</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>The role of community banks in the U.S. financial system, impact of community banks on local/state economic activity, community banks’ response to financial and economic shocks, effects of regulatory policy on community banks, challenges and opportunities faced by community banks, advantages and disadvantages of the community bank business model</t>
+          <t>All topics related to the field of finance</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
+          <t>2026 Annual Community Bank Research Conference</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Gleacher Center - Chicago</t>
+          <t>Federal Reserve Bank of St. Louis in St. Louis, MO</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crony capitalism in 21st century America, political economy, business and political elite interactions, economic power and political influence</t>
+          <t>The role of community banks in the U.S. financial system, impact of community banks on local/state economic activity, community banks’ response to financial and economic shocks, effects of regulatory policy on community banks, challenges and opportunities faced by community banks, advantages and disadvantages of the community bank business model</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
+          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>University of South Carolina in Columbia, SC</t>
+          <t>Gleacher Center - Chicago</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>fixed income, commercial and investment banks, asset management and mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
+          <t>Crony capitalism in 21st century America, political economy, business and political elite dynamics</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Higher Education Finance Research Conference</t>
+          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>University of South Carolina in Columbia, SC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>financial aid, student debt, higher education finance</t>
+          <t>fixed income, commercial and investment banks, asset management, mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
+          <t>Higher Education Finance Research Conference</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2521,34 +2497,34 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
+          <t>financial aid, student debt, higher education finance</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Financial Decision-Making Conference 2026</t>
+          <t>2026 Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bozeman, MT</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2558,34 +2534,34 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, financial inclusion</t>
+          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>39th Australasian Finance and Banking Conference</t>
+          <t>Financial Decision-Making Conference 2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>Bozeman, MT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2595,145 +2571,145 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
+          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, and financial inclusion</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Finance and Real Estate Conference 2026</t>
+          <t>39th Australasian Finance and Banking Conference</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Miami University, Oxford, OH</t>
+          <t>Sydney, Australia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
+          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>UGA Fall Finance Conference 2026</t>
+          <t>Finance and Real Estate Conference 2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Athens, GA</t>
+          <t>Miami University, Oxford, OH</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>70 USD</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
+          <t>UGA Fall Finance Conference 2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Prague, Czech Republic</t>
+          <t>Athens, GA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>70 USD</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>deviations from rational expectations and their implications; optimism and pessimism in asset valuations and market dynamics; investment strategies and anomalies; factor investing; strategic and tactical asset allocation; portfolio choice under model and parameter uncertainty; and short selling</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WFE’s Sustainability Conference 2026</t>
+          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Prague, Czech Republic</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2743,108 +2719,108 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Transition finance and market design, Regulatory fragmentation and divergence, Sustainability reporting, data and assurance, Nature and biodiversity in capital markets, Just transition, social and gender finance, Proportionality for SMEs and emerging markets, Carbon market architecture</t>
+          <t>Expectations and Asset Prices, deviations from rational expectations, optimism and pessimism in asset valuations, investment strategies and anomalies, factor investing, strategic and tactical asset allocation, portfolio choice under model and parameter uncertainty, short selling, institutional investing and asset management</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026 FMA Annual Meeting</t>
+          <t>WFE’s Sustainability Conference 2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>$75 (current FMA members); $85 (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Financial decision-making, financial management, all areas of finance</t>
+          <t>Transition finance and market design; Regulatory fragmentation and divergence; Sustainability reporting, data and assurance; Nature and biodiversity in capital markets; Just transition, social and gender finance; Proportionality for SMEs and emerging markets; Carbon market architecture</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI in Finance Conference</t>
+          <t>2026 FMA Annual Meeting</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 (current FMA members); $85 (non-members)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics; Portfolio management, trading strategies, and risk management using AI; Large language models (LLMs), NLP, and textual analysis in finance; Corporate finance applications including M&amp;A and investment decisions; Banking, credit markets, and financial intermediation; Cryptocurrency, digital assets, and decentralized finance; ESG, sustainability, and climate finance; Financial regulation, policy analysis, and central bank communication; Real estate finance and urban economics; Alternative data and high-dimensional financial datasets; Investor behavior, sentiment, and attention; Macroeconomic and financial risk forecasting; AI in Sustainability and Climate Finance; AI and Real Estate</t>
+          <t>All areas of finance, financial decision-making, financial management, research projects, results of work in progress, recently completed work.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026 Summer Research Conference</t>
+          <t>AI in Finance Conference 2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Indian School of Business, Hyderabad Campus</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2854,34 +2830,34 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Recent Advances in Finance, corporate finance, asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
+          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics, Portfolio management, trading strategies, and risk management using AI, Large language models (LLMs), NLP, and textual analysis in finance, Corporate finance applications including M&amp;A and investment decisions, Banking, credit markets, and financial intermediation, Cryptocurrency, digital assets, and decentralized finance, ESG, sustainability, and climate finance, Financial regulation, policy analysis, and central bank communication, Real estate finance and urban economics, Alternative data and high-dimensional financial datasets, Investor behavior, sentiment, and attention, Macroeconomic and financial risk forecasting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>International Risk Management Conference 2026</t>
+          <t>2026 Summer Research Conference</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Warsaw, Poland</t>
+          <t>Indian School of Business, Hyderabad Campus</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2891,34 +2867,34 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology</t>
+          <t>Recent Advances in Finance, corporate finance, asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Second USTC Frontiers in Finance Conference</t>
+          <t>International Risk Management Conference 2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R. China</t>
+          <t>Warsaw, Poland</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2928,14 +2904,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>All topics of finance</t>
+          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Fischer-Shain Research Conference 2026</t>
+          <t>Second USTC Frontiers in Finance Conference</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2945,91 +2921,91 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R. China</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>0 CNY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>financial intermediation, banking, and financial services</t>
+          <t>All topics of finance</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ECB Money Market Conference 2026</t>
+          <t>Fischer-Shain Research Conference 2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>European Central Bank, Frankfurt am Main, Germany</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Money markets and monetary policy implementation, technological innovation in money markets such as stable coins, CBDCs, instant payments, functioning of money markets including roles of non-bank financial institutions and dealer intermediation, macroeconomic implications of short-term rate volatility and geopolitical developments</t>
+          <t>financial intermediation, banking, financial services</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Finance in the Digital Age (FiDA) Workshop</t>
+          <t>ECB Money Market Conference 2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Calgary, Canada</t>
+          <t>European Central Bank, Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3039,34 +3015,34 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>AI, DeFi, robo-advisors, neurofinance, decentralized finance</t>
+          <t>Money markets and monetary policy implementation, money markets and technological innovation, functioning of money markets</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
+          <t>Finance in the Digital Age (FiDA) Workshop</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bank of Italy, Rome, Italy</t>
+          <t>Calgary, Canada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3076,14 +3052,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Long-term investors’ strategies and behavior, long-term investors’ role in financing the real economy, shifting equilibria in government bond markets, sustainable investment strategies, challenges for long-term investors, non-bank investors in credit intermediation, rise of cryptocurrencies and fintech, emerging trends in asset allocation and risk management, shock transmission mechanisms, use of big data and AI in investment, innovations in financial markets, geopolitical risks, demographic transitions effects on financial markets.</t>
+          <t>AI, DeFi, robo-advisors, neurofinance</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
+          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3093,239 +3069,239 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Madrid, Spain, and virtually</t>
+          <t>Bank of Italy, Rome, Italy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>€350 in person (for conference dinner, lunches, and coffee breaks), €50 online option (for administrative / tech support)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, and repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, and venture capital</t>
+          <t>Long-term investors’ strategies and behavior, long-term investors’ role in financing the real economy, shifting equilibria in government bond markets, sustainable investment strategies, challenges for long-term investors, non-bank investors in credit intermediation, rise of cryptocurrencies and fintech, asset allocation and risk management trends, shock transmission mechanisms, use of big data and AI in investment processes, innovations in financial markets, geopolitical risks, effects of demographic transitions on financial markets.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Fintech and Financial Institutions Research Conference</t>
+          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
+          <t>Madrid, Spain, and virtually</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€350 in person, €50 online option</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Interlinkages of the fintech sector and the broader financial system, economic consequences and impacts, regulatory implications of the fintech sector</t>
+          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, and repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, venture capital</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aarhus Finance Forum 2026</t>
+          <t>Fintech and Financial Institutions Research Conference</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Aarhus, Denmark</t>
+          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>375 DKK (approx. 50 Euros)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
+          <t>Economic consequences and impacts of the fintech sector, regulatory implications of the fintech sector</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>15th CDI Conference on Derivatives</t>
+          <t>Aarhus Finance Forum 2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Montreal, Canada</t>
+          <t>Aarhus, Denmark</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>375 DKK</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Conference on CSR, the Economy and Financial Markets</t>
+          <t>15th CDI Conference on Derivatives</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Düsseldorf, Germany</t>
+          <t>Montreal, Canada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>€ 150 for regular participants; € 100 for PhD students</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Climate risk and pricing; Role of financial markets, banks, institutional investors in CSR; Effects of CSR on valuation, performance, cost of capital, funding and capital structure; Socio-economic aspects and their implications for companies and financial markets; Corporate governance and CSR; Risk management and CSR; CSR reporting and disclosure; ESG backlash and politicization; Sustainability strategy under new constraints; Measurement: information content and reliability of ESG indices; CSR activities and the economy</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026 Vietnam Symposium on Global Economy (VSGE2026)</t>
+          <t>Conference on CSR, the Economy and Financial Markets</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Düsseldorf, Germany</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€150 for regular participants, €100 for PhD students</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Geopolitical, macroeconomic policy, and development; trade, foreign direct investment, and global value chain; climate change, green transition, and public finance; finance, stability, and sustainable investment; digitalization, labor markets, and social protection; urbanization, regional development and resilience; AI, growth, economic impacts, and government policies; global governance, institutions, and international cooperation.</t>
+          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
+          <t>2026 Vietnam Symposium on Global Economy (VSGE2026)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CONRAD Seoul</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3335,34 +3311,34 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Geopolitical, macroeconomic policy, and development; Trade, foreign direct investment, and global value chain; Climate change, green transition, and public finance; Finance, stability, and sustainable investment; Digitalization, labor markets, and social protection; Urbanization, regional development and resilience; AI, growth, economic impacts, and government policies; Global governance, institutions, and international cooperation.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>India Finance Conference (IFC) 2026</t>
+          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Indian Institute of Management Bangalore</t>
+          <t>CONRAD Seoul</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3372,34 +3348,34 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Theoretical and empirical asset pricing, Corporate finance, capital structure and dividend policy, Asset allocation and investment management, Financial crises, systemic risk and macro-finance, Quality of financial reporting and adoption of IFRS, Corporate governance, executive compensation and ownership structure, Computational finance and financial econometrics, Financial Econometrics, Financial risk analytics and management, Market microstructure and algorithmic trading, Financial policy choice, institutions and regulation, Financial Analytics, ESG, Climate Finance, Blended Finance, Insurance / Reinsurance / Pension Funds, Enhancing liquidity in commodity derivatives markets, Financial Literacy and Financial Education</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Edinburgh Financial Technology Conference</t>
+          <t>India Finance Conference (IFC) 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Indian Institute of Management Bangalore</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3409,34 +3385,34 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>The application of AI and Machine Learning in finance, The application of distributed ledger technologies in finance, Cryptofinance, Cyber risk in finance, The microstructure of modern financial markets (algorithmic/high frequency trading, dark trading, blockchain settlements etc.), Behavioural economics in financial technology, Alternative data (structured and unstructured datasets), Crowdsourcing and investment strategy, New exchange traded financial derivatives, Financial stability risks from the development of FinTech, RegTech, Open banking</t>
+          <t>Theoretical and empirical asset pricing, Corporate finance, capital structure and dividend policy, Asset allocation and investment management, Financial crises, systemic risk and macro-finance, Quality of financial reporting and adoption of IFRS, Corporate governance, executive compensation and ownership structure, Computational finance and financial econometrics, Financial Econometrics, Financial risk analytics and management, Market microstructure and algorithmic trading, Financial policy choice, institutions and regulation, Financial Analytics, ESG, Climate Finance, Blended Finance, Insurance / Reinsurance / Pension Funds, Enhancing liquidity in commodity derivatives markets, Financial Literacy and Financial Education</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5th Conference in Sustainable Finance</t>
+          <t>Edinburgh Financial Technology Conference</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>University of Luxembourg</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3446,34 +3422,34 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Any topic in sustainable finance</t>
+          <t>The application of AI and Machine Learning in finance, The application of distributed ledger technologies in finance, Cryptofinance, Cyber risk in finance, The microstructure of modern financial markets: algorithmic/high frequency trading, dark trading, blockchain settlements etc., Behavioural economics in financial technology, Alternative data (structured and unstructured datasets), Crowdsourcing and investment strategy, New exchange traded financial derivatives, Financial stability risks from the development of FinTech, RegTech, Open banking</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>7th CEAR-RSI Household Finance Workshop</t>
+          <t>5th Conference in Sustainable Finance</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HEC Montréal</t>
+          <t>University of Luxembourg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3483,34 +3459,34 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Consumption-saving decisions and investment choices, Financial literacy and education, Pensions and retirement, Financial planning and advice, Financial delinquency and bankruptcy, Household insurance and risk management</t>
+          <t>Any topic in sustainable finance</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Next-Gen AI and Autonomous Finance (NGAI) workshop</t>
+          <t>7th CEAR-RSI Household Finance Workshop</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rennes School of Business, Rennes, France</t>
+          <t>HEC Montréal</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3520,34 +3496,34 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Autonomous agents &amp; decision-making in finance, AI-driven trading, portfolio optimization &amp; market microstructure, Risk, robustness, and model governance (validation, monitoring, compliance), Ethics, fairness, transparency &amp; societal impacts of financial AI, Financial decision making and AI, Bias and stereotyping in relation to AI driven finance, AI, money and financial value formation</t>
+          <t>Consumption-saving decisions and investment choices, Financial literacy and education, Pensions and retirement, Financial planning and advice, Financial delinquency and bankruptcy, Household insurance and risk management</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>12th Annual ICGS Conference</t>
+          <t>Next-Gen AI and Autonomous Finance (NGAI) workshop</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HEC Montréal (Quebec, Canada)</t>
+          <t>Rennes School of Business, Rennes, France</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3557,108 +3533,108 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Behavioral perspectives on executives, boards, investors, and other governance actors; Institutional and political approaches in governance; Implications of AI adoption for governance; Evolving forms of activism/engagement from investors and stakeholders; Reconfiguration of governance systems under geopolitical crises; Governance mechanisms for managing state-firm relations.</t>
+          <t>Autonomous agents &amp; decision-making in finance; AI-driven trading, portfolio optimization &amp; market microstructure; Risk, robustness, and model governance; Ethics, fairness, transparency &amp; societal impacts of financial AI; Financial decision making and AI; Bias and stereotyping in relation to AI driven finance; AI, money and financial value formation.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Vienna Festival of Finance Theory 2026</t>
+          <t>12th Annual ICGS Conference</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Vienna, Austria</t>
+          <t>HEC Montréal (Quebec, Canada)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>65 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Corporate finance theory, financial intermediation theory</t>
+          <t>Behavioral perspectives on governance, Institutional and political approaches to governance, Implications of AI adoption for governance, Evolving forms of activism/engagement, Reconfiguration of governance systems under geopolitical crises, Governance mechanisms for managing state-firm relations</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cross Country Perspectives in Finance (CCPF) Conference</t>
+          <t>Vienna Festival of Finance Theory 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>both online and on-site (Nanjing, China)</t>
+          <t>Vienna, Austria</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>65 EUR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>credit, banking, asset pricing, market liquidity, corporate finance, corporate governance, entrepreneurial finance</t>
+          <t>Corporate finance theory, financial intermediation theory</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Private Capital Symposium 2026</t>
+          <t>11th (2026) Cross Country Perspectives in Finance (CCPF) Conference</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>London Business School, London</t>
+          <t>both online and on-site (Nanjing, China)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3668,7 +3644,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Research on private equity, venture capital, and broader private market themes</t>
+          <t>credit, banking, asset pricing, market liquidity, corporate finance, corporate governance, entrepreneurial finance in an international context</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3718,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Asset pricing, macro-finance, impact of institutional features on capital market dynamics</t>
+          <t>asset pricing, macro-finance, impact of institutional features on capital market dynamics</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3792,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Investor behavior, behavior of different investor types, market microstructure and investor trading behavior, behavioral biases and performance of investment strategies, household consumption, borrowing, saving, and portfolio choice, investor education, financial literacy and sophistication, behavior of finance professionals and impact of professional advice, biological, psychological, and cultural foundations of investor behavior, influence of analysts, media, and news coverage on investment decisions, social influence and networks in finance, impact of investor behavior on corporate policies and decision-making</t>
+          <t>Investor behavior, Behavior of different investor types, Market microstructure and investor trading behavior, Behavioral biases and performance of investment strategies, Household consumption, borrowing, saving, and portfolio choice, Investor education, financial literacy, and sophistication, Behavior of finance professionals and the impact of professional advice, Biological, psychological, and cultural foundations of investor behavior, The influence of analysts, media, and news coverage on investment decisions, Social influence and networks in finance, Impact of investor behavior on corporate policies and decision-making</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3861,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>$75</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3897,7 +3873,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>11th SDU Finance Workshop on Corporate Finance</t>
+          <t>11th SDU Finance Workshop on Corporate Finance -- Dynamics, Uncertainty, and Strategic Decisions</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3964,7 +3940,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>topics from all areas of finance including asset pricing, corporate finance, financial intermediation, investments, Canadian financial markets, insurance, household finance, sustainable finance, fintech, and AI</t>
+          <t>Topics from all areas of finance including asset pricing, corporate finance, financial intermediation, investments, Canadian financial markets, insurance, household finance, sustainable finance, fintech and AI</t>
         </is>
       </c>
     </row>
@@ -3996,19 +3972,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>£50</t>
+          <t>£50 GBP</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Papers from all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF26)</t>
+          <t>International Conference on Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF 2026)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4075,7 +4051,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Accounting, Finance, Banking (theoretical and empirical studies)</t>
+          <t>All areas of Accounting, Finance, and Banking, encompassing both theoretical and empirical studies</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4088,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>forecasting financial variables with AI, asset allocation and asset management with AI, AI-based factor models, natural language processing and large language models in finance, and AI applications in corporate finance</t>
+          <t>forecasting financial variables with AI, asset allocation and asset management with AI, AI-based factor models, natural language processing and large language models in finance, AI applications in corporate finance</t>
         </is>
       </c>
     </row>
@@ -4304,39 +4280,15 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>12th IWH-FIN-FIRE Workshop on “Challenges to Financial Stability”</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Halle/Saale, Germany</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>regulation and financial intermediation, corporate finance, law, politics and finance, monetary policy, inflation and financial resilience, macroprudential policy and real estate, financial networks and systemic risk, pricing of climate risk in financial markets, ecological hazards and the behaviour of firms and households, governance of financial firms and markets, private credit and risk transfer</t>
-        </is>
-      </c>
+          <t>I apologize, but it seems that you haven't provided the text of the announcement. Please share the text, and I'll be happy to extract the required information for you.</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4366,7 +4318,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>$50</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4378,39 +4330,15 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>11th Bank of Finland and European Systemic Risk Board Joint Conference on AI and Systemic Risk Analytics</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Bank of Finland, Helsinki</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Use of Large Language Models (LLM) and trustworthy AI, AI and changing interdependencies in the financial markets, Cyber security and operational risks as sources of systemic risk, AI and Quantum Computing as potential source of new systemic risks, Use of AI with big data for systemic risk analytics, Risks and opportunities stemming from disruptive innovations in financial technology (FinTech), Analysing emerging risks from interconnectedness of the financial system, Identifying risks from market-based finance, Modelling geopolitical risks, Using systemic risk analytics to support macro-prudential policy and regulation, Evidence of macroprudential policy measures</t>
-        </is>
-      </c>
+          <t>It appears that the text of the announcement was not included in your message. Please provide the text of the call for papers so I can extract the required information for you.</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4556,7 +4484,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Finance and Economics</t>
+          <t>Finance, Economics</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4521,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Monetary Policy Transmission, Expectations, and Communication; Inflation and Price Dynamics; Macro-Finance and Financial Stability; Fiscal–Monetary Interactions and Policy Making; International Macroeconomics, Trade, and Geoeconomics; Firms, Productivity, and the Real Economy; Data, Methods, and Artificial Intelligence</t>
+          <t>Monetary Policy Transmission, Expectations, and Communication, Inflation and Price Dynamics, Macro-Finance and Financial Stability, Fiscal–Monetary Interactions and Policy Making, International Macroeconomics, Trade, and Geoeconomics, Firms, Productivity, and the Real Economy, Data, Methods, and Artificial Intelligence</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4595,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Interaction between financial and labor markets, technological innovation, job-skill matches, firms’ employment policies, role of employees in governance and financing of companies, responses of wages and employment to shocks, risk-sharing arrangements between firms and workers</t>
+          <t>Interaction between financial and labor markets, technological innovation, job-skill matches, firms’ employment policies, role of employees in governance and financing of companies, responses of wages, employment, and career trajectories to shocks, risk-sharing arrangements between firms and workers</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4669,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fintech and Financial Institutions, Regulatory framework revisions, CBDC blockchains, and stablecoins, Sovereign bonds and sovereign bond capital regulation, Payment systems and European sovereignty, Safe assets and exchange rate dynamics under world polarization, Private credit and financial stability, Climate regulation U-turn and implications for climate finance, Defence policy needs and European financial architecture</t>
+          <t>Fintech and Financial Institutions, Regulatory framework revisions, CBDC blockchains and stablecoins, Sovereign bonds and sovereign bond capital regulation, Payment systems and European sovereignty, Safe assets and exchange rate dynamics under world polarization, Private credit and financial stability, Climate regulation U-turn and implications for climate finance, Defence policy needs and European financial architecture</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4738,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>£65</t>
+          <t>£65 GBP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4842,17 +4770,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Seattle, Washington | UW Foster School of Business</t>
+          <t>Seattle, Washington</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>USD $80 per paper</t>
+          <t>80 USD</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>All areas of finance, particularly submissions from junior faculty and preliminary papers</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4891,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>sustainable finance, corporate governance, sustainability</t>
+          <t>Sustainable finance and the intersection of corporate governance and sustainability</t>
         </is>
       </c>
     </row>
@@ -5000,7 +4928,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Energy, Sustainability, Fintech including AI, Climate change, Alternative Investments, Asset &amp; Wealth Management, Asset Allocation, Sovereign Funds, Hedge Funds, ETFs, SWFs, Banking &amp; Financial Services, Corporate Governance, Executive Compensation, Country Risk, Debt Issues, Insurance, Reinsurance, Derivatives, Financial Engineering, E-Business, E-Finance, Social Media, Emerging Markets, Entrepreneurship, Venture Capital, Ethics, Legal, Regulatory Issues, Financial Crises, Financial Technology, Foreign Currency Issues, Future of Global Economy, Global Trade Issues, IPOs, SEOs, Stock Buybacks, Mergers and Acquisitions, Non-Traditional Banking, Portfolio Flows, Private Equity, Real Estate, Valuation, Portfolio Management, and Managing Financial Risk.</t>
+          <t>Energy, Sustainability, Fintech including AI, Climate change, Alternative Investments, Asset &amp; Wealth Management, Asset Allocation/Sovereign Funds/Hedge Funds/ETFs/SWFs, Banking &amp; Financial Services, Corporate Governance/Executive Compensation, Country Risk/Debt Issues/Insurance/Reinsurance, Derivatives/Financial Engineering, E-Business/E-Finance/Social Media, Emerging Markets/BRICS, Entrepreneurship/Venture Capital Global Perspectives, Ethics/Legal/Regulatory, Financial Crises and Bubbles, Financial Technology including AI, Foreign Currency Issues, Future of Global Economy, Global Trade Issues, IPOs/SEOs/Stock buybacks/Privatization, Market Behavior Efficiency/Inefficiency, Mergers and Acquisitions, Non-Traditional Banking &amp; Financial Services, Portfolio Flows and Foreign Direct Investment, Private Equity, Real estate - global perspectives, Valuation, Portfolio Management and Managing Financial Risk</t>
         </is>
       </c>
     </row>
@@ -5037,7 +4965,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Asset management, Asset pricing, Papers that bridge asset management and asset pricing</t>
+          <t>Asset management, asset pricing, papers bridging both areas</t>
         </is>
       </c>
     </row>
@@ -5069,12 +4997,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>70 USD</t>
+          <t>USD 70</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Asset pricing, financial intermediation, investments, Demand Based Asset Pricing, Inelastic Markets Hypothesis, New Methods in Asset Pricing (Machine Learning, AI, unstructured data), Time series and Cross-Sectional Predictability, Portfolio Allocation for Long Term Investors, Retirement decisions and choices, Behavioral finance</t>
+          <t>Demand Based Asset Pricing, Inelastic Markets Hypothesis, New Methods in Asset Pricing (Machine Learning, Artificial Intelligence (AI), unstructured data), Time series and Cross-Sectional Predictability, Portfolio Allocation for Long Term Investors, Retirement decisions and choices, Behavioral finance</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5039,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>AI, asset pricing, banking, behavioral finance, big data, blockchain, CBDCs, compliance, crowdfunding, cryptocurrencies, cybersecurity, decentralized finance, digital finance, embedded finance, fintech, financial infrastructure, financial inclusion, financial innovation, financial intermediation, financial markets, household finance, insurtech, machine learning, market microstructure, payments, platforms, regulation, risk management, stablecoins, tokenization, text analytics</t>
+          <t>AI, asset pricing, banking, behavioral finance, big data, blockchain, CBDCs, compliance, crowdfunding, cryptocurrencies, cybersecurity, decentralized finance, digital finance, embedded finance, fintech, financial infrastructure, financial inclusion, financial innovation, financial intermediation, financial markets, household finance, insurtech, machine learning, market microstructure, payments, platforms, regulation, risk management, stablecoins, tokenization, text analytics.</t>
         </is>
       </c>
     </row>
@@ -5143,12 +5071,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>$50 USD (FMA-members) / $60 USD (non-members)</t>
+          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>High-quality papers in the fields of finance and accounting that inform practice, advance academic research, address contemporary global issues, and introduce new hypotheses.</t>
+          <t>Inform practice and advance the frontiers of academic research in directions relevant to practice; Address issues that are relevant to contemporary issues globally and for policy formation and assessment; Introduce new hypotheses that have the potential to stimulate additional research</t>
         </is>
       </c>
     </row>
@@ -5180,12 +5108,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 GBP</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sustainable finance, interdisciplinary research</t>
+          <t>Unpublished research papers on any topic related to sustainable finance, interdisciplinary research that draws together approaches and perspectives from different disciplines</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5150,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cryptofinance, cryptocurrencies, digital finance, blockchain economics, AI for finance, corporate finance, alternative investments</t>
+          <t>Cryptofinance, blockchain economics, digital finance, FinTech, corporate finance, entrepreneurship, alternative investments</t>
         </is>
       </c>
     </row>
@@ -5259,7 +5187,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Non-academic-friendly summaries of research, pressing questions informed by academic research, sustainability issues</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5261,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>sustainable finance, green finance, climate finance, international finance</t>
+          <t>Sustainable finance, green finance, climate finance, international finance</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5305,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
+          <t>The 22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5444,7 +5372,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>The impact of investment in AI and supporting technologies on corporate earnings and share prices; the effects of AI on portfolio choices and trading behavior; the role of AI in creating new measures of economic activity; the uses of AI in financial market regulation; the consequences of AI for the financial advice industry; the macroeconomic effects of AI on economy-wide discount rates</t>
+          <t>The impact of investment in AI and supporting technologies on corporate earnings and share prices; effects of AI on portfolio choices and trading behavior of financial market participants; role of AI in creating new measures of economic activity; uses of AI in financial market regulation; consequences of AI for the financial advice industry; macroeconomic effects of AI on economy-wide discount rates</t>
         </is>
       </c>
     </row>
@@ -5513,12 +5441,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>450 euros</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Venture capital; private equity and buyouts; Business angels and early-stage financing; Crowdfunding; token offerings and digital finance; Entrepreneurial banking and credit relationships; Corporate governance, contracts, and monitoring; Financial innovation; FinTech and AI in entrepreneurial finance; ESG, sustainability, and impact finance; Entrepreneurial ecosystems and regional financing gaps; Entrepreneurial risk-taking and behavioral finance; Impact assessment for publicly supported financial instruments and their real effects and societal outcomes.</t>
+          <t>Venture capital; private equity, and buyouts; Business angels and early-stage financing; Crowdfunding; token offerings, and digital finance; Entrepreneurial banking and credit relationships; Corporate governance, contracts, and monitoring; Financial innovation; FinTech, and AI in entrepreneurial finance; ESG, sustainability, and impact finance; Entrepreneurial ecosystems and regional financing gaps; Entrepreneurial risk-taking and behavioral finance; Impact assessment for publicly supported financial instruments</t>
         </is>
       </c>
     </row>
@@ -5550,12 +5478,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Maturity and liquidity transformation by banks, broker-dealers, money market mutual funds, and other financial intermediaries; Repo markets and their clearing institutions; Theories of frictions and fragility in short-term funding markets; Effects of regulation and central bank intervention on funding markets; Securities lending; Money creation and the demand for safe assets; Fintech and encrypted currency</t>
+          <t>Maturity and liquidity transformation, Repo markets and their clearing institutions, Theories of frictions and fragility in short-term funding markets, Effects of regulation and central bank intervention on funding markets, Securities lending, Money creation and the demand for safe assets, Fintech and encrypted currency</t>
         </is>
       </c>
     </row>
@@ -5629,7 +5557,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
+          <t>Private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5594,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Corporate Finance, including mergers and acquisitions, corporate governance, and financial institutions</t>
+          <t>Corporate Finance</t>
         </is>
       </c>
     </row>
@@ -5735,12 +5663,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Papers on any area of finance, panel discussions, special sessions, tutorials</t>
+          <t>Papers on any area of finance, proposals for panel discussions, special sessions, or tutorials</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5705,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Original empirical and theoretical papers in accounting and finance, including banking, with a focus on significant and impactful issues within these fields</t>
+          <t>Original empirical and theoretical papers in accounting and finance, with a focus on significant and impactful issues within these fields</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5742,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Risk Governance in the boardroom, Risk Governance and the monitoring role of supervisory boards, Balancing risk and opportunity, Stakeholder influence on decision-making, Sustainability and Risk Governance, Understanding black swans in decision-making, Strategic resilience, Risk strategies on bank boards, Tackling digitalization-related risks, Role of artificial intelligence in decisions, Machine learning in decision-making</t>
+          <t>Risk Governance in the boardroom, Risk Governance and the monitoring role of supervisory boards, Balancing risk and opportunity, Stakeholder influence on board decision-making, Sustainability and Risk Governance, Understanding black swans, Strategic resilience, Considering risk strategies on bank boards, Tackling digitalization-related risks, The role of artificial intelligence for board decisions</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5786,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>9th Annual J.P. Morgan Center International Commodities Symposium</t>
+          <t>CU Denver 9th Annual J.P. Morgan Center International Commodities Symposium</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5888,7 +5816,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Commodity business, energy, metals and minerals, agriculture, commodity futures, derivatives</t>
+          <t>Broad global commodity sectors (energy, metals and minerals, and agriculture), commodity futures, derivatives, and related research topics</t>
         </is>
       </c>
     </row>
@@ -6031,7 +5959,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>$75 USD (FMA-members) and $85 USD (non-members)</t>
+          <t>$75 USD (FMA-members), $85 USD (non-members)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6142,7 +6070,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>£50 GBP</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -6221,7 +6149,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Entrepreneurship and innovation, Scaling frontier technologies, Industrial policy and innovation, University-industry collaboration, Global innovation networks, Innovation finance, Universities, governments, and policy in the new geopolitical era</t>
+          <t>Entrepreneurship and innovation, scaling frontier technologies, industrial policy and innovation, university-industry collaboration, global innovation networks, innovation finance, universities, governments, and policy in the new geopolitical era</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6186,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>(1) Empirical finance with AI and Big Data applications (e.g., alternative data) (2) New empirical method development in machine learning and financial econometrics (3) Blockchain technology, digital assets, and frontier FinTech topics</t>
+          <t>Empirical finance with AI and Big Data applications, New empirical method development in machine learning and financial econometrics, Blockchain technology, digital assets, and frontier FinTech topics</t>
         </is>
       </c>
     </row>
@@ -6295,7 +6223,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>New Technologies and Their Implications for Monetary Policy and Financial Stability, AI and automation impact on inflation dynamics, risks to financial stability from technological developments, adaptation of central banks' toolkits, transformation of financial markets, macroprudential supervision, monetary policy transmission mechanism, optimization of monetary policy decision-making using AI</t>
+          <t>New Technologies and Their Implications for Monetary Policy and Financial Stability, AI and automation impact on inflation dynamics, financial stability risks from technological developments, central banks' toolkits in an AI-driven economy, transformation of financial markets, macroprudential supervision risks and opportunities, effects of technological advances on monetary policy transmission mechanism, use of AI in optimizing monetary policy decision making</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6260,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>All aspects of behavioral finance, including financial behavior of individuals, groups, and organizations, market dynamics, and intersection of these areas</t>
+          <t>all aspects of behavioral finance, financial behavior of individuals, financial behavior of groups and organizations, dynamics of markets</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6366,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6480,7 +6408,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Uses of AI by firms in corporate finance, AI use in trading and asset management, AI use by banks and other credit providers, AI use in financial forecasting, AI use for understanding consumer financial behavior, AI and labor replacement vs. augmentation, Financial market and macroeconomic implications of AI use, AI, financial stability, and disparities, Frictions and market failures in AI adoption/use and regulatory solutions</t>
+          <t>Opportunities and risks of AI technologies in Finance, uses of AI by firms in corporate finance, AI use in trading and asset management, AI use by banks and credit providers, AI in financial forecasting, AI and consumer financial behavior, AI and labor replacement vs. augmentation, financial market implications of AI, risks to financial stability, frictions in AI adoption</t>
         </is>
       </c>
     </row>
@@ -6507,17 +6435,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Coogee Beach (Sydney, Australia)</t>
+          <t>Coogee Beach, Sydney, Australia</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>All areas of Finance with a special focus on Corporate Finance, including banking, household and entrepreneurial finance</t>
+          <t>All areas of Finance, with a special focus on Corporate Finance, including banking, household and entrepreneurial finance</t>
         </is>
       </c>
     </row>
@@ -6554,46 +6482,22 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Theoretical and empirical papers in banking and financial intermediation</t>
+          <t>theoretical and empirical papers in banking and financial intermediation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CCA-ESCP Workshop on Financial Institutions and Corporate Finance</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>ESCP Business School - Turin Campus</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Interactions among banks, non-bank intermediaries, and capital markets; Effects of technological innovation; Consequences of bank regulatory and supervisory reforms; Determinants of financial fragility, liquidity transformation, and systemic risk; Climate, sustainability, and transition finance; Corporate investment, capital structure, and liquidity management; Governance, ownership structures, incentives, and diversity; Monetary-policy transmission through banks and non-banks; Household and entrepreneurial finance; Impacts of geopolitical, political-economy, and policy shocks in finance</t>
-        </is>
-      </c>
+          <t>Please provide the text of the announcement so I can extract the required information for you.</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6746,7 +6650,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>10th Vietnam International Conference in Finance</t>
+          <t>The 10th Vietnam International Conference in Finance</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6813,7 +6717,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>all areas of finance, financial economics</t>
+          <t>Innovative research across all areas of finance</t>
         </is>
       </c>
     </row>
@@ -6850,7 +6754,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>NLP &amp; large language models; Speech and multimedia analysis; AI agents &amp; automation; Machine learning &amp; predictive analytics; Big data &amp; computational methods; The role of AI in corporate decision-making and other aspects of financial and labor markets; Ethics, policy, and regulation</t>
+          <t>NLP &amp; large language models, Speech and multimedia analysis, AI agents &amp; automation, Machine learning &amp; predictive analytics, Big data &amp; computational methods, The role of AI in corporate decision-making and other aspects of financial and labor markets, Ethics, policy, and regulation</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6791,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Banks’ ESG and Climate Responsibilities; Banks as ESG and Climate Gatekeepers for Corporations; Banks, Climate Risk, and Financial Stability; Regulations, ESG, and Climate Risk; Central Banks, Banking Regulations, and Green Finance</t>
+          <t>Banks’ ESG and Climate Responsibilities, Banks as ESG and Climate Gatekeepers for Corporations, Banks, Climate Risk, and Financial Stability, Regulations, ESG, and Climate Risk, Central Banks, Banking Regulations, and Green Finance</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6902,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Energy and commodity finance, financial and operational risk analysis, decision making, optimization for sustainable ecosystems</t>
+          <t>Economics, finance, mathematics, operations, risk management, energy and commodity sourcing, processing, trading, financial and operational risk analysis, decision making, optimization for sustainable ecosystems</t>
         </is>
       </c>
     </row>
@@ -7036,80 +6940,6 @@
       <c r="G179" t="inlineStr">
         <is>
           <t>Big Data &amp; Information Efficiency, AI, Automation &amp; Liquidity, Modern Market Design, Blockchain &amp; Digital Market Microstructure, Stability, Systemic Risk &amp; Real Effects, Policy, Regulation &amp; SupTech</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/public/conference_list.xlsx
+++ b/public/conference_list.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G179"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,64 +456,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
+          <t>Financial Econometrics Conference</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-04-21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2027-04-23</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pullman Paris Montparnasse Hotel</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75€</t>
+          <t>£30 GBP</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>High-frequency econometrics, Market microstructure, Forecasting, Asset Pricing and investments, Risk neutral density estimation, Fintech &amp; blockchain, Cryptocurrencies, Climate econometrics, Volatility modelling, Artificial intelligence &amp; machine learning, Factor models, Term structure models, Risk modelling, Real time detection of extreme market events, Options &amp; derivatives modelling, Multivariate &amp; high dimensional time series modelling</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
+          <t>2026 Sydney Banking and Financial Stability Conference</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-12-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>The University of Sydney Business School, Sydney, Australia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -523,108 +523,108 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Unpublished and policy-relevant research papers on municipal bond markets, primary market frictions, secondary market frictions, role of retail investors, government policies affecting bond price formation, effects of state and federal policies on government access to external finance</t>
+          <t>Banking, financial stability, Financial Intermediation, Financial Institutions and Markets, Fintech, Cryptocurrency and Central Bank Digital Currency, Financial system stability, Corporate Finance, Asset Pricing, Investment and Funds Management, Macro Finance</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SFS Cavalcade Asia-Pacific 2026</t>
+          <t>IIMB-CCGS International Corporate Governance &amp; Sustainability Conference 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-12-07</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-12-09</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>Indian Institute of Management, Bangalore, India</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Financial studies, Asset pricing, Corporate finance</t>
+          <t>Corporate governance, sustainability, geo-political and economy risk, supply chain risk, AI and data analytics in governance, management and law, corporate governance and executive leadership, internal and external mechanisms of corporate governance, board diversity, governance for sustainable value creation, governance in startups, family business &amp; SMEs, balance between shareholders and stakeholders, role of auditors and institutional investors, corporate disclosures &amp; reporting practices, environment, social and governance, enterprise risk management, cyber security &amp; governance</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026 CLIMATE FINANCE &amp; POLICY (CFP-2026)</t>
+          <t>Conference on CSR, the Economy and Financial Markets</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bari, Italy</t>
+          <t>Düsseldorf, Germany</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>€150 for regular participants, €100 for PhD students</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
+          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026 Global AI Finance Research Conference</t>
+          <t>International Conference in Banking and Financial Studies 2026 (ICBFS 2026)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Taipei, Taiwan</t>
+          <t>Parma, Italy</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -634,14 +634,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
+          <t>Banking and finance, Accounting, auditing, and taxation, Asset allocation and valuation, Banking regulation and financial services, Behavioral and experimental finance/economics, Big data in finance, artificial intelligence, and cybersecurity, Climate finance and sustainability, Corporate finance, IPOs, SEOs, M&amp;A, and crowdfunding, Corporate governance, Country funds, sovereign funds, and hedge funds, Debt markets and instruments, Digital finance, cryptocurrencies, and blockchain, Emerging markets finance, Energy finance and environmental issues, Entrepreneurial finance, venture capital, and private equity, Ethical finance, green finance, ESG, and CSR, Financial accounting and regulation, Financial crises, contagion, integration, and global risk interconnections, Financial engineering and derivatives, Foreign exchange markets and currency issues, Global imbalances and sustainability, Household finance, real estate finance, and microfinance, Market efficiency and behavior, Multinational financial management, Portfolio management and optimization, Risk management and compliance, Small business finance</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
+          <t>Colorado Finance Summit 2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -651,54 +651,54 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>Vail, Colorado</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>$99.00 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Investment &amp; Management, Entrepreneurship, Personal Finance, Behavioral Finance applications.</t>
+          <t>All areas of finance, theoretical and empirical contributions</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colorado Finance Summit 2026</t>
+          <t>18th Annual Hedge Fund Research Conference</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2027-01-21</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vail, Colorado</t>
+          <t>Université Paris Dauphine - PSL, Paris</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -708,71 +708,71 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>All areas of finance, theoretical and empirical contributions</t>
+          <t>hedge funds, mutual funds, ETFs, private equity funds, institutional investors’ risks and performance, transparency (reporting) and due diligence, financial intermediation activity, macroeconomic issues such as systemic risk and contagion, institutional investors’ incentives and activism, portfolio liquidation and liquidity, financial regulation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026 UNSW Asset Pricing Workshop</t>
+          <t>15th LaBS International Banking Workshop</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sydney (NSW, Australia)</t>
+          <t>HSE University and online</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0 AUD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>All areas of Finance with a special focus on Asset Pricing</t>
+          <t>Banking in Emerging Markets: Challenges and Opportunities, theoretical and empirical research in Banking or Household finance</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
+          <t>Private Equity Research Consortium (PERC) Symposium</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Venice, Italy</t>
+          <t>Chapel Hill, NC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -782,71 +782,71 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Credit Risk and Advanced Analytics, Financial Innovation and Digital Transformation, Artificial Intelligence, Data Governance and Ethical Risk, Sustainability and Long-Term Value Creation, Systemic Risk, Resilience and Policy</t>
+          <t>Private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
+          <t>IMRC 2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-11-20</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-12-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Toronto, Ontario (Canada)</t>
+          <t>IIM Ahmedabad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100 CAD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Financial economics and accounting</t>
+          <t>Finance, Accounting, Economics, governance, financial risk &amp; analytics, theoretical and empirical asset pricing, quality of financial reporting and adoption of IFRS, market microstructure and algorithmic trading, insurance/reinsurance/pension funds, business cycles, corporate finance, capital structure and dividend policy, financial policy choice, institutions and regulation, enhancing liquidity in commodity derivatives markets, public economics, asset allocation and investment management, computational finance and financial econometrics, FDI and portfolio capital flows, household finance, international trade and exchange rates, financial crises, systemic risk and macro-finance, financial risk analytics and management, financial analytics, monetary policy and banking, global value chains and firm performance, macroeconomics, applied microeconomics</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
+          <t>16th Workshop on Exchange Rates</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lugano, Switzerland</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -856,14 +856,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Real estate finance, urban economics, regional economics</t>
+          <t>The drivers of exchange rates and related asset prices from a financial perspective, Exchange rates and the transmission of monetary policy, FX interventions and supply side shocks, Exchange rates and macrofinancial stability frameworks, FX risk premia and their drivers, Global linkages between capital flows, foreign exchange rates and risk appetite, The international use of currencies and its implications for exchange rates, Implications of digital and tokenised assets for FX markets</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Santiago Finance Workshop 2026</t>
+          <t>2026 New Zealand Finance Meeting</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-12-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
+          <t>Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -893,84 +893,108 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Any topic in finance or financial economics</t>
+          <t>All topics related to the field of finance</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Please provide the text of the announcement so I can extract the required information.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+          <t>6th Conference on Corporate Policies and Asset Prices (COAP)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-12-09</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Nice, France</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>€50</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>asset pricing anomalies and their explanations; corporate finance models of asset pricing anomalies; dynamic corporate finance and contracting models, and their asset pricing implications; the asset pricing implications of sustainable finance; feedback effects from asset prices to corporate decisions; structural estimation of dynamic models using asset price data</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Climate Finance &amp; Sustainability Conference</t>
+          <t>5th Contemporary Issues in Financial Markets and Banking</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2027-02-10</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2027-02-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Online Conference</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD 175</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Multi-stakeholder governance of sustainability initiatives, Managing business impacts on planetary boundaries, Inter- and intra-connectivity of environmental, social, and governance (ESG) factors, From disclosure to decision-usefulness in sustainability reporting, Regulatory competition in sustainability reporting and standard setting, ESG, sustainability, and climate finance, The role of artificial intelligence in advancing business sustainability, Design, scaling, and diffusion of sustainable business models, Social entrepreneurship and impact-driven ventures, Multi-dimensional sustainability claims and brand perceptions/performance, Stakeholder responses to corporate sustainability communication, Responsible consumption and consumer engagement in the circular economy, Operational resilience in the context of natural disasters and climate change, Technology adoption and implementation in sustainable supply chain management, Scope 3 emissions: measurement and management across the supply chain</t>
+          <t>Financial resilience; Green, climate and sustainable finance; Decentralised finance and disruptive financial technologies; Theoretical asset pricing; Empirical asset pricing, liquidity and behavioural economics and finance; Risk management; Financial inclusion; Alternative investments; Crowd-funding; Islamic banking; Banking and financial sector stability and regulation; Financial (dis)integration and Brexit; Artificial intelligence, machine and deep learning applications in finance; Corporate finance and sustainable energy financing; Crisis investment and portfolio management; Corporate governance; International financial management and investment; Market microstructure; Household finance; Real estate and property markets; Metaverse and Blockchain technologies in finance; Intersection between finance and economic theory, especially financial applications of game theory, decision theory, and computational financial economics; experimental economics with implications for financial theory and practice.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
+          <t>International Conference on Trade Wars, Geopolitical Fragmentation and Repercussions for Financial and Monetary Stability</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
+          <t>Brunel University of London (UK)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -980,71 +1004,71 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ESG in the AI Era: Challenges and Opportunities, AI-Driven ESG Reporting and Assurance, Algorithmic Bias, Ethics, and Fairness in ESG Analytics, Regulatory Responses to AI-Enabled ESG Practices, AI, Greenwashing, and Corporate Accountability, AI for Sustainable Finance and Investment Decision-Making</t>
+          <t>Art of the (trade) deal and financial costs, Asymmetric impacts on regions, commodity exporters, service-oriented economies and manufacturing centres, Capital flows and sudden stops due to trade wars, Central Banking in the age of trade wars and geopolitical conflicts, Central bank digital currencies (CBDCs), trade wars and geopolitical tensions, Currency weaponisation, competitive devaluation and financial instability, Digitisation, financial decoupling and financial stability during trade conflicts, Emerging markets and international financial flows under trade tensions, Empirical and theoretical analyses of strategic financial policies under trade restrictions, Exorbitant privilege of the US$ in the 21st century and the rise of alternative currencies, European Economic and Monetary Union’s financial integration with the US and the Global South, Financialization in the context of trade wars, Global financial imbalances, causes and financial consequences in the context of trade wars, International financial and monetary architecture and stress management in the age of trade conflict, Inflation targeting, trade wars and geopolitical conflicts, Productivity, innovation and efficiency related to technological spillovers and protectionism, Reallocation of global capital, safe havens and asset price bubbles during trade conflicts, Regional financial and monetary integration and the positive role of regions during trade conflicts, Role of central banks and macroprudential policy during trade conflicts, Sustainable financial development of the Global South and trade wars, Tariffs and non-tariff barriers and their negative financial impact on markets and firms</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026 FMA Asia/Pacific Conference</t>
+          <t>Labor &amp; Finance Group Fall 2026 Conference</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-12-02</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Massey University, Auckland, New Zealand</t>
+          <t>Penn State University – Smeal College of Business, State College, PA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Financial decision-making, financial management, related topics</t>
+          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sixth Biennial Conference on Auto Lending</t>
+          <t>CUHK-RAPS-RCFS Conference on Asset Pricing and Corporate Finance</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1054,71 +1078,71 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Auto lending, consumer finance, consumer demand and vehicle choice, loan pricing and contract design, underwriting and credit risk modeling, dealer intermediation and markups, borrower outcomes and delinquency dynamics, fraud and identity risk, fair lending and consumer compliance, subprime and near-prime market structure, repossession and loss mitigation, servicing and collections, role of alternative data and automated decisioning, electric vehicles and evolving collateral risk, used vehicle prices and depreciation, auto insurance interactions, fintech and market structure, auto asset-backed securities, spillovers from monetary policy and macroeconomic shocks.</t>
+          <t>Asset Pricing, Corporate Finance</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
+          <t>2026 ABFER-JFDS Conference on AI for Finance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2023-07-12</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>International Institute of Finance, Hefei, Anhui, China</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Methodological advances in analyzing complex and high-dimensional data sets, Methodological advances in natural language processing, particularly with respect to causal inference, Innovative applications of generative AI, The societal impacts of AI and algorithmic decision-making</t>
+          <t>Applications of artificial intelligence, machine learning, natural language processing, large language models, AI agents, high-performance computing in finance; Use of unstructured and alternative data in investment, auditing, and related fields; Social and economic impacts of AI adoption; Ethical, governance, and regulatory considerations of AI in finance; Quantitative investment strategies and portfolio optimization using AI.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Workshop on Innovations in Credit Scoring</t>
+          <t>Financial Economic Meeting</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1128,34 +1152,34 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Innovations in credit scoring, alternative data, fairness, transparency, data privacy, artificial intelligence, machine learning</t>
+          <t>Financial markets &amp; asset pricing, Banking, credit &amp; financial stability, Macroeconomics &amp; international finance, Sustainable finance &amp; climate risk, Quantitative methods &amp; emerging approaches</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
+          <t>39th Australasian Finance and Banking Conference</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>AGSM and the UNSW Business School, Sydney, Australia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1165,34 +1189,34 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>monitoring and forecasting of economic and financial developments, machine learning applications in real-time macroeconomics, probabilistic forecasts and assessments of crisis risks, using preliminary and revised data in economic policy formulation and analysis, related innovative data sets and toolboxes, seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
+          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
+          <t>Finance at a Time of Change and Uncertainty</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Renmin University of China, Beijing, China</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1202,108 +1226,108 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>quantitative methods and asset pricing</t>
+          <t>Finance and AI, Finance and politics, Finance and climate change</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
+          <t>MIT GCFP 13th Annual Conference</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-11-27</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-11-28</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
+          <t>Cambridge, MA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USD $250 for On-line Presenter &amp; USD $300 for On-site Presenter</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Financial regulation in an era of innovation and disruption, AI's impact on financial markets, labor markets and the economy, investor protection and fair lending, new risks to financial stability, changing market structure for equities, bonds, and derivatives, growth of event contracts and prediction markets, growth of non-bank credit, developments in stablecoins, digital currencies, and payment systems, risks in “safe” assets such as sovereign debt, international coordination and comparisons, innovations in market architecture and infrastructure</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026 AIM Investment Conference</t>
+          <t>EUROFIDAI-ESSEC Paris December Finance Meeting</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Austin, Texas</t>
+          <t>Pullman Paris Montparnasse Hotel</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>75€</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>mutual funds, hedge funds, pension funds, investment management</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
+          <t>Chicago Fed/University of Chicago Conference on Municipal Bond Markets</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1313,71 +1337,71 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
+          <t>Unpublished and highly policy-relevant research papers on municipal bond markets, focusing on primary market frictions, secondary market frictions, role of retail investors, government policies affecting bond price formation, and the effect of state and federal policies on government access to external finance.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
+          <t>SFS Cavalcade Asia-Pacific 2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-12-07</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-12-09</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Online Conference from Durham University, England, UK</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Islamic law and finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
+          <t>In-depth participation in finance-related topics including but not limited to asset pricing, corporate finance, and fixed income.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
+          <t>Sustainable Accounting, Finance and Economics International Conference 2026 (SAFE2026)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-11-22</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-11-24</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Casa de Campo, La Romana, Dominican Republic</t>
+          <t>Bandar Sunway, Malaysia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1387,34 +1411,34 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
+          <t>Sustainability-oriented research in accounting, finance, and economics</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
+          <t>2026 Climate Finance &amp; Policy (CFP-2026)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Australian National University (ANU), Canberra, Australia</t>
+          <t>Bari, Italy</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1424,34 +1448,34 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
+          <t>AI-driven Climate Risk Assessment and Prediction, Big Data and ESG Decision-making, Carbon Border Adjustment Mechanisms, Carbon Finance and Pricing, Climate Change and Corporate Behavior, Climate Finance for Energy Efficiency, Carbon Taxes, Climate Agreements and Frameworks, Climate Funds and Public Finance, Climate Risk Assessment and Disclosure, ESG Measurement, Ratings &amp; Data Quality, Financing Climate Adaptation and Resilience, Green Finance, Green Bonds and Socially Responsible Bonds, Just Transition, Nature, Biodiversity &amp; Finance, Role of Technology in Climate Finance, Sustainable Investing, Sustainability Regulation &amp; Political Economy</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Inaugural Annual Conference on Insurance</t>
+          <t>2026 Global AI Finance Research Conference</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Chicago</t>
+          <t>Taipei, Taiwan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1461,108 +1485,108 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
+          <t>Artificial Intelligence (AI), Big Data and Machine Learning, Blockchain and Cryptocurrencies, Security Token Offerings (STOs) and Initial Coin Offerings (ICOs), Decentralized Finance (DeFi), Peer-to-peer lending, FinTech regulation, High-frequency trading and market liquidity, Green FinTech</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
+          <t>37th Annual Conference of the Academy of Behavioral Finance &amp; Economics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Imperial Business School, London</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$99.00</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Innovative models for decision making and risk taking, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Trust in Financial/Capital Markets, Financial Management, Entrepreneurship, Sustainable Finance, Behavioral Finance &amp; Economics in Retirement Saving &amp; Planning, Empirical Works in Behavioral Finance, Evidence-Based Financial Planning, Neuromorphic-based Strategies, Nudging Clients and Markets, Behavioral/Cognitive Value Investing</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026 Conference on Auditing and Capital Markets</t>
+          <t>2026 UNSW Asset Pricing Workshop</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>Sydney (NSW, Australia)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 AUD</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Audit-related topics, economic impact of auditing, audit regulation, audit oversight</t>
+          <t>All areas of Finance, with a special focus on Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Future Scholars in Finance Forum</t>
+          <t>International Conference in Venice - Artificial Intelligence, Financial Innovation and Credit Risk</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Beijing, China</t>
+          <t>Venice, Italy</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1572,71 +1596,71 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Credit Risk and Advanced Analytics, AI- and machine learning-based credit risk models, Explainable AI (XAI) and model transparency in credit scoring, Stress testing, early warning systems and credit cycle analysis, Credit risk under macroeconomic, financial and geopolitical uncertainty, Financial Innovation and Digital Transformation, FinTech, BigTech and new models of credit intermediation, Open banking, open finance and alternative data in credit markets, Innovation in credit markets, securitization and risk transfer, Regulation of financial innovation, Artificial Intelligence, Data Governance and Ethical Risk, Algorithmic bias, fairness and discrimination in credit decisions, Data governance, privacy and cybersecurity in credit systems, Legal accountability and responsibility of AI-driven models, Regulatory implications of AI adoption in financial services, Sustainability and Long-Term Value Creation, ESG factors and climate risk in credit assessment, Sustainable finance and its impact on credit risk and pricing, Credit, access to finance and financial inclusion, The role of financial institutions in supporting the sustainable transition, Systemic Risk, Resilience and Policy Interactions between credit risk and systemic risk, Financial stability in a data-driven and AI-enabled economy, Macroprudential and microprudential policy responses, Coordination between regulators, supervisors and market participants</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
+          <t>36th Annual Conference on Financial Economics and Accounting (CFEA)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dubai, UAE</t>
+          <t>Toronto, Ontario (Canada)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>100 CAD</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
+          <t>Financial economics and accounting</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>15th LaBS International Banking Workshop</t>
+          <t>2026 Lugano Real Estate and Urban Economics Conference</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HSE University and online</t>
+          <t>Lugano, Switzerland</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1646,34 +1670,34 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Banking in Emerging Markets: Challenges and Opportunities, theoretical and empirical research in Banking or Household finance</t>
+          <t>Real estate economics, real estate finance, regional economics, urban economics</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026 Federal Reserve Stress Testing Research Conference</t>
+          <t>Santiago Finance Workshop 2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-12-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Boston, Massachusetts</t>
+          <t>Universidad de Chile, Diag. Paraguay 257, Santiago, Chile</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1683,34 +1707,34 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>The economic and macroprudential effects of stress tests and bank regulation; Novel approaches to modeling bank profitability, financial risks, and operational risks; Design and applications of stress scenarios and reverse stress testing; Nonbank credit intermediation; Financial instruments for risk transfer; Recent developments in bank regulation; The impact of emerging technologies on banks and their regulators</t>
+          <t>Any topic in finance or financial economics</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EBA's 15th Policy Research Workshop</t>
+          <t>4th International Conference on Circular Economy, Business Strategy &amp; Management</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>EBA premises (Paris, France) and remotely</t>
+          <t>EM Normandie Business School, Caen campus, France</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1720,34 +1744,34 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience, impacts of efficiency and proportionality, competition, innovation, market entry, cross border growth and new areas under financial supervision, proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
+          <t>sustainability, ESG, innovation, resilience, circular business models, future of management research</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Financial Fraud, Misconduct and Market Manipulation Conference</t>
+          <t>Climate Finance &amp; Sustainability Conference</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lancaster University, England</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1757,34 +1781,34 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Theoretical and empirical analysis of financial fraud, Case studies of recent instances of market misconduct, Insider trading, Implication of financial fraud/market manipulation for market efficiency, stability, and asset pricing, Market manipulation at a high-frequency (intraday) level, Fraudulent activities and crypto currency markets, Social networks, fake news, and their effect on financial markets, Money laundering and banking, Conflicts of interests and their implications for various stakeholders and financial markets, Hedge funds/Mutual funds and their involvement in market misconduct, Statistical/ Machine Learning methods for fraud detection, Cyber security and cyber risk management, Regulatory response to financial misconduct, Unintended consequences of politics and regulations</t>
+          <t>Sustainability in business, multi-stakeholder governance, managing business impacts on planetary boundaries, ESG factors, sustainability reporting, regulatory competition, climate finance, role of artificial intelligence in sustainability, sustainable business models, responsible consumption, operational resilience, and sustainable supply chain management</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
+          <t>China Accounting and Finance Review (CAFR) Special Issue Conference 2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>California State University, Fullerton</t>
+          <t>Zhongnan University of Economics and Law, Wuhan, China</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1794,108 +1818,108 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>All areas of accounting and finance, interdisciplinary research related to corporate reporting, governance, and financial markets</t>
+          <t>ESG in the AI Era: Challenges and Opportunities, AI-Driven ESG Reporting and Assurance, Algorithmic Bias, Ethics, and Fairness in ESG Analytics, Regulatory Responses to AI-Enabled ESG Practices, AI, Greenwashing, and Corporate Accountability, AI for Sustainable Finance and Investment Decision-Making</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>25th Annual Bank Research Conference</t>
+          <t>2026 FMA Asia/Pacific Conference</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-12-02</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arlington, VA</t>
+          <t>Massey University, Auckland, New Zealand</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
+          <t>Financial decision-making, financial management, current issues in finance</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
+          <t>Sixth Biennial Conference on Auto Lending</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Santa Monica, California, USA</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>$99.00 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Financial/Capital Markets, Investment &amp; Management, Entrepreneurship, Personal Finance, Pedagogy, Behavioral Finance in Practice</t>
+          <t>Auto lending, consumer finance, loan pricing, contract design, underwriting, credit risk modeling, dealer intermediation, borrower outcomes, fraud, fair lending, subprime market structure, repossession, servicing, alternative data, electric vehicles, used vehicle prices, auto insurance, fintech, auto asset-backed securities, monetary policy spillovers</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>17th Emerging Markets Conference</t>
+          <t>Frontiers in Machine Learning and Economics: Methods and Applications</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-12-13</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mumbai, India</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1905,34 +1929,34 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>The sources of economic success or failure in EMs, Finance in EMs (households, financial markets, financial intermediaries, firms and finance, finance and growth), Political economy, law, public administration, regulation in EMs, The impact of populism upon the possibility of sustained growth, Insights into large EMs that matter in and of themselves, Insights from narrow research projects that illuminate EMs in general, The new phase of globalisation and its consequences for international trade, international finance and the nature of the EM firm, Features of a society that enable or disable convergence into the “normal” package of high levels of freedom and prosperity, The puzzles faced by all kinds of decision makers: individuals, civil society actors, firms, all levels of government, Grand challenges such as climate change: implications for EMs and ramifications of choices made in EMs, State capability in EMs, The interplay of military affairs, foreign policy and economics for EMs</t>
+          <t>Methodological advances in analyzing complex and high-dimensional data sets, Methodological advances in natural language processing (particularly with respect to causal inference), Innovative applications of generative AI, The societal impacts of AI and algorithmic decision-making</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026 International Forum on Financial Regulation and RegTech</t>
+          <t>Workshop on Innovations in Credit Scoring</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Beihang University, Beijing, China</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1942,34 +1966,34 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Financial Regulation &amp; RegTech Innovation, Risk Assessment &amp; Management, AI, LLMs &amp; Financial Infrastructure</t>
+          <t>Innovations in credit scoring, alternative data, artificial intelligence, machine learning, risk management, credit access</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
+          <t>2026 Conference on Real-Time Data Analysis, Methods, and Applications</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>House of Management Science, Paris Pantheon-Assas University, 1 rue Guy-de-la-Brosse 75005 Paris, France</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1979,145 +2003,145 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Finance, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives: Pricing and Hedging, Energy Markets: Modeling and Forecasting, Energy, Environment, and Climate Models, Financial and Economic Analysis of Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Natural Resources, Risk, Welfare, and Social Preferences, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
+          <t>monitoring and forecasting of economic and financial developments, high-frequency data, survey data, text as data, transactions data, granular data, using preliminary and revised data in economic policy formulation and analysis, machine learning applications in real-time macroeconomics, probabilistic forecasts and assessments of crisis risks, related innovative data sets and toolboxes, seasonal and cyclical adjustment for real-time monitoring and forecasting</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
+          <t>2026 Jacobs Levy Center Frontiers in Quantitative Finance Conference</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>The Shard, London, UK</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>£45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges, Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
+          <t>quantitative methods and asset pricing</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
+          <t>34th Annual PBFEAM and 20th NYCU International conferences</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-11-27</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-11-28</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lund, Sweden</t>
+          <t>National Yang Ming Chiao Tung University, Hsinchu, Taiwan</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>USD $250 (On-line Presenter), USD $300 (On-site Presenter)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crypto and blockchain technology, Crypto markets, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
+          <t>2026 AIM Investment Conference</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
+          <t>Austin, Texas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>New risks in a changing political environment, innovative research related to investment management</t>
+          <t>mutual funds, hedge funds, pension funds, investment management</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
+          <t>2026 Wharton Conference on Liquidity and Financial Fragility</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shanghai and online</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2127,34 +2151,34 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Financial development, financial inclusion, and their role in sustainable economic growth; Policy frameworks and regulatory challenges shaping sustainable finance adoption in developed and emerging markets; Cross-border sustainable finance flows and international regulatory coordination; Corporate governance, greenwashing detection, and market responses to ESG commitments; ESG backlash, anti-ESG movements, and the political economy of sustainable finance; AI and machine learning applications in ESG investment strategies, sustainability disclosure, and climate risk modelling; Big data and natural language processing in measuring and monitoring ESG performance; Blockchain applications in carbon markets, green bonds, and regulatory compliance; Digital finance, decentralised finance (DeFi), and emerging technologies in supporting a low-carbon transition; Fintech-enabled green lending, climate insurance, and impact investing</t>
+          <t>Coordination failures, self-fulfilling beliefs, and runs; Fragility in banks and non-bank institutions; Liquidity and frictions in financial markets and macroeconomy; Systemic risk and financial regulation; Monetary policy and financial stability; Artificial intelligence (AI) and its implications for financial macroeconomic stability; The rise and potential risks in private credit markets; New payment technologies, stablecoins, tokenization, and their financial stability implications; Geopolitical tensions, trade conflicts, currency competition, and financial fragility; Inflation, interest rate risks, and implications on financial fragility; The real impact of crises and fragility on firms’ financing and investment policies</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
+          <t>Towards a New Synthesis in Islamic Finance: Law, Economics and Shari’ah</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Busan, Korea</t>
+          <t>Online Conference from Durham University, England, UK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2164,71 +2188,71 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
+          <t>Islamic finance, financial innovation, regulatory oversight, governance mechanisms, economic development, sustainability, social equity, inclusive economic development</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FIRN Melbourne Asset Pricing Meeting</t>
+          <t>74th Meeting of the EURO Working Group for Commodities and Financial Modelling (EWGCFM)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-22</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-11-24</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Melbourne, Australia</t>
+          <t>Casa de Campo, La Romana, Dominican Republic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0 AUD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments</t>
+          <t>Asset Pricing, Corporate Finance, Banking and Financial Institutions, Commodities and Energy Markets, Financial Modelling and Econometrics, Blockchain and Cryptocurrencies, Derivatives and Risk Management, Market Microstructure, Sustainable Finance</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Finance Conference</t>
+          <t>FIRN 2026 ANU Money, Credit, and Financial Stability Meeting</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
+          <t>Australian National University (ANU), Canberra, Australia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2238,71 +2262,71 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>All areas of finance, particularly early-stage papers</t>
+          <t>Monetary policy and transmission mechanisms, Credit markets and financial intermediation, Banking, liquidity, and regulation, Financial crises and systemic risk, Macro-finance</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5th Holden Conference in Finance and Real Estate</t>
+          <t>Inaugural Annual Conference on Insurance</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bloomington, IN</t>
+          <t>Federal Reserve Bank of Chicago</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>$95 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>empirical and theoretical papers in all finance and real estate areas</t>
+          <t>Life insurance, Property &amp; Casualty insurance, Reinsurance and risk transfer, Mergers and other ownership changes, Private equity ownership and impact on industry, Indexed, variable annuities, and other savings products, Household insurance choices, Insurances’ investment and funding strategies, Catastrophe risk, Impact of insurance regulation</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
+          <t>Payments, Digital Assets, AI and the Future of Financial Markets</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Astana, Kazakhstan</t>
+          <t>Imperial Business School, London</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2312,34 +2336,34 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
+          <t>Digital platforms, banking, and financial intermediation; Artificial intelligence, machine learning, and financial decision-making; Blockchain, tokenization, digital assets, and decentralized finance; Payment systems, central bank digital currencies, and stablecoins; FinTech regulation, supervision, market design, and financial stability; Data, privacy, cybersecurity, and consumer protection in finance; Entrepreneurial finance, venture capital, and innovation in financial services; Household finance, inclusion, and welfare effects of financial technology; Market microstructure, trading technologies, and liquidity; Competition between banks, platforms, and non-bank financial institutions</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026 New Zealand Finance Meeting</t>
+          <t>2026 Conference on Auditing and Capital Markets</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Auckland, New Zealand</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2349,71 +2373,71 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>All topics related to the field of finance</t>
+          <t>Economic impact of auditing, audit regulation, audit oversight on capital markets</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026 Annual Community Bank Research Conference</t>
+          <t>Future Scholars in Finance Forum</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of St. Louis in St. Louis, MO</t>
+          <t>Beijing, China</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>The role of community banks in the U.S. financial system, impact of community banks on local/state economic activity, community banks’ response to financial and economic shocks, effects of regulatory policy on community banks, challenges and opportunities faced by community banks, advantages and disadvantages of the community bank business model</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
+          <t>Prototypes for Humanity 2026 Short Papers Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-15</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gleacher Center - Chicago</t>
+          <t>Dubai, UAE</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2423,14 +2447,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crony capitalism in 21st century America, political economy, business and political elite dynamics</t>
+          <t>Wellbeing and Human Performance, Infrastructures and Cities, Autonomous Systems and Advanced Manufacturing, Environment, Sustainability and Energy, Mobility and Logistics, Socio-Economic Empowerment, Digital Economies and Future Markets, Open and Speculative</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
+          <t>2026 Federal Reserve Stress Testing Research Conference</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2440,54 +2464,54 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-31</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>University of South Carolina in Columbia, SC</t>
+          <t>Boston, Massachusetts</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>fixed income, commercial and investment banks, asset management, mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
+          <t>The economic and macroprudential effects of stress tests and bank regulation, Novel approaches to modeling bank profitability, financial risks, and operational risks, Design and applications of stress scenarios and reverse stress testing, Nonbank credit intermediation, such as from nonbank financial institutions, private credit, business development companies, and their interactions with stress testing, Financial instruments for risk transfer, such as hedges and synthetic securitizations, and their implications, Recent developments in bank regulation, The impact of emerging technologies on banks and their regulators</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Higher Education Finance Research Conference</t>
+          <t>EBA's 15th Policy Research Workshop</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-11-19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia</t>
+          <t>EBA premises (Paris, France) and remotely</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2497,34 +2521,34 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>financial aid, student debt, higher education finance</t>
+          <t>Competitiveness and efficiency in the prudential rulebook without undermining resilience; Impacts of efficiency and proportionality; Competition, innovation, market entry, cross border growth and new areas under financial supervision; Proportionate integration of ESG risks in governance, strategy, and remuneration frameworks</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026 Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
+          <t>Financial Fraud, Misconduct and Market Manipulation Conference</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>University of Pennsylvania, Philadelphia, PA</t>
+          <t>Lancaster University, England</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2534,34 +2558,34 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
+          <t>Theoretical and empirical analysis of financial fraud, Case studies of recent instances of market misconduct, Insider trading, Implication of financial fraud/market manipulation for market efficiency, stability, and asset pricing, Market manipulation at a high-frequency (intraday) level, Fraudulent activities and crypto currency markets, Social networks, fake news, and their effect on financial markets, Money laundering and banking, Conflicts of interests and their implications for various stakeholders and financial markets, Hedge funds/Mutual funds and their involvement in market misconduct, Statistical/ Machine Learning methods for fraud detection, Cyber security and cyber risk management, Regulatory response to financial misconduct, Unintended consequences of politics and regulations</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Financial Decision-Making Conference 2026</t>
+          <t>22nd Annual Haskell &amp; White Corporate Reporting and Governance Conference</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bozeman, MT</t>
+          <t>California State University, Fullerton</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2571,34 +2595,34 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, and financial inclusion</t>
+          <t>All areas of accounting and finance, corporate reporting, governance, financial markets</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>39th Australasian Finance and Banking Conference</t>
+          <t>25th Annual Bank Research Conference</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-12-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sydney, Australia</t>
+          <t>Arlington, VA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2608,108 +2632,108 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Opportunities and Risks of AI Technology in Finance, CBDCs, Fintech, and Digital Finance, Sustainable Investment</t>
+          <t>Regulatory reform options and considerations, Risk and resiliency in the financial system, Real effects of financial turmoil, Innovations in financial intermediation, Deposit insurance and stability, Emerging competitive threats to traditional banking, AI and technology in finance, Banks’ role in the 21st Century</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Finance and Real Estate Conference 2026</t>
+          <t>The Future of Decision-Making and Risk-Taking: Bridging Finance, Economics, Brain, and Behavior</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Miami University, Oxford, OH</t>
+          <t>Santa Monica, California, USA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>$99.00</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
+          <t>Behavioral/Cognitive Finance &amp; Economics, Neuroscience/Neuromorphic Computing, Political Economy, Biological Anthropology, Brain-Computer Interfaces, Development of New Financial &amp; Economic Models, Decision Making under risk and uncertainty, Venture Startups &amp; Exits, Trust in Financial Markets, Personal Finance, and Behavioral Finance applications.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>UGA Fall Finance Conference 2026</t>
+          <t>17th Emerging Markets Conference</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-12-13</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Athens, GA</t>
+          <t>Mumbai, India</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>70 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>The sources of economic success or failure in EMs, Finance in EMs (households, financial markets, financial intermediaries, firms and finance, finance and growth), Political economy, law, public administration, regulation in EMs, The impact of populism upon the possibility of sustained growth, Insights into large EMs that matter in and of themselves, Insights from narrow research projects that illuminate EMs in general, The new phase of globalisation and its consequences for international trade, international finance and the nature of the EM firm, Features of a society that enable or disable convergence into the “normal” package of high levels of freedom and prosperity, The puzzles faced by all kinds of decision makers: individuals, civil society actors, firms, all levels of government, Grand challenges such as climate change: implications for EMs and ramifications of choices made in EMs, State capability in EMs, The interplay of military affairs, foreign policy and economics for EMs</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
+          <t>2026 International Forum on Financial Regulation and RegTech</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Prague, Czech Republic</t>
+          <t>Beihang University, Beijing, China</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2719,34 +2743,34 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Expectations and Asset Prices, deviations from rational expectations, optimism and pessimism in asset valuations, investment strategies and anomalies, factor investing, strategic and tactical asset allocation, portfolio choice under model and parameter uncertainty, short selling, institutional investing and asset management</t>
+          <t>Financial Regulation &amp; RegTech Innovation, Risk Assessment &amp; Management, AI, LLMs &amp; Financial Infrastructure</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WFE’s Sustainability Conference 2026</t>
+          <t>2026 International Symposium on Climate, Finance, and Sustainability (ISCFS-2026)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>House of Management Science, Paris Pantheon-Assas University, 1 rue Guy-de-la-Brosse 75005 Paris, France</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2756,71 +2780,71 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Transition finance and market design; Regulatory fragmentation and divergence; Sustainability reporting, data and assurance; Nature and biodiversity in capital markets; Just transition, social and gender finance; Proportionality for SMEs and emerging markets; Carbon market architecture</t>
+          <t>Carbon Finance and Taxes, Climate and Economic Modeling in Policy Making, Climate Finance, Climate Negotiations and Scenarios, Climate Risk and Disclosures, Climate-resilient Economies, Energy Derivatives: Pricing and Hedging, Energy Markets: Modeling and Forecasting, Energy, Environment, and Climate Models, Financial and Economic Analysis of Energy Markets, Financial Regulation of Energy and Environmental Markets, Green Finance and Sustainable Investment, Just Energy Transition, Macroeconomic Implications of Net-Zero Carbon Emissions, Nature-based Financial Instruments for Climate Change Mitigation, Natural Resources, Risk, Welfare, and Social Preferences, Renewable Energy, Regulation and Energy Governance, Role of Financial Institutions in Sustainability</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026 FMA Annual Meeting</t>
+          <t>5th Annual Academic - 2026 DeFi &amp; Digital Currencies Conference</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tampa, FL</t>
+          <t>The Shard, London, UK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>$75 (current FMA members); $85 (non-members)</t>
+          <t>£45</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>All areas of finance, financial decision-making, financial management, research projects, results of work in progress, recently completed work.</t>
+          <t>DeFi Protocols, Lending and Borrowing Protocols, Decentralized Exchanges, Blockchain Economics, Stablecoins and CBDCs, Digital Money and Payments, Tokenisation of real-world assets, Traditional and Decentralized Finance Interaction, Digital Finance and Inclusion</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI in Finance Conference 2026</t>
+          <t>3rd Arne Ryde Conference on Crypto, Fintech and Payments</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Montréal, QC, Canada</t>
+          <t>Lund, Sweden</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2830,34 +2854,34 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics, Portfolio management, trading strategies, and risk management using AI, Large language models (LLMs), NLP, and textual analysis in finance, Corporate finance applications including M&amp;A and investment decisions, Banking, credit markets, and financial intermediation, Cryptocurrency, digital assets, and decentralized finance, ESG, sustainability, and climate finance, Financial regulation, policy analysis, and central bank communication, Real estate finance and urban economics, Alternative data and high-dimensional financial datasets, Investor behavior, sentiment, and attention, Macroeconomic and financial risk forecasting</t>
+          <t>Crypto and blockchain technology, Crypto markets, households, and the real economy, Environmental and social impact of crypto markets, Interaction between traditional finance and decentralized finance, Stablecoins, Central Bank Digital Currencies (CBDCs), Financial technology (Fintech), Payment systems, Open banking and data sharing, Digital tools in financial services, Financial inclusion, development, and welfare in digital finance</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026 Summer Research Conference</t>
+          <t>Institute for Quantitative Investment Research Autumn Residential Seminar 2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Indian School of Business, Hyderabad Campus</t>
+          <t>Ashdown Park Hotel &amp; Country Club, Wych Cross, East Sussex, UK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2867,34 +2891,34 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Recent Advances in Finance, corporate finance, asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
+          <t>New risks in a changing political environment; papers relevant to investment practitioners</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>International Risk Management Conference 2026</t>
+          <t>10th Shanghai-Edinburgh-London Finance Conference On Sustainable Finance in the Digital Era</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Warsaw, Poland</t>
+          <t>Shanghai and online</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2904,108 +2928,108 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology</t>
+          <t>Financial development, financial inclusion and their role in sustainable economic growth; Policy frameworks and regulatory challenges shaping sustainable finance adoption in developed and emerging markets; Cross-border sustainable finance flows and international regulatory coordination; Corporate governance, greenwashing detection, and market responses to ESG commitments; ESG backlash, anti-ESG movements, and the political economy of sustainable finance; AI and machine learning applications in ESG investment strategies, sustainability disclosure, and climate risk modelling; Big data and natural language processing in measuring and monitoring ESG performance; Blockchain applications in carbon markets, green bonds, and regulatory compliance; Digital finance, decentralised finance (DeFi), and emerging technologies in supporting a low-carbon transition; Fintech-enabled green lending, climate insurance, and impact investing.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Second USTC Frontiers in Finance Conference</t>
+          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R. China</t>
+          <t>Busan, Korea</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>0 CNY</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>All topics of finance</t>
+          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Fischer-Shain Research Conference 2026</t>
+          <t>FIRN Melbourne Asset Pricing Meeting</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Philadelphia, PA</t>
+          <t>Melbourne, Australia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>0 AUD</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>financial intermediation, banking, financial services</t>
+          <t>theoretical and empirical models of asset prices and returns, return predictability, empirical methodology, macro-finance, the study of financial institutions as related to asset prices, information and liquidity in asset markets, behavioural investment studies, asset market structure and microstructure, risk analysis, hedge funds, mutual funds, pension funds, ESG, and alternative investments</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ECB Money Market Conference 2026</t>
+          <t>Johns Hopkins Carey Finance Conference</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>European Central Bank, Frankfurt am Main, Germany</t>
+          <t>Johns Hopkins Carey Business School, 100 International Drive, Baltimore, MD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3015,71 +3039,71 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Money markets and monetary policy implementation, money markets and technological innovation, functioning of money markets</t>
+          <t>All areas of finance, particularly early-stage papers that would benefit from feedback and discussion</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Finance in the Digital Age (FiDA) Workshop</t>
+          <t>5th Holden Conference in Finance and Real Estate</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Calgary, Canada</t>
+          <t>Bloomington, IN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$95 USD</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>AI, DeFi, robo-advisors, neurofinance</t>
+          <t>Empirical and theoretical papers in all finance and real estate areas</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
+          <t>12th P2P Financial Systems International Workshop (P2PFISY 2026)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bank of Italy, Rome, Italy</t>
+          <t>Astana, Kazakhstan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3089,14 +3113,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Long-term investors’ strategies and behavior, long-term investors’ role in financing the real economy, shifting equilibria in government bond markets, sustainable investment strategies, challenges for long-term investors, non-bank investors in credit intermediation, rise of cryptocurrencies and fintech, asset allocation and risk management trends, shock transmission mechanisms, use of big data and AI in investment processes, innovations in financial markets, geopolitical risks, effects of demographic transitions on financial markets.</t>
+          <t>Regulation &amp; Compliance in Digital Asset Markets, Fraud, Financial Crime &amp; Forensics in Crypto Markets, CBDCs and Digital Public Infrastructure, Stablecoins and Digital Payment Systems, Artificial Intelligence in Financial Systems, Consumer Protection, Data Governance, and Trust in Digital Finance, Tokenisation of Real-World Assets (RWA)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
+          <t>2026 Annual Community Bank Research Conference</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3106,54 +3130,54 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Madrid, Spain, and virtually</t>
+          <t>Federal Reserve Bank of St. Louis in St. Louis, MO</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>€350 in person, €50 online option</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, and repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, venture capital</t>
+          <t>The role of community banks in the U.S. financial system, the provision of financial services to households, small businesses, and small farms, impact of community banks on local/state economic activity, community banks’ response to financial and economic shocks and the associated policy responses, the effects of regulatory policy on community banks, quantifying regulatory and compliance costs, intended and unintended effects of regulatory requirements, antitrust policy and community banks, challenges and opportunities faced by community banks, competition from large banks, credit unions, and nonbanks including financial technology firms, funding and liquidity issues, collaborations/partnerships with financial technology and crypto firms, payments issues, the effects of rapid technological advances in banking, operational risk, advantages and disadvantages of the community bank business model, bank consolidation, noninterest/fee income, benefits of local knowledge and strong relationships, costs of operating at a small scale.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Fintech and Financial Institutions Research Conference</t>
+          <t>Stigler Center-CEPR Political Economy of Finance Conference 2026: Crony Capitalism in 21st Century America</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-11-07</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
+          <t>Gleacher Center - Chicago</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3163,71 +3187,71 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Economic consequences and impacts of the fintech sector, regulatory implications of the fintech sector</t>
+          <t>Crony capitalism in 21st century America</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aarhus Finance Forum 2026</t>
+          <t>15th Fixed Income and Financial Institutions (FIFI) Conference</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aarhus, Denmark</t>
+          <t>University of South Carolina in Columbia, SC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>375 DKK</t>
+          <t>75 USD</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
+          <t>fixed income, commercial and investment banks, asset management and mutual fund companies, short sellers, hedge funds, broker-dealers, insurance companies</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>15th CDI Conference on Derivatives</t>
+          <t>Higher Education Finance Research Conference</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Montreal, Canada</t>
+          <t>Federal Reserve Bank of Philadelphia</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3237,71 +3261,71 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>financial aid, student debt, higher education finance</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Conference on CSR, the Economy and Financial Markets</t>
+          <t>Wharton–Chicago–Harvard Insolvency and Restructuring Conference (WCHIRC)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Düsseldorf, Germany</t>
+          <t>University of Pennsylvania, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>€150 for regular participants, €100 for PhD students</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement: information content and reliability of ESG indices, CSR activities and the economy</t>
+          <t>Corporate financial distress and bankruptcy, Liability management and out-of-court restructurings, Chapter 11 and formal reorganization processes, Consumer bankruptcy, Leveraged lending and private credit, Creditor governance and capital structure dynamics, Distressed debt markets and asset pricing, Financial contracting and covenant design, Bankruptcy law, courts, and institutional design, Operational restructuring and firm performance</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026 Vietnam Symposium on Global Economy (VSGE2026)</t>
+          <t>Financial Decision-Making Conference 2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City, Vietnam</t>
+          <t>Bozeman, MT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3311,108 +3335,108 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Geopolitical, macroeconomic policy, and development; Trade, foreign direct investment, and global value chain; Climate change, green transition, and public finance; Finance, stability, and sustainable investment; Digitalization, labor markets, and social protection; Urbanization, regional development and resilience; AI, growth, economic impacts, and government policies; Global governance, institutions, and international cooperation.</t>
+          <t>household finance, financial literacy and education, consumer financial behavior, retirement and savings decisions, financial education interventions, fintech and digital finance, financial advice and delegation, debt and credit decisions, insurance decisions, behavioral finance, and financial inclusion</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
+          <t>Finance and Real Estate Conference 2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-12-10</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-12-11</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>CONRAD Seoul</t>
+          <t>Miami University, Oxford, OH</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Asset pricing and valuation, Corporate finance, Real estate markets and investment, Risk management and financial regulation, Urban economics and housing policy, Sustainable and green finance, Behavioral finance</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>India Finance Conference (IFC) 2026</t>
+          <t>UGA Fall Finance Conference 2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-12-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Indian Institute of Management Bangalore</t>
+          <t>Athens, GA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>70 USD</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Theoretical and empirical asset pricing, Corporate finance, capital structure and dividend policy, Asset allocation and investment management, Financial crises, systemic risk and macro-finance, Quality of financial reporting and adoption of IFRS, Corporate governance, executive compensation and ownership structure, Computational finance and financial econometrics, Financial Econometrics, Financial risk analytics and management, Market microstructure and algorithmic trading, Financial policy choice, institutions and regulation, Financial Analytics, ESG, Climate Finance, Blended Finance, Insurance / Reinsurance / Pension Funds, Enhancing liquidity in commodity derivatives markets, Financial Literacy and Financial Education</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Edinburgh Financial Technology Conference</t>
+          <t>Inquire Europe Autumn Conference: “Expectations and Asset Prices”</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Prague, Czech Republic</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3422,34 +3446,34 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>The application of AI and Machine Learning in finance, The application of distributed ledger technologies in finance, Cryptofinance, Cyber risk in finance, The microstructure of modern financial markets: algorithmic/high frequency trading, dark trading, blockchain settlements etc., Behavioural economics in financial technology, Alternative data (structured and unstructured datasets), Crowdsourcing and investment strategy, New exchange traded financial derivatives, Financial stability risks from the development of FinTech, RegTech, Open banking</t>
+          <t>deviations from rational expectations and their implications; optimism and pessimism in asset valuations and market dynamics; investment strategies and anomalies; factor investing; strategic and tactical asset allocation; portfolio choice under model and parameter uncertainty; short selling; institutional investing and asset management</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5th Conference in Sustainable Finance</t>
+          <t>WFE’s Sustainability Conference 2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>University of Luxembourg</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3459,71 +3483,71 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Any topic in sustainable finance</t>
+          <t>Transition finance and market design, Regulatory fragmentation and divergence, Sustainability reporting, Nature and biodiversity in capital markets, Just transition, social and gender finance, Proportionality for SMEs and emerging markets, Carbon market architecture</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>7th CEAR-RSI Household Finance Workshop</t>
+          <t>2026 FMA Annual Meeting</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-11-14</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HEC Montréal</t>
+          <t>Tampa, FL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 (current FMA members); $85 (non-members)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Consumption-saving decisions and investment choices, Financial literacy and education, Pensions and retirement, Financial planning and advice, Financial delinquency and bankruptcy, Household insurance and risk management</t>
+          <t>Financial decision-making, financial management, all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Next-Gen AI and Autonomous Finance (NGAI) workshop</t>
+          <t>3rd AI in Finance Conference</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rennes School of Business, Rennes, France</t>
+          <t>Montréal, QC, Canada</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3533,34 +3557,34 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Autonomous agents &amp; decision-making in finance; AI-driven trading, portfolio optimization &amp; market microstructure; Risk, robustness, and model governance; Ethics, fairness, transparency &amp; societal impacts of financial AI; Financial decision making and AI; Bias and stereotyping in relation to AI driven finance; AI, money and financial value formation.</t>
+          <t>Machine learning and artificial intelligence in asset pricing and financial econometrics, Portfolio management, trading strategies, and risk management using AI, Large language models (LLMs), NLP, and textual analysis in finance, Corporate finance applications including M&amp;A and investment decisions, Banking, credit markets, and financial intermediation, Cryptocurrency, digital assets, and decentralized finance, ESG, sustainability, and climate finance, Financial regulation, policy analysis, and central bank communication, Real estate finance and urban economics, Alternative data and high-dimensional financial datasets, Investor behavior, sentiment, and attention, Macroeconomic and financial risk forecasting.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>12th Annual ICGS Conference</t>
+          <t>2026 Summer Research Conference</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>HEC Montréal (Quebec, Canada)</t>
+          <t>Indian School of Business, Hyderabad Campus</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3570,145 +3594,145 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Behavioral perspectives on governance, Institutional and political approaches to governance, Implications of AI adoption for governance, Evolving forms of activism/engagement, Reconfiguration of governance systems under geopolitical crises, Governance mechanisms for managing state-firm relations</t>
+          <t>Recent Advances in Finance, corporate finance, asset pricing, behavioral finance, financial intermediation, household finance, market microstructure</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Vienna Festival of Finance Theory 2026</t>
+          <t>International Risk Management Conference 2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Vienna, Austria</t>
+          <t>Warsaw, Poland</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>65 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Corporate finance theory, financial intermediation theory</t>
+          <t>Asset pricing; Banking; Financial econometrics; Capital markets; Financial intermediation; Corporate finance; Financial crises; Corporate governance; Market microstructure; Financial regulation; International corporate finance; Risk management; Emerging market; Corporate investment decision; Global risk markets; Macro-financial linkages; Financial policy securitization; Behavioural finance; Financial integration; Mathematical &amp; computational finance; Stochastic optimization approaches in finance; Mergers &amp; acquisitions; Modelling, money and liquidity; Sustainable finance; Climate change risk; AI innovation; crypto and related assets and technology.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11th (2026) Cross Country Perspectives in Finance (CCPF) Conference</t>
+          <t>Second USTC Frontiers in Finance Conference</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>both online and on-site (Nanjing, China)</t>
+          <t>International Finance Institute, University of Science and Technology of China, No. 1789 Guangxi Road, Binhu New District, Hefei City, Anhui Province, P.R. China</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 CNY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>credit, banking, asset pricing, market liquidity, corporate finance, corporate governance, entrepreneurial finance in an international context</t>
+          <t>All topics of finance</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6th Annual Bristol Financial Markets Conference</t>
+          <t>Fischer-Shain Research Conference 2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bristol, UK</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Skill, performance, and evaluation in delegated portfolio management; The rise of passive investment and its effects on financial markets; New developments and trends in delegation: ESG / thematic/private markets; Machine learning and AI in asset management; Textual analysis and news coverage in delegated investment decisions; The role of index providers in delegated portfolio management</t>
+          <t>financial intermediation, banking, financial services</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Inaugural CEIBS-APS Centre for Financial Markets (CAC) Academic Conference</t>
+          <t>ECB Money Market Conference 2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>China Europe International Business School (CEIBS), Shanghai, China</t>
+          <t>European Central Bank, Frankfurt am Main, Germany</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3718,34 +3742,34 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>asset pricing, macro-finance, impact of institutional features on capital market dynamics</t>
+          <t>Money markets and monetary policy implementation; Money markets and technological innovation (stable coins, CBDCs, instant payments, AI impacts); The functioning of money markets (role of non-bank financial institutions, funding strategies, effects of central clearing, macroeconomic implications of volatile short-term rates and geopolitical developments)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dauphine Finance PhD Workshop</t>
+          <t>Finance in the Digital Age (FiDA) Workshop</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Paris, France</t>
+          <t>Calgary, Canada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3755,34 +3779,34 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Papers in all areas of Finance and Financial Economics</t>
+          <t>AI, DeFi, robo-advisors, neurofinance</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14th Helsinki Finance Summit on Investor Behavior</t>
+          <t>7th LTI@UniTO/Bank of Italy Workshop on Long-term investors’ trends: theory and practice</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Helsinki/Espoo, Finland</t>
+          <t>Bank of Italy, Rome, Italy</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3792,219 +3816,219 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Investor behavior, Behavior of different investor types, Market microstructure and investor trading behavior, Behavioral biases and performance of investment strategies, Household consumption, borrowing, saving, and portfolio choice, Investor education, financial literacy, and sophistication, Behavior of finance professionals and the impact of professional advice, Biological, psychological, and cultural foundations of investor behavior, The influence of analysts, media, and news coverage on investment decisions, Social influence and networks in finance, Impact of investor behavior on corporate policies and decision-making</t>
+          <t>Long-term investors’ strategies and behavior, long-term investors’ role in financing the real economy, shifting equilibria in government bond markets, evolution of sustainable investment strategies, challenges for long-term investors from equity market concentration, non-bank investors in credit intermediation, rise of cryptocurrencies and fintech, emerging trends in asset allocation and risk management, shock transmission mechanisms in financial institutions, use of big data and AI in investment processes, innovations in financial markets, geopolitical risks' effect on banks vs. non-banks, effects of demographic transitions on financial markets</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026 Clemson Finance Research Conference</t>
+          <t>7th Annual RCF-ECGI Corporate Finance and Governance Conference</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Clemson, SC</t>
+          <t>Madrid, Spain, and virtually</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>75 USD</t>
+          <t>€350 in person (for conference dinner, lunches, and coffee breaks), €50 online option (for administrative / tech support)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>corporate finance, asset pricing, investment, banking, asset management, household finance, labor economics, behavioral finance, Fintech, real estate</t>
+          <t>capital structure, corporate and securities law, corporate culture, corporate failure, corporate finance and public policy, corporate governance, corporate restructuring, corporate social responsibility, crowdfunding, dividends, payout policy, repurchases, entrepreneurial finance, family business, financial contracting, financial intermediation, financial literacy, fintech, fraud, innovation, IPOs and SEOs, mergers and acquisitions, misconduct, private debt, private equity, trade credit, socially responsible investments, sustainable finance, real options, venture capital</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Politics in Finance 2026 Conference</t>
+          <t>Fintech and Financial Institutions Research Conference</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>McDonough School of Business, Rafik B. Hariri Building 37th and O Streets, N.W Washington, D.C. 20057 USA</t>
+          <t>Federal Reserve Bank of Philadelphia, Philadelphia, PA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>The role of political connections and political ideologies in shaping capital market forces; How political ideologies affect the decision making by firms and workers; Political connections and corruption in developing economies; The political economy of financial development; The interaction between government and financial institutions; Implications of political uncertainty and political connections for asset prices and corporate policies; Political economy of financial regulation and financial crises</t>
+          <t>Interlinkages of the fintech sector and the broader financial system, economic consequences and impacts of the fintech sector, regulatory implications of the fintech sector</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>11th SDU Finance Workshop on Corporate Finance -- Dynamics, Uncertainty, and Strategic Decisions</t>
+          <t>Aarhus Finance Forum 2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>University of Southern Denmark (SDU), Odense, Denmark</t>
+          <t>Aarhus, Denmark</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>300 DKK (approx. 40 EUR)</t>
+          <t>375 DKK</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Corporate Finance -- Dynamics, Uncertainty, and Strategic Decisions</t>
+          <t>Financial Decisions under Uncertainty and Ambiguity, Household Finance, Real Estate Finance, Corporate Finance, Climate Finance, Digital Finance, Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Northern Finance Association 2026 Annual Meeting</t>
+          <t>15th CDI Conference on Derivatives</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Quebec City, Canada</t>
+          <t>Montreal, Canada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Canadian $75 (about US $55)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Topics from all areas of finance including asset pricing, corporate finance, financial intermediation, investments, Canadian financial markets, insurance, household finance, sustainable finance, fintech and AI</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>London Business School 2026 Summer Finance Symposium</t>
+          <t>Conference on CSR, the Economy and Financial Markets</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-11-05</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-11-06</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>London Business School</t>
+          <t>Düsseldorf, Germany</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>£50 GBP</t>
+          <t>€ 150 for regular participants, € 100 for PhD students</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Papers from all areas of finance</t>
+          <t>Climate risk and pricing, Role of financial markets, banks, institutional investors in CSR, Effects of CSR on valuation, performance, cost of capital, funding and capital structure, Socio-economic aspects and their implications for companies and financial markets, Corporate governance and CSR, Risk management and CSR, CSR reporting and disclosure, ESG backlash and politicization, Sustainability strategy under new constraints, Measurement of ESG indices, CSR activities and the economy</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>International Conference on Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF 2026)</t>
+          <t>Vietnam Symposium on Global Economy (VSGE2026)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Ho Chi Minh City, Vietnam</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4014,34 +4038,34 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Climate Finance, Artificial Intelligence (AI) and Machine Learning in Finance and Accounting, Green Finance, Sustainable Finance, ESG Reporting, and Climate Risk, FinTech, Blockchain, and Digital Currencies, Corporate Governance and Technological Innovation, Big Data in Accounting and Finance, Green Accounting and Carbon Disclosure, RegTech and Financial Compliance, Data Analytics and Financial Decision-Making, Digital Transformation in Public Sector Accounting, Ethical Implications of AI and Automation in Financial Services, Evolving Accounting Standards in Response to Sustainability/Technology</t>
+          <t>Geopolitical, macroeconomic policy, trade and foreign direct investment, climate change and public finance, finance and sustainable investment, digitalization, urbanization, AI's economic impacts, global governance</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>11th International Conference on Accounting and Finance (ICOAF-2026)</t>
+          <t>21st Annual Conference on Asia-Pacific Financial Markets (CAFM)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-12-10</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-12-11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Danang, Vietnam</t>
+          <t>CONRAD Seoul</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4051,34 +4075,34 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>All areas of Accounting, Finance, and Banking, encompassing both theoretical and empirical studies</t>
+          <t>All areas of finance</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Liechtenstein Workshop on AI in Finance 2026</t>
+          <t>India Finance Conference (IFC) 2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-12-23</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vaduz, Liechtenstein</t>
+          <t>Indian Institute of Management Bangalore</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4088,34 +4112,34 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>forecasting financial variables with AI, asset allocation and asset management with AI, AI-based factor models, natural language processing and large language models in finance, AI applications in corporate finance</t>
+          <t>Theoretical and empirical asset pricing, Corporate finance, capital structure and dividend policy, Asset allocation and investment management, Financial crises, systemic risk and macro-finance, Quality of financial reporting and adoption of IFRS, Corporate governance, executive compensation and ownership structure, Computational finance and financial econometrics, Financial Econometrics, Financial risk analytics and management, Market microstructure and algorithmic trading, Financial policy choice, institutions and regulation, Financial Analytics, ESG, Climate Finance, Blended Finance, Insurance / Reinsurance / Pension Funds, Enhancing liquidity in commodity derivatives markets, Financial Literacy and Financial Education</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3rd Modern Finance Conference (MFC 2026)</t>
+          <t>Edinburgh Financial Technology Conference</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Krakow, Poland</t>
+          <t>Edinburgh</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4125,71 +4149,71 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Asset pricing and valuation, Banking and financial services, Behavioral finance and decision making, Capital structure, Corporate finance, Corporate governance, Cryptocurrencies, Derivatives, Economic development, Exchange rates and currency markets, Finance and accounting standards, Financial econometrics and quantitative methods, Financial markets and instruments, Financial, management, and tax accounting, Financial regulation and supervisions, Financial stability, Fintech and financial innovation, Green finance, Investment and portfolio management, Insurance, Market microstructure, Mergers and acquisitions, Microfinance, Monetary policy and central banking, Risk management, Sustainable finance and responsible investment</t>
+          <t>The application of AI and Machine Learning in finance; The application of distributed ledger technologies in finance; Cryptofinance; Cyber risk in finance; The microstructure of modern financial markets (algorithmic/high frequency trading, dark trading, blockchain settlements, etc.); Behavioural economics in financial technology; Alternative data (structured and unstructured datasets); Crowdsourcing and investment strategy; New exchange traded financial derivatives; Financial stability risks from the development of FinTech; RegTech; Open banking</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>First University of Maryland/Singapore Management University/UBS Quant Investment Forum: AI and Finance</t>
+          <t>5th Conference in Sustainable Finance</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>University of Luxembourg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>95 SGD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>AI for Investments &amp; Asset Pricing, Alternative Data and Investment Insights, Portfolio &amp; Risk Management, Algorithmic Trading &amp; Market Impact</t>
+          <t>any topic in sustainable finance</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026 City University of Hong Kong International Finance Conference</t>
+          <t>7th CEAR-RSI Household Finance Workshop</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-11-14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>City University of Hong Kong</t>
+          <t>HEC Montréal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4199,71 +4223,71 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Corporate Finance, Asset Pricing</t>
+          <t>Consumption-saving decisions and investment choices, Financial literacy and education, Pensions and retirement, Financial planning and advice, Financial delinquency and bankruptcy, Household insurance and risk management</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026 Research Summer Workshop on Regulated Funds and Retail-oriented Investment Products</t>
+          <t>Next-Gen AI and Autonomous Finance (NGAI) workshop</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Washington, DC, USA</t>
+          <t>Rennes School of Business, Rennes, France</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Regulated funds, retail-oriented investment products, mutual fund industry</t>
+          <t>Autonomous agents &amp; decision-making in finance; AI-driven trading, portfolio optimization &amp; market microstructure; Risk, robustness, and model governance; Ethics, fairness, transparency &amp; societal impacts of financial AI; Financial decision making and AI; Bias and stereotyping in relation to AI driven finance; AI, money and financial value formation</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026 Vietnam Symposium in Entrepreneurship, Finance, and Innovation</t>
+          <t>12th Annual ICGS Conference</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>HEC Montréal (Quebec, Canada)</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4273,77 +4297,125 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>AI, Big Data, and Machine Learning Applications in Finance; Asset Pricing; Bankruptcy and Liquidation; Biodiversity Finance; Climate Finance; Corporate Finance and Governance; Corporate Responsibility and Sustainability; Crypto Assets, Blockchain, and Decentralized Finance; Electronic Markets, Trading Platforms, and Market Microstructure; ESG and Sustainable Finance; Financial Markets; Household Finance; Information Disclosure, Market Efficiency, and Transparency; Portfolio and Investment Decisions; FinTech, Alternative Finance, and Digital Financial Infrastructure; Tokenomics, Digital Currencies, and Payment Systems; Business Model Innovation and Corporate Digital Transformation; Digital Innovation, Knowledge Management, and Innovation Systems; Digital Human Resources and the Future of Work; Innovation Management and Growth Strategies; Innovation and Industrial Policy; Institutions, Regulation, and Innovation Systems; Science, R&amp;D, and the Economics of Knowledge Creation; Sustainability in the Digital Economy; Crowdfunding, Peer-to-Peer Lending, and Platform-Based Finance; Entrepreneurship, Intrapreneurship, and Innovation; Entrepreneurship in Emerging and Transition Markets; Family-Owned Businesses and Governance; Governance and Financing of High-Tech Firms; New Venture Creation and Performance; Social and Sustainable Entrepreneurship; Startups, SMEs, and Resource Allocation; Venture Financing and Entrepreneurial Growth</t>
+          <t>Behavioral perspectives on executives, boards, investors, and other governance actors; Institutional and political approaches to governance; Implications of AI adoption for governance; Evolving forms of activism/engagement; Reconfiguration of governance systems under geopolitical crises; Governance mechanisms for managing state-firm relations.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>I apologize, but it seems that you haven't provided the text of the announcement. Please share the text, and I'll be happy to extract the required information for you.</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+          <t>Vienna Festival of Finance Theory 2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Vienna, Austria</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>65 EUR</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Corporate finance theory, financial intermediation theory</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Bridging Theory and Empirical Research in Finance</t>
+          <t>The 11th (2026) Cross Country Perspectives in Finance (CCPF) Conference</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Boston College</t>
+          <t>both online and on-site (Nanjing, China)</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>$50 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>corporate finance, corporate governance, financial intermediation, agency and delegation, information and securities, financial markets</t>
+          <t>credit, banking, asset pricing, market liquidity, corporate finance, corporate governance, entrepreneurial finance</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>It appears that the text of the announcement was not included in your message. Please provide the text of the call for papers so I can extract the required information for you.</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+          <t>6th Annual Bristol Financial Markets Conference</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Bristol, UK</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>0 GBP</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Skill, performance, and evaluation in delegated portfolio management; The rise of passive investment and its effects on financial markets; New developments and trends in delegation: ESG / thematic/private markets; Machine learning and AI in asset management; Textual analysis and news coverage in delegated investment decisions; The role of index providers in delegated portfolio management</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Bank of Finland and CEPR Joint conference on Navigating Monetary Policy by the Northern Lights</t>
+          <t>Inaugural CEIBS-APS Centre for Financial Markets (CAC) Academic Conference</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4353,17 +4425,17 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-12-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-12-18</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Saariselkä, Lapland</t>
+          <t>China Europe International Business School (CEIBS), Shanghai, China</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4373,34 +4445,34 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Monetary Policy Transmission, Inflation Dynamics and Expectations; Heterogeneity in Macro and Monetary Economics Models; Monetary-Fiscal Interactions; Technological Advances, Financial Market Developments, and Central Banks; Geopolitical Shocks and Monetary Policy; Central bank credibility and independence</t>
+          <t>asset pricing, macro-finance, the impact of institutional features on capital market dynamics</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026 FIRN/UQ Asset Management Meeting</t>
+          <t>Dauphine Finance PhD Workshop</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Brisbane, Australia</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4410,34 +4482,34 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>asset management, FinTech, mutual funds, hedge funds, pension funds, ETFs, alternative investments, data assets/markets, digital finance, platform finance, financial technology, artificial intelligence, big data in asset management</t>
+          <t>Papers in all areas of Finance and Financial Economics</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>World Finance &amp; Banking Symposium</t>
+          <t>14th Helsinki Finance Summit on Investor Behavior</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-12-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-12-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>University of Latvia, Riga</t>
+          <t>Helsinki/Espoo, Finland</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4447,219 +4519,219 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>All areas of finance, economics, and banking</t>
+          <t>Investor behavior, behavior of different investor types, market microstructure and investor trading behavior, behavioral biases and performance of investment strategies, household consumption, borrowing, saving, and portfolio choice, investor education, financial literacy, and sophistication, behavior of finance professionals and the impact of professional advice, biological, psychological, and cultural foundations of investor behavior, influence of analysts, media, and news coverage on investment decisions, social influence and networks in finance, impact of investor behavior on corporate policies and decision-making</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Research Symposium on Finance and Economics (RSFE) 2026</t>
+          <t>2026 Clemson Finance Research Conference</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Krea University, Andhra Pradesh, India</t>
+          <t>Clemson, SC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Finance, Economics</t>
+          <t>corporate finance, asset pricing, investment, banking, asset management, household finance, labor economics, behavioral finance, Fintech, real estate</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Annual Meeting of the Central Bank Research Association CEBRA</t>
+          <t>Politics in Finance 2026 Conference</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>McDonough School of Business, Rafik B. Hariri Building 37th and O Streets, N.W Washington, D.C. 20057 USA</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$75 USD</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Monetary Policy Transmission, Expectations, and Communication, Inflation and Price Dynamics, Macro-Finance and Financial Stability, Fiscal–Monetary Interactions and Policy Making, International Macroeconomics, Trade, and Geoeconomics, Firms, Productivity, and the Real Economy, Data, Methods, and Artificial Intelligence</t>
+          <t>The role of political connections and political ideologies in shaping capital market forces; How political ideologies affect the decision making by firms and workers; Political connections and corruption in developing economies; The political economy of financial development; The interaction between government and financial institutions; Implications of political uncertainty and political connections for asset prices and corporate policies; Political economy of financial regulation and financial crises</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>IBEFA Annual Meeting at the 2027 ASSA Conference</t>
+          <t>11th SDU Finance Workshop on Corporate Finance</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2027-01-03</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2027-01-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Washington, DC</t>
+          <t>University of Southern Denmark (SDU), Odense, Denmark</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>US$100 per paper; US$75 for papers solely authored by PhD students</t>
+          <t>300 DKK (approx. 40 EUR)</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>banking; financial risk measurement and management; non-bank financial intermediation and private credit; FinTech; the role of AI in financial intermediation; geo-economic fragmentation and capital flows; sustainable finance; household finance; financial market structure and regulation; monetary policy</t>
+          <t>Corporate Finance -- Dynamics, Uncertainty, and Strategic Decisions</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CSEF- CEPR Conference on Labor and Finance</t>
+          <t>Northern Finance Association 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Villa Orlandi Conference Centre, University of Naples Federico II, Capri (Italy)</t>
+          <t>Quebec City, Canada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Canadian $75 (about US $55) per paper</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Interaction between financial and labor markets, technological innovation, job-skill matches, firms’ employment policies, role of employees in governance and financing of companies, responses of wages, employment, and career trajectories to shocks, risk-sharing arrangements between firms and workers</t>
+          <t>Topics from all areas of finance including asset pricing, corporate finance, financial intermediation, investments, with special interest in Canadian financial markets, insurance, household finance, sustainable finance, fintech, and AI</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Happy Valley Finance Conference</t>
+          <t>London Business School 2026 Summer Finance Symposium</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>State College, PA</t>
+          <t>London Business School</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£50 GBP</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Papers from all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3rd CEPR-SAFE Frankfurt Hub Conference of RPNs</t>
+          <t>Sustainability, Technology, and the Transformation of Accounting and Finance (STTAF26)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>House of Finance, Campus Westend, Frankfurt, Germany</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4669,34 +4741,34 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Fintech and Financial Institutions, Regulatory framework revisions, CBDC blockchains and stablecoins, Sovereign bonds and sovereign bond capital regulation, Payment systems and European sovereignty, Safe assets and exchange rate dynamics under world polarization, Private credit and financial stability, Climate regulation U-turn and implications for climate finance, Defence policy needs and European financial architecture</t>
+          <t>Climate Finance, Artificial Intelligence (AI) and Machine Learning in Finance and Accounting, Green Finance, Sustainable Finance, ESG Reporting, and Climate Risk, FinTech, Blockchain, and Digital Currencies, Corporate Governance and Technological Innovation, Big Data in Accounting and Finance, Green Accounting and Carbon Disclosure, RegTech and Financial Compliance, Data Analytics and Financial Decision-Making, Digital Transformation in Public Sector Accounting, Ethical Implications of AI and Automation in Financial Services, Evolving Accounting Standards in Response to Sustainability/Technology</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Conference on The Industrial Organization of Financial Markets</t>
+          <t>11th International Conference on Accounting and Finance (ICOAF-2026)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>SKEMA Business School, Sophia Antipolis (Nice) campus, France</t>
+          <t>Danang, Vietnam</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4706,145 +4778,145 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>market structure and competition, innovation and strategic behavior in the organization of the financial markets, payment card industry, lending and digital banking, primary and secondary markets for equity, government debt and corporate debt, financial regulation and competition policy, interbank lending markets, retail funding markets, credit markets, including mortgages</t>
+          <t>Accounting, Finance, and Banking</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Fourteenth Oxford Financial Intermediation Theory Conference (OxFIT)</t>
+          <t>Liechtenstein Workshop on AI in Finance 2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Saïd Business School, University of Oxford</t>
+          <t>Vaduz, Liechtenstein</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>£65 GBP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Financial crises, Governance of financial institutions, The role of central banks and regulators, Financial innovation, International regulatory coordination, Certification in financial markets</t>
+          <t>forecasting financial variables with AI, asset allocation and asset management with AI, AI-based factor models, natural language processing and large language models in finance, AI applications in corporate finance</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>University of Washington 7th Summer Finance Conference</t>
+          <t>3rd Modern Finance Conference (MFC 2026)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Seattle, Washington</t>
+          <t>Krakow, Poland</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>80 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Asset pricing and valuation, Banking and financial services, Behavioral finance and decision making, Capital structure, Corporate finance, Corporate governance, Cryptocurrencies, Derivatives, Economic development, Exchange rates and currency markets, Finance and accounting standards, Financial econometrics and quantitative methods, Financial markets and instruments, Financial, management, and tax accounting, Financial regulation and supervision, Financial stability, Fintech and financial innovation, Green finance, Investment and portfolio management, Insurance, Market microstructure, Mergers and acquisitions, Microfinance, Monetary policy and central banking, Risk management, Sustainable finance and responsible investment</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>4th Tilburg Finance Summit</t>
+          <t>The First University of Maryland/Singapore Management University/UBS Quant Investment Forum: AI and Finance</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tilburg, Netherlands</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>95 SGD</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Asset Pricing, Behavioral Finance</t>
+          <t>AI for Investments &amp; Asset Pricing, Alternative Data and Investment Insights, Portfolio &amp; Risk Management, Algorithmic Trading &amp; Market Impact</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026 PHBS–IER conference on “Technology, Innovation, Platforms, and Economic Performance”</t>
+          <t>2026 City University of Hong Kong International Finance Conference</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-12-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-12-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Peking University HSBC Business School, Shenzhen, China</t>
+          <t>City University of Hong Kong</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4854,71 +4926,71 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Innovation, Technology Emergence, and Technology Transfer; Technology Adoption, Diffusion, and Automation; Resource Reallocation, Productivity, and Aggregate Dynamics; Geoeconomics and Technology Policy: Fragmentation, Trade, and Innovation; Trading Platforms and Digital Markets: Design, Competition, and Information; Institutions, Finance, Digital Payments, and Regulation in the Digital Economy</t>
+          <t>Corporate Finance, Asset Pricing</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>7th Canadian Sustainable Finance Network Conference</t>
+          <t>2026 Research Summer Workshop on Regulated Funds and Retail-oriented Investment Products</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Alberta School of Business, University of Alberta, Edmonton, Canada</t>
+          <t>Washington, DC, USA</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sustainable finance and the intersection of corporate governance and sustainability</t>
+          <t>Regulated funds, retail-oriented investment products, mutual fund industry</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026 Global Finance Conference</t>
+          <t>2026 Vietnam Symposium in Entrepreneurship, Finance, and Innovation</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>University of Azores, Portugal</t>
+          <t>Hanoi, Vietnam</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4928,219 +5000,219 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Energy, Sustainability, Fintech including AI, Climate change, Alternative Investments, Asset &amp; Wealth Management, Asset Allocation/Sovereign Funds/Hedge Funds/ETFs/SWFs, Banking &amp; Financial Services, Corporate Governance/Executive Compensation, Country Risk/Debt Issues/Insurance/Reinsurance, Derivatives/Financial Engineering, E-Business/E-Finance/Social Media, Emerging Markets/BRICS, Entrepreneurship/Venture Capital Global Perspectives, Ethics/Legal/Regulatory, Financial Crises and Bubbles, Financial Technology including AI, Foreign Currency Issues, Future of Global Economy, Global Trade Issues, IPOs/SEOs/Stock buybacks/Privatization, Market Behavior Efficiency/Inefficiency, Mergers and Acquisitions, Non-Traditional Banking &amp; Financial Services, Portfolio Flows and Foreign Direct Investment, Private Equity, Real estate - global perspectives, Valuation, Portfolio Management and Managing Financial Risk</t>
+          <t>AI, Big Data, and Machine Learning Applications in Finance; Asset Pricing; Bankruptcy and Liquidation; Biodiversity Finance; Climate Finance; Corporate Finance and Governance; Corporate Responsibility and Sustainability; Crypto Assets, Blockchain, and Decentralized Finance; Electronic Markets, Trading Platforms, and Market Microstructure; ESG and Sustainable Finance; Financial Markets; Household Finance; Information Disclosure, Market Efficiency, and Transparency; Portfolio and Investment Decisions; FinTech, Alternative Finance, and Digital Financial Infrastructure; Tokenomics, Digital Currencies, and Payment Systems; Business Model Innovation and Corporate Digital Transformation; Digital Innovation, Knowledge Management, and Innovation Systems; Digital Human Resources and the Future of Work; Innovation Management and Growth Strategies; Innovation and Industrial Policy; Institutions, Regulation, and Innovation Systems; Science, R&amp;D, and the Economics of Knowledge Creation; Sustainability in the Digital Economy; Crowdfunding, Peer-to-Peer Lending, and Platform-Based Finance; Entrepreneurship, Intrapreneurship, and Innovation; Entrepreneurship in Emerging and Transition Markets; Family-Owned Businesses and Governance; Governance and Financing of High-Tech Firms; New Venture Creation and Performance; Social and Sustainable Entrepreneurship; Startups, SMEs, and Resource Allocation; Venture Financing and Entrepreneurial Growth</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Bayes Junior Asset Management and Asset Pricing Workshop</t>
+          <t>12th IWH-FIN-FIRE Workshop on “Challenges to Financial Stability”</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bayes Business School, London</t>
+          <t>Halle Institute for Economic Research (IWH), Halle/Saale Germany</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>£50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Asset management, asset pricing, papers bridging both areas</t>
+          <t>regulation and financial intermediation, corporate finance, law, politics and finance, monetary policy, inflation and financial resilience, macroprudential policy and real estate, financial networks and systemic risk, pricing of climate risk in financial markets, ecological hazards and the behaviour of firms and households, governance of financial firms and markets, private credit and risk transfer</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Second Annual Notre Dame Investment Management Conference</t>
+          <t>Bridging Theory and Empirical Research in Finance</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>University of Notre Dame - Notre Dame, Indiana</t>
+          <t>Boston College</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>USD 70</t>
+          <t>$50</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Demand Based Asset Pricing, Inelastic Markets Hypothesis, New Methods in Asset Pricing (Machine Learning, Artificial Intelligence (AI), unstructured data), Time series and Cross-Sectional Predictability, Portfolio Allocation for Long Term Investors, Retirement decisions and choices, Behavioral finance</t>
+          <t>corporate finance, corporate governance, financial intermediation, agency and delegation, information and securities, financial markets</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Future Finance Fest (3f)</t>
+          <t>11th Bank of Finland and European Systemic Risk Board Joint Conference on AI and Systemic Risk Analytics</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Bank of Finland, Helsinki</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>0 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>AI, asset pricing, banking, behavioral finance, big data, blockchain, CBDCs, compliance, crowdfunding, cryptocurrencies, cybersecurity, decentralized finance, digital finance, embedded finance, fintech, financial infrastructure, financial inclusion, financial innovation, financial intermediation, financial markets, household finance, insurtech, machine learning, market microstructure, payments, platforms, regulation, risk management, stablecoins, tokenization, text analytics.</t>
+          <t>Use of Large Language Models (LLM) and trustworthy AI, AI and changing interdependencies in the financial markets, Cyber security and operational risks as sources of systemic risk, AI and Quantum Computing as potential source of new systemic risks, Use of AI with big data for systemic risk analytics, Risks and opportunities stemming from disruptive innovations in financial technology (FinTech), Analysing emerging risks from interconnectedness of the financial system, Identifying risks from market-based finance, Modelling geopolitical risks, Using systemic risk analytics to support macro-prudential policy and regulation, Evidence of macroprudential policy measures</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026 FMA Applied Finance Conference</t>
+          <t>Bank of Finland and CEPR Joint conference on Navigating Monetary Policy by the Northern Lights</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-12-17</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-12-18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>St. John's University - Manhattan Campus, New York, NY</t>
+          <t>Saariselkä, Lapland</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>$50 USD (FMA-members), $60 USD (non-members)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Inform practice and advance the frontiers of academic research in directions relevant to practice; Address issues that are relevant to contemporary issues globally and for policy formation and assessment; Introduce new hypotheses that have the potential to stimulate additional research</t>
+          <t>Monetary Policy Transmission, Inflation Dynamics and Expectations; Heterogeneity in Macro and Monetary Economics Models; Monetary-Fiscal Interactions; Technological Advances, Financial Market Developments, and Central Banks; Geopolitical Shocks and Monetary Policy; Central bank credibility and independence</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Exeter Sustainable Finance Conference 2026</t>
+          <t>2026 FIRN/UQ Asset Management Meeting</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>University of Exeter Business School, Exeter, UK</t>
+          <t>Brisbane, Australia</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0 GBP</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Unpublished research papers on any topic related to sustainable finance, interdisciplinary research that draws together approaches and perspectives from different disciplines</t>
+          <t>asset management, FinTech, mutual funds, hedge funds, pension funds, ETFs, alternative investments, data assets/markets, digital finance, platform finance, financial technology, artificial intelligence, big data in asset management</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>9th Cryptocurrency Research Conference (CRC2026)</t>
+          <t>World Finance &amp; Banking Symposium</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-12-14</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-12-16</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>University of Latvia, Riga</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -5150,182 +5222,182 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cryptofinance, blockchain economics, digital finance, FinTech, corporate finance, entrepreneurship, alternative investments</t>
+          <t>All areas of finance, economics, and banking</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Accountability in a Sustainable World Conference</t>
+          <t>Research Symposium on Finance and Economics (RSFE) 2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>Krea University, Andhra Pradesh, India</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>$200 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Various topics in the field of finance and economics</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>33rd Finance Forum</t>
+          <t>Annual Meeting of the Central Bank Research Association CEBRA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Alicante, Spain</t>
+          <t>Copenhagen, Denmark</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>50 €</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Asset Pricing, Corporate Finance, Banking, Portfolio Choice and Asset Management, Microstructure, Regulation, Financial Stability, Macrofinance</t>
+          <t>Monetary Policy Transmission, Expectations, and Communication; Inflation and Price Dynamics; Macro-Finance and Financial Stability; Fiscal–Monetary Interactions and Policy Making; International Macroeconomics, Trade, and Geoeconomics; Firms, Productivity, and the Real Economy; Data, Methods, and Artificial Intelligence</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3rd Workshop on Recent Trends and New Developments in Sustainable, Green and International Finance</t>
+          <t>IBEFA Annual Meeting at the 2027 ASSA Conference</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2027-01-03</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2027-01-05</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>EDHEC Business School, Nice Campus, Nice, France</t>
+          <t>Washington, DC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>220 EUR (academics and professionals), 180 EUR (Ph.D. students)</t>
+          <t>US$100 per paper; US$75 for papers solely authored by PhD students</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sustainable finance, green finance, climate finance, international finance</t>
+          <t>banking; financial risk measurement and management; non-bank financial intermediation and private credit; FinTech; the role of AI in financial intermediation; geo-economic fragmentation and capital flows; sustainable finance; household finance; financial market structure and regulation; monetary policy</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Alpine Finance Summit (AFS) 2026</t>
+          <t>CSEF- CEPR Conference on Labor and Finance</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Garmisch-Partenkirchen, Germany</t>
+          <t>Villa Orlandi Conference Centre, University of Naples Federico II, Capri (Italy)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>50 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Asset Pricing, Investments, Sustainable Finance, FinTech</t>
+          <t>Interaction between financial and labor markets, technological innovation, job-skill matches, firms’ employment policies, role of employees in governance and financing of companies, responses of wages, employment, and career trajectories to shocks, risk-sharing arrangements between firms and workers</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>The 22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
+          <t>Happy Valley Finance Conference</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Busan, Korea</t>
+          <t>State College, PA</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5335,34 +5407,34 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
+          <t>all areas of finance</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NBER-SAIF Conference on AI and Financial Markets</t>
+          <t>3rd CEPR-SAFE Frankfurt Hub Conference of RPNs</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Virtual</t>
+          <t>House of Finance, Campus Westend, Frankfurt, Germany</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5372,14 +5444,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>The impact of investment in AI and supporting technologies on corporate earnings and share prices; effects of AI on portfolio choices and trading behavior of financial market participants; role of AI in creating new measures of economic activity; uses of AI in financial market regulation; consequences of AI for the financial advice industry; macroeconomic effects of AI on economy-wide discount rates</t>
+          <t>Fintech and Financial Institutions, Regulatory framework revisions, CBDC blockchains and stablecoins, Sovereign bonds and sovereign bond capital regulation, Payment systems and European sovereignty, Safe assets and exchange rate dynamics under world polarization, Private credit and financial stability, Climate regulation U-turn and implications for climate finance, Defence policy needs and European financial architecture</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>12th Workshop on Banking and Institutions</t>
+          <t>Conference on The Industrial Organization of Financial Markets</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5389,17 +5461,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bank of Finland, Helsinki</t>
+          <t>SKEMA Business School, Sophia Antipolis (Nice) campus, France</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5409,14 +5481,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>geopolitics and banking, political economy of banking, banking and society, banking in emerging markets, climate and banking, monetary policy and institutions</t>
+          <t>market structure and competition, innovation and strategic behavior in the organization of the financial markets, payment card industry, lending and digital banking, primary and secondary markets for equity, government debt and corporate debt, financial regulation and competition policy, interbank lending markets, retail funding markets, credit markets, including mortgages</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ENTFIN 2026 Conference</t>
+          <t>Fourteenth Oxford Financial Intermediation Theory Conference (OxFIT)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5426,91 +5498,91 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kedge Business School, Marseille, France</t>
+          <t>Saïd Business School, University of Oxford</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£65</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Venture capital; private equity, and buyouts; Business angels and early-stage financing; Crowdfunding; token offerings, and digital finance; Entrepreneurial banking and credit relationships; Corporate governance, contracts, and monitoring; Financial innovation; FinTech, and AI in entrepreneurial finance; ESG, sustainability, and impact finance; Entrepreneurial ecosystems and regional financing gaps; Entrepreneurial risk-taking and behavioral finance; Impact assessment for publicly supported financial instruments</t>
+          <t>Financial crises, Governance of financial institutions, The role of central banks and regulators, Financial innovation, International regulatory coordination, Certification in financial markets</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>9th Short-Term Funding Markets Conference</t>
+          <t>University of Washington 7th Summer Finance Conference</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Federal Reserve Board, Washington, D.C.</t>
+          <t>Seattle, Washington</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>0 USD</t>
+          <t>80 USD</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Maturity and liquidity transformation, Repo markets and their clearing institutions, Theories of frictions and fragility in short-term funding markets, Effects of regulation and central bank intervention on funding markets, Securities lending, Money creation and the demand for safe assets, Fintech and encrypted currency</t>
+          <t>All areas of finance, with encouragement for submissions from junior faculty and preliminary papers</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>21st Central Bank Conference on the Microstructure of Financial Markets</t>
+          <t>4th Tilburg Finance Summit</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Eltville am Rhein, Germany</t>
+          <t>Tilburg, Netherlands</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5520,108 +5592,108 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Artificial intelligence and market microstructure, The functioning and resilience of sovereign bond and repo markets</t>
+          <t>Asset Pricing and Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026 PRIVATE EQUITY RESEARCH CONSORTIUM (PERC) EUROPE SYMPOSIUM</t>
+          <t>2026 PHBS–IER conference on “Technology, Innovation, Platforms, and Economic Performance”</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-12-20</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-12-21</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Oxford, England</t>
+          <t>Peking University HSBC Business School, Shenzhen, China</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
+          <t>Innovation, Technology Emergence, and Technology Transfer; Technology Adoption, Diffusion, and Automation; Resource Reallocation, Productivity, and Aggregate Dynamics; Geoeconomics and Technology Policy: Fragmentation, Trade, and Innovation; Trading Platforms and Digital Markets: Design, Competition, and Information; Institutions, Finance, Digital Payments, and Regulation in the Digital Economy</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lake District Workshop in Corporate Finance</t>
+          <t>7th Canadian Sustainable Finance Network Conference</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Windermere, Lake District, United Kingdom</t>
+          <t>Alberta School of Business, University of Alberta, Edmonton, Canada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>£60 GBP</t>
+          <t>0 CAD</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Corporate Finance</t>
+          <t>sustainable finance and the intersection of corporate governance and sustainability</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>8th Annual Workshop on Financial Institutions Research</t>
+          <t>2026 Global Finance Conference</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Gateway Conference Center, Federal Reserve Bank of St. Louis; St. Louis, MO USA</t>
+          <t>University of Azores, Portugal</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5631,108 +5703,108 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bank Regulation, Supervision, and Compliance; Bank Risk-taking, Stability, and Financial Crises; Lending and Credit Allocation; Bank Governance, Ownership, and Compensation; Bank Disclosure, Accounting, and the Information Environment; Deposits, Funding Structure, and Liability Management; Financial Technology, Innovation, and Bank Competition</t>
+          <t>Energy, Sustainability, Fintech including AI, Climate change, Alternative Investments, Asset &amp; Wealth Management, Asset Allocation/Sovereign Funds/Hedge Funds/ETFs/SWFs, Banking &amp; Financial Services – Integrations – Linkages, Corporate Governance/Executive Compensation, Country Risk/Debt Issues/Insurance/Reinsurance, Derivatives/Financial Engineering, E-Business/E-Finance/Social Media, Emerging Markets/BRICS, Entrepreneurship/Venture Capital Global Perspectives, Ethics/Legal/Regulatory, Accounting, Auditing and Taxation Issues, Financial Crises and Bubbles: Causes/Impacts/Solutions, Financial Technology including AI, ML &amp; Financial Information Systems, Foreign Currency Issues – Global Multi-Currency System, Future of Global Economy- Imbalances, Sustainability, CSR, Climate Issues, Global Trade Issues – Free Trade – Trade Barriers &amp; Protections, IPOs/SEOS/Stock buybacks/Privatization, Market Behavior Efficiency/Inefficiency, Mergers and Acquisitions/Corporate and State SWFs, Non-Traditional Banking &amp; Financial Services, Portfolio Flows and Foreign Direct Investment, Private Equity, Real estate - global perspectives, Valuation, Portfolio Management and Managing Financial Risk</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Southern Finance Association 2026 Annual Meeting</t>
+          <t>Bayes Junior Asset Management and Asset Pricing Workshop</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-11-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>LaQuinta Resort, Palm Springs, CA</t>
+          <t>Bayes Business School, London</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>50 USD</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Papers on any area of finance, proposals for panel discussions, special sessions, or tutorials</t>
+          <t>Asset management, Asset pricing</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>International Accounting &amp; Finance Doctoral Symposium (IAFDS)</t>
+          <t>Second Annual Notre Dame Investment Management Conference</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cagliari, Sardinia, Italy</t>
+          <t>University of Notre Dame - Notre Dame, Indiana</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>£300</t>
+          <t>USD 70</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Original empirical and theoretical papers in accounting and finance, with a focus on significant and impactful issues within these fields</t>
+          <t>Demand Based Asset Pricing, Inelastic Markets Hypothesis, New Methods in Asset Pricing (Machine Learning, Artificial Intelligence (AI), unstructured data), Time series and Cross-Sectional Predictability, Portfolio Allocation for Long Term Investors, Retirement decisions and choices, Behavioral finance</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>13th Annual Conference on Risk Governance</t>
+          <t>Future Finance Fest (3f)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>University of Siegen, Siegen/Germany</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5742,209 +5814,209 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Risk Governance in the boardroom, Risk Governance and the monitoring role of supervisory boards, Balancing risk and opportunity, Stakeholder influence on board decision-making, Sustainability and Risk Governance, Understanding black swans, Strategic resilience, Considering risk strategies on bank boards, Tackling digitalization-related risks, The role of artificial intelligence for board decisions</t>
+          <t>AI, asset pricing, banking, behavioral finance, big data, blockchain, CBDCs, compliance, crowdfunding, cryptocurrencies, cybersecurity, decentralized finance, digital finance, embedded finance, fintech, financial infrastructure, financial inclusion, financial innovation, financial intermediation, financial markets, household finance, insurtech, machine learning, market microstructure, payments, platforms, regulation, risk management, stablecoins, tokenization, text analytics.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SHoF Annual Conference on the Future of Private Capital Markets</t>
+          <t>2026 FMA Applied Finance Conference</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>St. John's University - Manhattan Campus, New York, NY</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$50 USD (FMA-members) and $60 USD (non-members)</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Private equity and private credit market structure, Private capital strategies and performance, The interaction between private and public capital markets, Private capital and corporate investment, productivity, and innovation, Structured lending within the private market, Fund organization, governance, and incentives, Financing of infrastructure and energy transition, Risk-taking and financial stability implications, The role of private capital in downturns and periods of financial stress, Regulatory and policy implications of the growth of private markets, ESG, sustainability, and impact in private capital markets</t>
+          <t>high-quality papers from scholars and practitioners in the fields of finance and accounting that inform practice, address contemporary global issues, and introduce new hypotheses for research</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CU Denver 9th Annual J.P. Morgan Center International Commodities Symposium</t>
+          <t>Exeter Sustainable Finance Conference 2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Denver, CO</t>
+          <t>University of Exeter Business School, Exeter, UK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 GBP</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Broad global commodity sectors (energy, metals and minerals, and agriculture), commodity futures, derivatives, and related research topics</t>
+          <t>Sustainable finance, interdisciplinary research approaches</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Bocconi-Bristol Second Sustainability and Green Finance Research Workshop</t>
+          <t>9th Cryptocurrency Research Conference (CRC2026)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bocconi University, Milan (Italy)</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>0 EUR</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>New Global Challenges: Climate Change, Biodiversity Loss, and Geopolitical Risk</t>
+          <t>cryptocurrencies, digital finance, FinTech, tokenomics, blockchain economics</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Alliance for Research on Corporate Sustainability (ARCS) 18th Annual Research Conference</t>
+          <t>Accountability in a Sustainable World Conference</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Nanyang Business School, Nanyang Technological University (Singapore)</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>200 USD</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Climate change/risk management, decarbonization challenges and opportunities, technology/AI-driven sustainability solutions, corporate impacts on biodiversity and nature-based business solutions, sustainability reporting and disclosure, sustainable/responsible supply chains, sustainable finance, green marketing, green entrepreneurship, renewable energy investments, cleantech innovation, sustainable natural resource management, business/NGO partnerships, sustainable mobility, social dimensions of sustainability such as inequality, fair wages and working conditions, social and environmental justice, cross-border impacts of geopolitical and regulatory dynamics, and “base of the pyramid” (BoP) development strategies.</t>
+          <t>Non-academic-friendly summaries of research, sustainability, accountability in research</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Finance Research Revolution Conference</t>
+          <t>33rd Finance Forum</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Weggis, Switzerland</t>
+          <t>Alicante, Spain</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CHF 75 per paper</t>
+          <t>50 €</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Machine learning for the cross-section of returns, Big data analysis, Large language models and unstructured data, Non-standard datasets for return predictions, Systematic expectations mistakes and predictable returns, Feasible and implementable portfolios, Predictable turning points</t>
+          <t>Financial Economics research, including Asset Pricing, Corporate Finance, Banking, Portfolio Choice and Asset Management, Microstructure, Regulation, Financial Stability, and Macrofinance</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026 FMA European Conference</t>
+          <t>3rd Workshop on Recent Trends and New Developments in Sustainable, Green and International Finance</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5954,81 +6026,81 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Braga, Portugal</t>
+          <t>Nice, France</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>$75 USD (FMA-members), $85 USD (non-members)</t>
+          <t>220 EUR (academics and professionals), 180 EUR (Ph.D. students)</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>sustainable finance, green finance, climate finance, international finance</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>40th Annual Mitsui Symposium: Private Capital Markets</t>
+          <t>Alpine Finance Summit (AFS) 2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Ann Arbor, Michigan</t>
+          <t>Garmisch-Partenkirchen, Germany</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>50 EUR</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Technology and Private Markets, Private Markets and Real Economic Outcomes, Access to and Democratization of Private Markets, Private Equity and Venture Capital, Private Credit and Direct Lending, Private Real Assets, Entrepreneurship and Innovation</t>
+          <t>Asset Pricing, Investments, Sustainable Finance, FinTech</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Third Chicago Booth Treasury Markets Conference</t>
+          <t>22nd Annual Conference of the Asia-Pacific Association of Derivatives</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Chicago, Illinois</t>
+          <t>Busan, Korea</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6038,71 +6110,71 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Debt sustainability and public finance, Interactions between monetary and fiscal policy, The international role of U.S. Treasuries and the U.S. dollar, Market structure and fragilities in Treasury markets, Treasury basis trades and leveraged intermediation, Interactions between funding markets and Treasury markets, Liquidity provision, market-making capacity, and regulatory constraints, Financial stability implications of Treasury market dynamics</t>
+          <t>Derivatives; Volatility; Risk Management; Asset Pricing; Investments; Corporate Finance; Market Microstructure; Fintech; Regulation; Behavioral Finance</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Cambridge Corporate Finance Theory Symposium 2026</t>
+          <t>NBER-SAIF Conference on AI and Financial Markets</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Cambridge, UK</t>
+          <t>Virtual</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>£50</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Theoretical corporate finance, banking, market micro-structure, asset pricing, financial accounting</t>
+          <t>The impact of investment in AI and supporting technologies on corporate earnings and share prices; the effects of AI on portfolio choices and trading behavior of financial market participants; the role of AI in creating new measures of economic activity; the uses of AI in financial market regulation and risk detection; the consequences of AI for the financial advice industry; the macroeconomic effects of AI on economy-wide discount rates.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Fifth Annual Conference on Financial Markets</t>
+          <t>12th Workshop on Banking and Institutions</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>UCLA Anderson, Los Angeles, CA</t>
+          <t>Bank of Finland, Helsinki</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -6112,108 +6184,108 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Financial markets</t>
+          <t>banking and institutions, geopolitics and banking, political economy of banking, banking and society, banking in emerging markets, climate and banking, monetary policy and institutions</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026 Global Entrepreneurship and Innovation Research Conference (GEIRC)</t>
+          <t>ENTFIN 2026 Conference</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Cambridge, United Kingdom</t>
+          <t>Kedge Business School, Marseille, France</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>200 USD</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Entrepreneurship and innovation, scaling frontier technologies, industrial policy and innovation, university-industry collaboration, global innovation networks, innovation finance, universities, governments, and policy in the new geopolitical era</t>
+          <t>Venture capital; private equity, and buyouts; Business angels and early-stage financing; Crowdfunding; token offerings, and digital finance; Entrepreneurial banking and credit relationships; Corporate governance, contracts, and monitoring; Financial innovation; FinTech, and AI in entrepreneurial finance; ESG, sustainability, and impact finance; Entrepreneurial ecosystems and regional financing gaps; Entrepreneurial risk-taking and behavioral finance; Impact assessment for publicly supported financial instruments.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>5th Annual Hong Kong Conference on FinTech and AI in Finance</t>
+          <t>9th Short-Term Funding Markets Conference</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Hong Kong SAR</t>
+          <t>Federal Reserve Board, Washington, D.C.</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0 USD</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Empirical finance with AI and Big Data applications, New empirical method development in machine learning and financial econometrics, Blockchain technology, digital assets, and frontier FinTech topics</t>
+          <t>Maturity and liquidity transformation by financial intermediaries, Repo markets and clearing institutions, Theories of frictions and fragility in funding markets, Effects of regulation and central bank intervention, Securities lending, Money creation and demand for safe assets, Fintech and encrypted currency</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026 Annual International Journal of Central Banking Research Conference</t>
+          <t>21st Central Bank Conference on the Microstructure of Financial Markets</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Swiss National Bank, Bern</t>
+          <t>Eltville am Rhein, Germany</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -6223,34 +6295,34 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>New Technologies and Their Implications for Monetary Policy and Financial Stability, AI and automation impact on inflation dynamics, financial stability risks from technological developments, central banks' toolkits in an AI-driven economy, transformation of financial markets, macroprudential supervision risks and opportunities, effects of technological advances on monetary policy transmission mechanism, use of AI in optimizing monetary policy decision making</t>
+          <t>Artificial intelligence and market microstructure, The functioning and resilience of sovereign bond and repo markets</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Research in Behavioral Finance Conference 2026</t>
+          <t>2026 PRIVATE EQUITY RESEARCH CONSORTIUM (PERC) EUROPE SYMPOSIUM</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Amsterdam, the Netherlands</t>
+          <t>Oxford, England</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6260,71 +6332,71 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>all aspects of behavioral finance, financial behavior of individuals, financial behavior of groups and organizations, dynamics of markets</t>
+          <t>private equity, buyouts, distressed securities, mezzanine financing, special situations, private credit, venture capital, real estate, real assets</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>9th Annual GRASFI Conference</t>
+          <t>Lake District Workshop in Corporate Finance</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Liège, Belgium</t>
+          <t>Windermere, Lake District, United Kingdom</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£60</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sustainable Finance</t>
+          <t>Corporate finance, mergers and acquisitions, corporate governance, financial institutions</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Red Rock Finance Conference 2026</t>
+          <t>8th Annual Workshop on Financial Institutions Research</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Zion National Park</t>
+          <t>Gateway Conference Center, Federal Reserve Bank of St. Louis; St. Louis, MO USA</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6334,108 +6406,108 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Any topic related to finance</t>
+          <t>Bank Regulation, Supervision, and Compliance; Bank Risk-taking, Stability, and Financial Crises; Lending and Credit Allocation; Bank Governance, Ownership, and Compensation; Bank Disclosure, Accounting, and the Information Environment; Deposits, Funding Structure, and Liability Management; Financial Technology, Innovation, and Bank Competition</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Inaugural Rutgers Finance Research Conference</t>
+          <t>Southern Finance Association 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-11-18</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Rutgers Business School – Newark &amp; New Brunswick, NJ</t>
+          <t>LaQuinta Resort, Palm Springs, CA</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>$75 USD</t>
+          <t>50 USD</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>All areas of finance</t>
+          <t>Papers on any area of finance, panel discussions, special sessions, tutorials</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AI in Finance Conference</t>
+          <t>International Accounting &amp; Finance Doctoral Symposium (IAFDS)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Washington, DC, USA</t>
+          <t>Cagliari, Sardinia, Italy</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£300</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Opportunities and risks of AI technologies in Finance, uses of AI by firms in corporate finance, AI use in trading and asset management, AI use by banks and credit providers, AI in financial forecasting, AI and consumer financial behavior, AI and labor replacement vs. augmentation, financial market implications of AI, risks to financial stability, frictions in AI adoption</t>
+          <t>Original empirical and theoretical papers in accounting and finance (including banking), focusing on significant and impactful issues within these fields.</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026 UNSW Corporate Finance Workshop</t>
+          <t>13th Annual Conference on Risk Governance</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Coogee Beach, Sydney, Australia</t>
+          <t>University of Siegen, Siegen/Germany</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6445,34 +6517,34 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>All areas of Finance, with a special focus on Corporate Finance, including banking, household and entrepreneurial finance</t>
+          <t>Risk Governance in the boardroom, Risk Governance and the monitoring role of supervisory boards, Balancing risk and opportunity, Stakeholder influence and external pressure, Sustainability and Risk Governance, Understanding black swans, Strategic resilience at the top, Considering risk strategies on bank boards, Tackling digitalization-related risks, The role of artificial intelligence for board decisions, Machine learning and risk-responsive decision-making</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>9th Bristol Workshop on Banking and Financial Intermediation</t>
+          <t>SHoF Annual Conference on the Future of Private Capital Markets</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>University of Bristol, Bristol UK</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6482,47 +6554,71 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>theoretical and empirical papers in banking and financial intermediation</t>
+          <t>Private equity and private credit market structure, Private capital strategies and performance, The interaction between private and public capital markets, Private capital and corporate investment, productivity, and innovation, Structured lending within the private market, Fund organization, governance, and incentives, Financing of infrastructure and energy transition, Risk-taking and financial stability implications, The role of private capital in downturns and periods of financial stress, Regulatory and policy implications of the growth of private markets, ESG, sustainability, and impact in private capital markets</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Please provide the text of the announcement so I can extract the required information for you.</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr"/>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
+          <t>CU Denver 9th Annual J.P. Morgan Center International Commodities Symposium</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Denver, CO</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Recent developments in commodity business, research on global commodity sectors (energy, metals and minerals, agriculture), commodity futures, derivatives, and related research topics</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Boulder Summer Conference on Consumer Financial Decision Making</t>
+          <t>Bocconi-Bristol Second Sustainability and Green Finance Research Workshop</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Boulder, Colorado (St. Julien Hotel and Spa)</t>
+          <t>Bocconi University, Milan (Italy)</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6532,145 +6628,145 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Financial behavior and consumer decision-making</t>
+          <t>New Global Challenges: Climate Change, Biodiversity Loss, and Geopolitical Risk</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Oxford Saïd - VU SBE Macro-finance Conference</t>
+          <t>Alliance for Research on Corporate Sustainability (ARCS) 18th Annual Research Conference</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Saïd Business School, University of Oxford</t>
+          <t>Nanyang Business School, Nanyang Technological University (Singapore)</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>₤45</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Monetary policy, macroprudential policy, and fiscal policy; Credit, banks, bankruptcy and systemic risks; International finance, exchange rates, sovereign debt, and debt sustainability; Climate risks and macro-financial implications</t>
+          <t>Climate change/risk management, decarbonization challenges and opportunities, technology/AI-driven sustainability solutions, corporate impacts on biodiversity and nature-based business solutions, sustainability reporting and disclosure, sustainable/responsible supply chains, sustainable finance, green marketing, green entrepreneurship, renewable energy investments, cleantech innovation, sustainable natural resource management, business/NGO partnerships, sustainable mobility, social dimensions of sustainability such as inequality, fair wages and working conditions, social and environmental justice, cross-border impacts of geopolitical and regulatory dynamics, and “base of the pyramid” (BoP) development strategies.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Labor &amp; Finance Group Spring 2026 Conference</t>
+          <t>Finance Research Revolution Conference</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Vanderbilt University - Owen Graduate School of Management, Nashville, TN</t>
+          <t>Weggis, Switzerland</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>CHF 75 per paper</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Human capital, compensation, and incentives; Labor market power, monopsony/oligopsony, and wage setting; Unions, collective bargaining, and worker representation; Organizational design, internal labor markets, and corporate governance; Labor mobility, non-compete agreements, and talent flows; Labor-related disclosure, regulation, and policy; Labor and financial markets, asset pricing, and corporate policies; Entrepreneurship and innovation</t>
+          <t>Machine learning for the cross-section of returns, Big data analysis, Large language models and unstructured data, Non-standard datasets for return predictions, Systematic expectations mistakes and predictable returns, Feasible and implementable portfolios, Predictable turning points</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CEPR 11th European Workshop on Household Finance</t>
+          <t>2026 FMA European Conference</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2025-01-29</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Deutsche Bundesbank Training Centre at Eltville am Rhein</t>
+          <t>Braga, Portugal</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>50 euro</t>
+          <t>$75 USD (FMA-members), $85 USD (non-members)</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Patterns of asset allocation and debt behaviour over the life cycle, Financing retirement and the demographic transition, Consumer indebtedness, financial distress and default decisions, Behavioural approaches to household finances, Financial literacy and financial education programmes, Trust, subjective expectations, pessimism, and financial decisions, International comparisons of household finances using micro-data, Cognitive and genetic studies on individual financial performance, Financial advice and legal protection of investors and borrowers, The impact of technology on household financial behaviour</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>The 10th Vietnam International Conference in Finance</t>
+          <t>40th Annual Mitsui Symposium: Private Capital Markets</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Hanoi, Vietnam</t>
+          <t>Ann Arbor, Michigan</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6680,34 +6776,34 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Corporate finance and governance, Asset pricing, investment, and portfolio management, Finance and sustainability, Financial markets and institutions, Financial technology, artificial intelligence, and big data, Banking and financial regulations, Behavioral finance, Risk management and quantitative finance, Household finance and financial consumer protection</t>
+          <t>Technology and Private Markets, Private Markets and Real Economic Outcomes, Access to and Democratization of Private Markets, Private Equity and Venture Capital, Private Credit and Direct Lending, Private Real Assets, Entrepreneurship and Innovation</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Inaugural Rutgers Finance Research Conference</t>
+          <t>Third Chicago Booth Treasury Markets Conference</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Rutgers Business School - Newark, NJ</t>
+          <t>Chicago, Illinois</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6717,71 +6813,71 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Innovative research across all areas of finance</t>
+          <t>Debt sustainability and public finance, Interactions between monetary and fiscal policy, The international role of U.S. Treasuries and the U.S. dollar, Market structure and fragilities in Treasury markets, Treasury basis trades and leveraged intermediation, Interactions between funding markets and Treasury markets, Liquidity provision, market-making capacity, and regulatory constraints, Financial stability implications of Treasury market dynamics</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2nd EDHEC AI and Finance Workshop</t>
+          <t>Cambridge Corporate Finance Theory Symposium 2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>EDHEC Business School, Nice, France</t>
+          <t>Cambridge, UK</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>£50</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>NLP &amp; large language models, Speech and multimedia analysis, AI agents &amp; automation, Machine learning &amp; predictive analytics, Big data &amp; computational methods, The role of AI in corporate decision-making and other aspects of financial and labor markets, Ethics, policy, and regulation</t>
+          <t>Theoretical corporate finance, banking, market micro-structure, asset pricing, financial accounting</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Journal of International Money and Finance Special Issue and Conference</t>
+          <t>The Fifth Annual Conference on Financial Markets</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Hitotsubashi University, Tokyo, Japan</t>
+          <t>UCLA Anderson, Los Angeles, CA</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6791,14 +6887,14 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Banks’ ESG and Climate Responsibilities, Banks as ESG and Climate Gatekeepers for Corporations, Banks, Climate Risk, and Financial Stability, Regulations, ESG, and Climate Risk, Central Banks, Banking Regulations, and Green Finance</t>
+          <t>financial markets</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3rd Structured Retail Products and Derivatives Conference</t>
+          <t>2026 Global Entrepreneurship and Innovation Research Conference (GEIRC)</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6808,138 +6904,27 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Hagen, Germany</t>
+          <t>Cambridge, United Kingdom</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>200 USD</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>behavioral aspects, hedging strategies, market microstructure, pricing policies, product innovations, product valuation, regulatory issues</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>QRFE Workshop on Climate Change</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Durham, United Kingdom</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>Climate Risk Pricing &amp; Asset Valuation, Institutional Investors &amp; Climate Exposure, Green Finance, ESG, and Real Effects, Carbon Emissions, Disclosure, and Regulatory Policy, Climate Risk Transmission Across Markets, Innovation, Transition Technologies, and Real Economic Impact, Data and Methodological Frontiers</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Commodity and Energy Markets Association (CEMA) 2026 Annual Meeting</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>ESSEC Business School, France</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>Economics, finance, mathematics, operations, risk management, energy and commodity sourcing, processing, trading, financial and operational risk analysis, decision making, optimization for sustainable ecosystems</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>3rd QRFE Workshop on Quantitative Finance</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Durham, United Kingdom</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Big Data &amp; Information Efficiency, AI, Automation &amp; Liquidity, Modern Market Design, Blockchain &amp; Digital Market Microstructure, Stability, Systemic Risk &amp; Real Effects, Policy, Regulation &amp; SupTech</t>
+          <t>Entrepreneurship and innovation, scaling frontier technologies, industrial policy and innovation, university-industry collaboration, global innovation networks, innovation finance, universities and policy in the new geopolitical era</t>
         </is>
       </c>
     </row>
